--- a/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
+++ b/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I368"/>
+  <dimension ref="A1:I374"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -384,7 +384,7 @@
       </c>
       <c r="G6" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">✨ {name}が練習で目を引くプレーを見せた</t>
+          <t xml:space="preserve">✨ {name}が練習で目を引く動きを見せた</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.label</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.label</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -7574,19 +7574,19 @@
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.label</t>
+          <t xml:space="preserve">faction_decree.label</t>
         </is>
       </c>
       <c r="G261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コーチ雇用決裁書</t>
+          <t xml:space="preserve">派閥解散命令</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.categoryLabel</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.categoryLabel</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.categoryLabel</t>
+          <t xml:space="preserve">faction_decree.categoryLabel</t>
         </is>
       </c>
       <c r="G262" t="inlineStr" s="3">
@@ -7613,7 +7613,7 @@
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.body</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.body</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -7628,19 +7628,19 @@
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.body</t>
+          <t xml:space="preserve">faction_decree.body</t>
         </is>
       </c>
       <c r="G263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新たなスタッフを招聘し、団体の指導体制を強化する</t>
+          <t xml:space="preserve">団体内の派閥を社長命令で解散させ、以後の結成を認めるかどうかを決める</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.detailText</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.detailText</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -7655,19 +7655,19 @@
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.detailText</t>
+          <t xml:space="preserve">faction_decree.detailText</t>
         </is>
       </c>
       <c r="G264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新たなコーチを招聘し、指導体制を強化する。机には並ばず、コーチ画面から実行する特殊書類。</t>
+          <t xml:space="preserve">選手たちが自然に作った群れを、上から畳む。畳まれた側は当然おもしろくない。とくに束ねていた本人には深く残る。勢いに乗っていた派閥ほど、その傷は深い。</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.effectSummary</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.effectSummary</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -7682,19 +7682,19 @@
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.effectSummary</t>
+          <t xml:space="preserve">faction_decree.effectSummary</t>
         </is>
       </c>
       <c r="G265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コーチを1名新しく迎える(決裁枠を2消費)</t>
+          <t xml:space="preserve">選択した内容によって、解散のみ／解散して以後禁止／禁止の解除 が実行される</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.recommendation</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.recommendation</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -7709,19 +7709,19 @@
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.recommendation</t>
+          <t xml:space="preserve">faction_decree.recommendation</t>
         </is>
       </c>
       <c r="G266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コーチ枠に空きがあり、新規雇用を検討している週に。机に書類として表示されない点に注意。</t>
+          <t xml:space="preserve">派閥の揉め事を団体から切り離したいときに。まだ派閥が生まれていないうちに禁止しておけば、誰の信頼も損なわずに済む。</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.label</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -7731,24 +7731,24 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">hireCoach.label</t>
         </is>
       </c>
       <c r="G267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無難な線です。ただ、響くかどうかは相手次第かと。</t>
+          <t xml:space="preserve">コーチ雇用決裁書</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.categoryLabel</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -7758,24 +7758,24 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">hireCoach.categoryLabel</t>
         </is>
       </c>
       <c r="G268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">彼女の格に見合った額かと存じます。</t>
+          <t xml:space="preserve">人事</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[3]</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.body</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -7785,24 +7785,24 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">hireCoach.body</t>
         </is>
       </c>
       <c r="G269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相場を超えています。誠意は伝わるはずです。</t>
+          <t xml:space="preserve">新たなスタッフを招聘し、団体の指導体制を強化する</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[4]</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.detailText</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -7812,24 +7812,24 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">hireCoach.detailText</t>
         </is>
       </c>
       <c r="G270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……思い切りましたな。ここまで出す団体は他にありません。</t>
+          <t xml:space="preserve">新たなコーチを招聘し、指導体制を強化する。机には並ばず、コーチ画面から実行する特殊書類。</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.effectSummary</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -7839,24 +7839,24 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">hireCoach.effectSummary</t>
         </is>
       </c>
       <c r="G271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}と{name2}が朝から激しいスパーリングを繰り広げている…！</t>
+          <t xml:space="preserve">コーチを1名新しく迎える(決裁枠を2消費)</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.recommendation</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -7866,24 +7866,24 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">hireCoach.recommendation</t>
         </is>
       </c>
       <c r="G272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夜の自主練で{name1}が黙々とスクワットをしている…</t>
+          <t xml:space="preserve">コーチ枠に空きがあり、新規雇用を検討している週に。机に書類として表示されない点に注意。</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[3]</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[1]</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -7893,24 +7893,24 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}が{name2}に技の受け身を教えている場面が見られた</t>
+          <t xml:space="preserve">無難な線です。ただ、響くかどうかは相手次第かと。</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[4]</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[2]</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -7920,24 +7920,24 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿の食事は{name1}が率先して準備していた</t>
+          <t xml:space="preserve">彼女の格に見合った額かと存じます。</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[5]</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[3]</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -7947,24 +7947,24 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}と{name2}が夕食後のランニングで競い合っている</t>
+          <t xml:space="preserve">相場を超えています。誠意は伝わるはずです。</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[6]</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[4]</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -7974,24 +7974,24 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[6]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早朝の海辺で{name1}が一人、基礎練習に励んでいた</t>
+          <t xml:space="preserve">……思い切りましたな。ここまで出す団体は他にありません。</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[7]</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[1]</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -8006,19 +8006,19 @@
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[7]</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}が新技の研究に没頭している姿が印象的だった</t>
+          <t xml:space="preserve">{name1}と{name2}が朝から激しいスパーリングを繰り広げている…！</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[8]</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[2]</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -8033,19 +8033,19 @@
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[8]</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">消灯後も{name1}と{name2}がリングで語り合っていた</t>
+          <t xml:space="preserve">夜の自主練で{name1}が黙々とスクワットをしている…</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[9]</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[3]</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -8060,19 +8060,19 @@
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[9]</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}が合宿の記念写真を撮ろうとみんなを集めていた</t>
+          <t xml:space="preserve">{name1}が{name2}に技の受け身を教えている場面が見られた</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[10]</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[4]</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -8087,19 +8087,19 @@
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[10]</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員で浜辺を走るメニューに{name1}が一番乗りでゴールした</t>
+          <t xml:space="preserve">合宿の食事は{name1}が率先して準備していた</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[11]</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[5]</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -8114,19 +8114,19 @@
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[11]</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}のムードメーカーぶりで合宿の雰囲気がぐっと明るくなった</t>
+          <t xml:space="preserve">{name1}と{name2}が夕食後のランニングで競い合っている</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[12]</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[6]</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -8141,19 +8141,19 @@
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[12]</t>
+          <t xml:space="preserve">[6]</t>
         </is>
       </c>
       <c r="G282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習後の大浴場で{name1}と{name2}が今後の抱負を語り合っていた</t>
+          <t xml:space="preserve">早朝の海辺で{name1}が一人、基礎練習に励んでいた</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].text</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[7]</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -8163,24 +8163,24 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[1].text</t>
+          <t xml:space="preserve">[7]</t>
         </is>
       </c>
       <c r="G283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}が練習中にアクシデント</t>
+          <t xml:space="preserve">{name1}が新技の研究に没頭している姿が印象的だった</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].detail</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[8]</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -8190,24 +8190,24 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[1].detail</t>
+          <t xml:space="preserve">[8]</t>
         </is>
       </c>
       <c r="G284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が練習中に技を受けた際にバランスを崩し、負傷してしまった。</t>
+          <t xml:space="preserve">消灯後も{name1}と{name2}がリングで語り合っていた</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].text</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[9]</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -8217,24 +8217,24 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[2].text</t>
+          <t xml:space="preserve">[9]</t>
         </is>
       </c>
       <c r="G285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}が練習で負傷</t>
+          <t xml:space="preserve">{name1}が合宿の記念写真を撮ろうとみんなを集めていた</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].detail</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[10]</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -8244,24 +8244,24 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[2].detail</t>
+          <t xml:space="preserve">[10]</t>
         </is>
       </c>
       <c r="G286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スパーリング中に{name}が相手の技を受け損ね、マットに叩きつけられた。</t>
+          <t xml:space="preserve">全員で浜辺を走るメニューに{name1}が一番乗りでゴールした</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].text</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[11]</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -8271,24 +8271,24 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[3].text</t>
+          <t xml:space="preserve">[11]</t>
         </is>
       </c>
       <c r="G287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}に練習中のトラブル</t>
+          <t xml:space="preserve">{name1}のムードメーカーぶりで合宿の雰囲気がぐっと明るくなった</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].detail</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[12]</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -8298,24 +8298,24 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[3].detail</t>
+          <t xml:space="preserve">[12]</t>
         </is>
       </c>
       <c r="G288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が新技の練習中に着地に失敗。痛みを訴えている。</t>
+          <t xml:space="preserve">練習後の大浴場で{name1}と{name2}が今後の抱負を語り合っていた</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].text</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -8330,19 +8330,19 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[4].text</t>
+          <t xml:space="preserve">B1[1].text</t>
         </is>
       </c>
       <c r="G289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}がロープワーク中に負傷</t>
+          <t xml:space="preserve">⚠️ {name}が練習中にアクシデント</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].detail</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -8357,19 +8357,19 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[4].detail</t>
+          <t xml:space="preserve">B1[1].detail</t>
         </is>
       </c>
       <c r="G290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ロープの反動を利用した連続技の練習中、{name}の足がロープに絡まり転倒。すぐには立ち上がれなかった。</t>
+          <t xml:space="preserve">{name}が練習中に技を受けた際にバランスを崩し、負傷してしまった。</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].text</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -8384,19 +8384,19 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[5].text</t>
+          <t xml:space="preserve">B1[2].text</t>
         </is>
       </c>
       <c r="G291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}がスパーリング中に痛みを訴えた</t>
+          <t xml:space="preserve">⚠️ {name}が練習で負傷</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].detail</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -8411,19 +8411,19 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[5].detail</t>
+          <t xml:space="preserve">B1[2].detail</t>
         </is>
       </c>
       <c r="G292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習パートナーとのスパーリングで{name}が技を受けた直後、顔をしかめて膝をついた。本人は続けられると言うが…</t>
+          <t xml:space="preserve">スパーリング中に{name}が相手の技を受け損ね、マットに叩きつけられた。</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].text</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -8438,19 +8438,19 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[6].text</t>
+          <t xml:space="preserve">B1[3].text</t>
         </is>
       </c>
       <c r="G293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}が練習後に体の異変を報告</t>
+          <t xml:space="preserve">⚠️ {name}に練習中のトラブル</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].detail</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -8465,19 +8465,19 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[6].detail</t>
+          <t xml:space="preserve">B1[3].detail</t>
         </is>
       </c>
       <c r="G294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を終えた{name}が、動かすと痛む箇所があると申告。無理をしていた可能性がある。</t>
+          <t xml:space="preserve">{name}が新技の練習中に着地に失敗。痛みを訴えている。</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].text</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -8492,19 +8492,19 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[1].text</t>
+          <t xml:space="preserve">B1[4].text</t>
         </is>
       </c>
       <c r="G295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}が衝突</t>
+          <t xml:space="preserve">⚠️ {name}がロープワーク中に負傷</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].detail</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -8519,19 +8519,19 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[1].detail</t>
+          <t xml:space="preserve">B1[4].detail</t>
         </is>
       </c>
       <c r="G296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">控室で{name1}と{name2}の間に激しい口論が発生。周囲の制止も聞かず一触即発の状態になっている。</t>
+          <t xml:space="preserve">ロープの反動を利用した連続技の練習中、{name}の足がロープに絡まり転倒。すぐには立ち上がれなかった。</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].text</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -8546,19 +8546,19 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[2].text</t>
+          <t xml:space="preserve">B1[5].text</t>
         </is>
       </c>
       <c r="G297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}の対立が深刻化</t>
+          <t xml:space="preserve">⚠️ {name}がスパーリング中に痛みを訴えた</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].detail</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -8573,19 +8573,19 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[2].detail</t>
+          <t xml:space="preserve">B1[5].detail</t>
         </is>
       </c>
       <c r="G298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前から不穏な空気があった{name1}と{name2}の関係がついに破綻。練習にも支障が出始めている。</t>
+          <t xml:space="preserve">練習パートナーとのスパーリングで{name}が技を受けた直後、顔をしかめて膝をついた。本人は続けられると言うが…</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].text</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -8600,19 +8600,19 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[3].text</t>
+          <t xml:space="preserve">B1[6].text</t>
         </is>
       </c>
       <c r="G299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}がスパーリングでエスカレート</t>
+          <t xml:space="preserve">⚠️ {name}が練習後に体の異変を報告</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].detail</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -8627,19 +8627,19 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[3].detail</t>
+          <t xml:space="preserve">B1[6].detail</t>
         </is>
       </c>
       <c r="G300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本来は軽い打ち合いのはずが、{name1}と{name2}のスパーリングが本気のぶつかり合いに発展。コーチが間に割って入る事態となった。</t>
+          <t xml:space="preserve">練習を終えた{name}が、動かすと痛む箇所があると申告。無理をしていた可能性がある。</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].text</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -8654,19 +8654,19 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[4].text</t>
+          <t xml:space="preserve">B2[1].text</t>
         </is>
       </c>
       <c r="G301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}の間に亀裂</t>
+          <t xml:space="preserve">💥 {name1}と{name2}が衝突</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].detail</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -8681,19 +8681,19 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[4].detail</t>
+          <t xml:space="preserve">B2[1].detail</t>
         </is>
       </c>
       <c r="G302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}がSNSに意味深な投稿をしたことで{name2}が激怒。控室で怒鳴り合う二人の声が外まで漏れていた。</t>
+          <t xml:space="preserve">控室で{name1}と{name2}の間に激しい口論が発生。周囲の制止も聞かず一触即発の状態になっている。</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].text</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -8708,19 +8708,19 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[5].text</t>
+          <t xml:space="preserve">B2[2].text</t>
         </is>
       </c>
       <c r="G303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}の関係が限界に</t>
+          <t xml:space="preserve">💥 {name1}と{name2}の対立が深刻化</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].detail</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -8735,19 +8735,19 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[5].detail</t>
+          <t xml:space="preserve">B2[2].detail</t>
         </is>
       </c>
       <c r="G304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合同練習中、{name1}が{name2}への不満を公然と口にした。全員の前での出来事に、チーム全体が凍りついた。</t>
+          <t xml:space="preserve">以前から不穏な空気があった{name1}と{name2}の関係がついに破綻。練習にも支障が出始めている。</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].text</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -8762,19 +8762,19 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[1].text</t>
+          <t xml:space="preserve">B2[3].text</t>
         </is>
       </c>
       <c r="G305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚔️ {orgName}から挑戦状</t>
+          <t xml:space="preserve">💥 {name1}と{name2}がスパーリングでエスカレート</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].detail</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -8789,19 +8789,19 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[1].detail</t>
+          <t xml:space="preserve">B2[3].detail</t>
         </is>
       </c>
       <c r="G306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{orgName}が「実力を見せてやる」と挑戦状を叩きつけてきた。</t>
+          <t xml:space="preserve">本来は軽い打ち合いのはずが、{name1}と{name2}のスパーリングが本気のぶつかり合いに発展。コーチが間に割って入る事態となった。</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].text</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -8816,19 +8816,19 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[2].text</t>
+          <t xml:space="preserve">B2[4].text</t>
         </is>
       </c>
       <c r="G307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚔️ {orgName}が宣戦布告</t>
+          <t xml:space="preserve">💥 {name1}と{name2}の間に亀裂</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].detail</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -8843,19 +8843,19 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[2].detail</t>
+          <t xml:space="preserve">B2[4].detail</t>
         </is>
       </c>
       <c r="G308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{orgName}の代表が公の場でこちらの団体を挑発。挑戦状で決着をつけようと迫ってきた。</t>
+          <t xml:space="preserve">{name1}がSNSに意味深な投稿をしたことで{name2}が激怒。控室で怒鳴り合う二人の声が外まで漏れていた。</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].text</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -8870,19 +8870,19 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[3].text</t>
+          <t xml:space="preserve">B2[5].text</t>
         </is>
       </c>
       <c r="G309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚔️ {orgName}の選手が記者会見で挑発</t>
+          <t xml:space="preserve">💥 {name1}と{name2}の関係が限界に</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].detail</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -8897,19 +8897,19 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[3].detail</t>
+          <t xml:space="preserve">B2[5].detail</t>
         </is>
       </c>
       <c r="G310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{orgName}の選手がメディアの前でこちらの団体名を出し、「いつでも受けて立つ」と公開挑戦状を叩きつけた。</t>
+          <t xml:space="preserve">合同練習中、{name1}が{name2}への不満を公然と口にした。全員の前での出来事に、チーム全体が凍りついた。</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].text</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -8924,19 +8924,19 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[4].text</t>
+          <t xml:space="preserve">B3[1].text</t>
         </is>
       </c>
       <c r="G311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚔️ {orgName}から果たし状が届いた</t>
+          <t xml:space="preserve">⚔️ {orgName}から挑戦状</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].detail</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -8951,19 +8951,19 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[4].detail</t>
+          <t xml:space="preserve">B3[1].detail</t>
         </is>
       </c>
       <c r="G312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{orgName}から正式な書面が届いた。「団体の威信をかけて一騎打ちを行いたい」——無視するわけにはいかない雰囲気だ。</t>
+          <t xml:space="preserve">{orgName}が「実力を見せてやる」と挑戦状を叩きつけてきた。</t>
         </is>
       </c>
     </row>
     <row r="313" ht="40" customHeight="1">
       <c r="A313" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].text</t>
         </is>
       </c>
       <c r="B313" t="inlineStr" s="2">
@@ -8978,19 +8978,19 @@
       </c>
       <c r="D313" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[5].text</t>
+          <t xml:space="preserve">B3[2].text</t>
         </is>
       </c>
       <c r="G313" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚔️ {orgName}が興行に乗り込んできた</t>
+          <t xml:space="preserve">⚔️ {orgName}が宣戦布告</t>
         </is>
       </c>
     </row>
     <row r="314" ht="40" customHeight="1">
       <c r="A314" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].detail</t>
         </is>
       </c>
       <c r="B314" t="inlineStr" s="2">
@@ -9005,19 +9005,19 @@
       </c>
       <c r="D314" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[5].detail</t>
+          <t xml:space="preserve">B3[2].detail</t>
         </is>
       </c>
       <c r="G314" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">こちらの興行会場に{orgName}の関係者が姿を見せ、「リングで語り合おう」と挑戦状を突きつけてきた。</t>
+          <t xml:space="preserve">{orgName}の代表が公の場でこちらの団体を挑発。挑戦状で決着をつけようと迫ってきた。</t>
         </is>
       </c>
     </row>
     <row r="315" ht="40" customHeight="1">
       <c r="A315" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].text</t>
         </is>
       </c>
       <c r="B315" t="inlineStr" s="2">
@@ -9032,19 +9032,19 @@
       </c>
       <c r="D315" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.youngStar[1].text</t>
+          <t xml:space="preserve">B3[3].text</t>
         </is>
       </c>
       <c r="G315" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}から若手特集の申し入れ</t>
+          <t xml:space="preserve">⚔️ {orgName}の選手が記者会見で挑発</t>
         </is>
       </c>
     </row>
     <row r="316" ht="40" customHeight="1">
       <c r="A316" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].detail</t>
         </is>
       </c>
       <c r="B316" t="inlineStr" s="2">
@@ -9059,19 +9059,19 @@
       </c>
       <c r="D316" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.youngStar[1].detail</t>
+          <t xml:space="preserve">B3[3].detail</t>
         </is>
       </c>
       <c r="G316" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「次世代のスターを追いかけたい」と密着取材を申し出ている。</t>
+          <t xml:space="preserve">{orgName}の選手がメディアの前でこちらの団体名を出し、「いつでも受けて立つ」と公開挑戦状を叩きつけた。</t>
         </is>
       </c>
     </row>
     <row r="317" ht="40" customHeight="1">
       <c r="A317" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].text</t>
         </is>
       </c>
       <c r="B317" t="inlineStr" s="2">
@@ -9086,19 +9086,19 @@
       </c>
       <c r="D317" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.youngStar[2].text</t>
+          <t xml:space="preserve">B3[4].text</t>
         </is>
       </c>
       <c r="G317" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}が注目の新星を追いたいと打診</t>
+          <t xml:space="preserve">⚔️ {orgName}から果たし状が届いた</t>
         </is>
       </c>
     </row>
     <row r="318" ht="40" customHeight="1">
       <c r="A318" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].detail</t>
         </is>
       </c>
       <c r="B318" t="inlineStr" s="2">
@@ -9113,19 +9113,19 @@
       </c>
       <c r="D318" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.youngStar[2].detail</t>
+          <t xml:space="preserve">B3[4].detail</t>
         </is>
       </c>
       <c r="G318" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}のディレクターが「若い才能に密着したい」と話を持ちかけてきた。</t>
+          <t xml:space="preserve">{orgName}から正式な書面が届いた。「団体の威信をかけて一騎打ちを行いたい」——無視するわけにはいかない雰囲気だ。</t>
         </is>
       </c>
     </row>
     <row r="319" ht="40" customHeight="1">
       <c r="A319" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].text</t>
         </is>
       </c>
       <c r="B319" t="inlineStr" s="2">
@@ -9140,19 +9140,19 @@
       </c>
       <c r="D319" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.youngStar[3].text</t>
+          <t xml:space="preserve">B3[5].text</t>
         </is>
       </c>
       <c r="G319" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}の「若手発掘」企画にうちの選手が候補に</t>
+          <t xml:space="preserve">⚔️ {orgName}が興行に乗り込んできた</t>
         </is>
       </c>
     </row>
     <row r="320" ht="40" customHeight="1">
       <c r="A320" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].detail</t>
         </is>
       </c>
       <c r="B320" t="inlineStr" s="2">
@@ -9167,19 +9167,19 @@
       </c>
       <c r="D320" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.youngStar[3].detail</t>
+          <t xml:space="preserve">B3[5].detail</t>
         </is>
       </c>
       <c r="G320" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「プロレス界の未来を担う若手を追う」——{outletName}からそんな企画の依頼が来た。</t>
+          <t xml:space="preserve">こちらの興行会場に{orgName}の関係者が姿を見せ、「リングで語り合おう」と挑戦状を突きつけてきた。</t>
         </is>
       </c>
     </row>
     <row r="321" ht="40" customHeight="1">
       <c r="A321" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].text</t>
         </is>
       </c>
       <c r="B321" t="inlineStr" s="2">
@@ -9194,19 +9194,19 @@
       </c>
       <c r="D321" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ace[1].text</t>
+          <t xml:space="preserve">B4.youngStar[1].text</t>
         </is>
       </c>
       <c r="G321" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}がエース密着企画を提案</t>
+          <t xml:space="preserve">📺 {outletName}から若手特集の申し入れ</t>
         </is>
       </c>
     </row>
     <row r="322" ht="40" customHeight="1">
       <c r="A322" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].detail</t>
         </is>
       </c>
       <c r="B322" t="inlineStr" s="2">
@@ -9221,19 +9221,19 @@
       </c>
       <c r="D322" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ace[1].detail</t>
+          <t xml:space="preserve">B4.youngStar[1].detail</t>
         </is>
       </c>
       <c r="G322" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「団体の顔に密着したい」とドキュメンタリー企画を持ち込んできた。</t>
+          <t xml:space="preserve">{outletName}が「次世代のスターを追いかけたい」と密着取材を申し出ている。</t>
         </is>
       </c>
     </row>
     <row r="323" ht="40" customHeight="1">
       <c r="A323" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].text</t>
         </is>
       </c>
       <c r="B323" t="inlineStr" s="2">
@@ -9248,19 +9248,19 @@
       </c>
       <c r="D323" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ace[2].text</t>
+          <t xml:space="preserve">B4.youngStar[2].text</t>
         </is>
       </c>
       <c r="G323" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}から「頂点の景色」取材オファー</t>
+          <t xml:space="preserve">📺 {outletName}が注目の新星を追いたいと打診</t>
         </is>
       </c>
     </row>
     <row r="324" ht="40" customHeight="1">
       <c r="A324" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].detail</t>
         </is>
       </c>
       <c r="B324" t="inlineStr" s="2">
@@ -9275,19 +9275,19 @@
       </c>
       <c r="D324" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ace[2].detail</t>
+          <t xml:space="preserve">B4.youngStar[2].detail</t>
         </is>
       </c>
       <c r="G324" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「頂点に立つ選手の日常を追いたい」と密着取材を打診してきた。</t>
+          <t xml:space="preserve">{outletName}のディレクターが「若い才能に密着したい」と話を持ちかけてきた。</t>
         </is>
       </c>
     </row>
     <row r="325" ht="40" customHeight="1">
       <c r="A325" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].text</t>
         </is>
       </c>
       <c r="B325" t="inlineStr" s="2">
@@ -9302,19 +9302,19 @@
       </c>
       <c r="D325" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ace[3].text</t>
+          <t xml:space="preserve">B4.youngStar[3].text</t>
         </is>
       </c>
       <c r="G325" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}がトップ選手の特集を企画中</t>
+          <t xml:space="preserve">📺 {outletName}の「若手発掘」企画にうちの選手が候補に</t>
         </is>
       </c>
     </row>
     <row r="326" ht="40" customHeight="1">
       <c r="A326" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].detail</t>
         </is>
       </c>
       <c r="B326" t="inlineStr" s="2">
@@ -9329,19 +9329,19 @@
       </c>
       <c r="D326" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.ace[3].detail</t>
+          <t xml:space="preserve">B4.youngStar[3].detail</t>
         </is>
       </c>
       <c r="G326" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「団体を背負うエースに迫る」——{outletName}からそんなオファーが届いた。推薦する選手を選んでほしいという。</t>
+          <t xml:space="preserve">「プロレス界の未来を担う若手を追う」——{outletName}からそんな企画の依頼が来た。</t>
         </is>
       </c>
     </row>
     <row r="327" ht="40" customHeight="1">
       <c r="A327" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].text</t>
         </is>
       </c>
       <c r="B327" t="inlineStr" s="2">
@@ -9356,19 +9356,19 @@
       </c>
       <c r="D327" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.veteran[1].text</t>
+          <t xml:space="preserve">B4.ace[1].text</t>
         </is>
       </c>
       <c r="G327" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}がベテラン特集を企画</t>
+          <t xml:space="preserve">📺 {outletName}がエース密着企画を提案</t>
         </is>
       </c>
     </row>
     <row r="328" ht="40" customHeight="1">
       <c r="A328" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].detail</t>
         </is>
       </c>
       <c r="B328" t="inlineStr" s="2">
@@ -9383,19 +9383,19 @@
       </c>
       <c r="D328" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.veteran[1].detail</t>
+          <t xml:space="preserve">B4.ace[1].detail</t>
         </is>
       </c>
       <c r="G328" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「長く戦い続ける選手の矜持に迫りたい」と密着取材を申し出ている。</t>
+          <t xml:space="preserve">{outletName}が「団体の顔に密着したい」とドキュメンタリー企画を持ち込んできた。</t>
         </is>
       </c>
     </row>
     <row r="329" ht="40" customHeight="1">
       <c r="A329" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].text</t>
         </is>
       </c>
       <c r="B329" t="inlineStr" s="2">
@@ -9410,19 +9410,19 @@
       </c>
       <c r="D329" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.veteran[2].text</t>
+          <t xml:space="preserve">B4.ace[2].text</t>
         </is>
       </c>
       <c r="G329" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}から「キャリアの深み」取材依頼</t>
+          <t xml:space="preserve">📺 {outletName}から「頂点の景色」取材オファー</t>
         </is>
       </c>
     </row>
     <row r="330" ht="40" customHeight="1">
       <c r="A330" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].detail</t>
         </is>
       </c>
       <c r="B330" t="inlineStr" s="2">
@@ -9437,19 +9437,19 @@
       </c>
       <c r="D330" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.veteran[2].detail</t>
+          <t xml:space="preserve">B4.ace[2].detail</t>
         </is>
       </c>
       <c r="G330" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「経験豊富な選手の素顔を追いたい」とのこと。</t>
+          <t xml:space="preserve">{outletName}が「頂点に立つ選手の日常を追いたい」と密着取材を打診してきた。</t>
         </is>
       </c>
     </row>
     <row r="331" ht="40" customHeight="1">
       <c r="A331" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].text</t>
         </is>
       </c>
       <c r="B331" t="inlineStr" s="2">
@@ -9464,19 +9464,19 @@
       </c>
       <c r="D331" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.veteran[3].text</t>
+          <t xml:space="preserve">B4.ace[3].text</t>
         </is>
       </c>
       <c r="G331" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}が「円熟の技」ドキュメントを提案</t>
+          <t xml:space="preserve">📺 {outletName}がトップ選手の特集を企画中</t>
         </is>
       </c>
     </row>
     <row r="332" ht="40" customHeight="1">
       <c r="A332" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].detail</t>
         </is>
       </c>
       <c r="B332" t="inlineStr" s="2">
@@ -9491,19 +9491,19 @@
       </c>
       <c r="D332" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4.veteran[3].detail</t>
+          <t xml:space="preserve">B4.ace[3].detail</t>
         </is>
       </c>
       <c r="G332" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「ベテランだからこそ見える景色がある」——{outletName}からそんなテーマの企画が持ち込まれた。</t>
+          <t xml:space="preserve">「団体を背負うエースに迫る」——{outletName}からそんなオファーが届いた。推薦する選手を選んでほしいという。</t>
         </is>
       </c>
     </row>
     <row r="333" ht="40" customHeight="1">
       <c r="A333" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].text</t>
         </is>
       </c>
       <c r="B333" t="inlineStr" s="2">
@@ -9518,19 +9518,19 @@
       </c>
       <c r="D333" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm[1].text</t>
+          <t xml:space="preserve">B4.veteran[1].text</t>
         </is>
       </c>
       <c r="G333" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📸 {outletName}からCM出演の打診</t>
+          <t xml:space="preserve">📺 {outletName}がベテラン特集を企画</t>
         </is>
       </c>
     </row>
     <row r="334" ht="40" customHeight="1">
       <c r="A334" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].detail</t>
         </is>
       </c>
       <c r="B334" t="inlineStr" s="2">
@@ -9545,19 +9545,19 @@
       </c>
       <c r="D334" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm[1].detail</t>
+          <t xml:space="preserve">B4.veteran[1].detail</t>
         </is>
       </c>
       <c r="G334" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}から「選手をCMの顔として起用したい」と打診が来た。</t>
+          <t xml:space="preserve">{outletName}が「長く戦い続ける選手の矜持に迫りたい」と密着取材を申し出ている。</t>
         </is>
       </c>
     </row>
     <row r="335" ht="40" customHeight="1">
       <c r="A335" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].text</t>
         </is>
       </c>
       <c r="B335" t="inlineStr" s="2">
@@ -9572,19 +9572,19 @@
       </c>
       <c r="D335" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm[2].text</t>
+          <t xml:space="preserve">B4.veteran[2].text</t>
         </is>
       </c>
       <c r="G335" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📸 {outletName}がCMキャストを探している</t>
+          <t xml:space="preserve">📺 {outletName}から「キャリアの深み」取材依頼</t>
         </is>
       </c>
     </row>
     <row r="336" ht="40" customHeight="1">
       <c r="A336" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].detail</t>
         </is>
       </c>
       <c r="B336" t="inlineStr" s="2">
@@ -9599,19 +9599,19 @@
       </c>
       <c r="D336" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm[2].detail</t>
+          <t xml:space="preserve">B4.veteran[2].detail</t>
         </is>
       </c>
       <c r="G336" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「プロレスラーのカッコよさをCMで表現したい」——{outletName}からそんな依頼が届いた。</t>
+          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「経験豊富な選手の素顔を追いたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="337" ht="40" customHeight="1">
       <c r="A337" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].text</t>
         </is>
       </c>
       <c r="B337" t="inlineStr" s="2">
@@ -9626,19 +9626,19 @@
       </c>
       <c r="D337" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm[3].text</t>
+          <t xml:space="preserve">B4.veteran[3].text</t>
         </is>
       </c>
       <c r="G337" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📸 {outletName}のCM出演オファー</t>
+          <t xml:space="preserve">📺 {outletName}が「円熟の技」ドキュメントを提案</t>
         </is>
       </c>
     </row>
     <row r="338" ht="40" customHeight="1">
       <c r="A338" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].detail</t>
         </is>
       </c>
       <c r="B338" t="inlineStr" s="2">
@@ -9653,19 +9653,19 @@
       </c>
       <c r="D338" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_cm[3].detail</t>
+          <t xml:space="preserve">B4.veteran[3].detail</t>
         </is>
       </c>
       <c r="G338" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「うちの団体の選手を広告塔に使いたい」とのこと。</t>
+          <t xml:space="preserve">「ベテランだからこそ見える景色がある」——{outletName}からそんなテーマの企画が持ち込まれた。</t>
         </is>
       </c>
     </row>
     <row r="339" ht="40" customHeight="1">
       <c r="A339" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].text</t>
         </is>
       </c>
       <c r="B339" t="inlineStr" s="2">
@@ -9680,19 +9680,19 @@
       </c>
       <c r="D339" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure[1].text</t>
+          <t xml:space="preserve">B4_cm[1].text</t>
         </is>
       </c>
       <c r="G339" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📷 {outletName}からグラビア撮影の依頼</t>
+          <t xml:space="preserve">📸 {outletName}からCM出演の打診</t>
         </is>
       </c>
     </row>
     <row r="340" ht="40" customHeight="1">
       <c r="A340" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].detail</t>
         </is>
       </c>
       <c r="B340" t="inlineStr" s="2">
@@ -9707,19 +9707,19 @@
       </c>
       <c r="D340" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure[1].detail</t>
+          <t xml:space="preserve">B4_cm[1].detail</t>
         </is>
       </c>
       <c r="G340" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「プロレスラーの魅力をグラビアで届けたい」と申し出てきた。</t>
+          <t xml:space="preserve">{outletName}から「選手をCMの顔として起用したい」と打診が来た。</t>
         </is>
       </c>
     </row>
     <row r="341" ht="40" customHeight="1">
       <c r="A341" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].text</t>
         </is>
       </c>
       <c r="B341" t="inlineStr" s="2">
@@ -9734,19 +9734,19 @@
       </c>
       <c r="D341" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure[2].text</t>
+          <t xml:space="preserve">B4_cm[2].text</t>
         </is>
       </c>
       <c r="G341" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📷 {outletName}がグラビア特集企画を検討</t>
+          <t xml:space="preserve">📸 {outletName}がCMキャストを探している</t>
         </is>
       </c>
     </row>
     <row r="342" ht="40" customHeight="1">
       <c r="A342" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].detail</t>
         </is>
       </c>
       <c r="B342" t="inlineStr" s="2">
@@ -9761,19 +9761,19 @@
       </c>
       <c r="D342" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure[2].detail</t>
+          <t xml:space="preserve">B4_cm[2].detail</t>
         </is>
       </c>
       <c r="G342" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「女子プロレスラーの素顔に迫りたい」——{outletName}からそんな企画の打診が来た。</t>
+          <t xml:space="preserve">「プロレスラーのカッコよさをCMで表現したい」——{outletName}からそんな依頼が届いた。</t>
         </is>
       </c>
     </row>
     <row r="343" ht="40" customHeight="1">
       <c r="A343" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].text</t>
         </is>
       </c>
       <c r="B343" t="inlineStr" s="2">
@@ -9788,19 +9788,19 @@
       </c>
       <c r="D343" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure[3].text</t>
+          <t xml:space="preserve">B4_cm[3].text</t>
         </is>
       </c>
       <c r="G343" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📷 {outletName}からグラビア出演のオファー</t>
+          <t xml:space="preserve">📸 {outletName}のCM出演オファー</t>
         </is>
       </c>
     </row>
     <row r="344" ht="40" customHeight="1">
       <c r="A344" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].detail</t>
         </is>
       </c>
       <c r="B344" t="inlineStr" s="2">
@@ -9815,19 +9815,19 @@
       </c>
       <c r="D344" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_gravure[3].detail</t>
+          <t xml:space="preserve">B4_cm[3].detail</t>
         </is>
       </c>
       <c r="G344" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}の編集長から直接連絡が入った。「ぜひ選手を誌面に起用したい」とのこと。</t>
+          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「うちの団体の選手を広告塔に使いたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="345" ht="40" customHeight="1">
       <c r="A345" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].text</t>
         </is>
       </c>
       <c r="B345" t="inlineStr" s="2">
@@ -9842,19 +9842,19 @@
       </c>
       <c r="D345" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety[1].text</t>
+          <t xml:space="preserve">B4_gravure[1].text</t>
         </is>
       </c>
       <c r="G345" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}からバラエティ出演のオファー</t>
+          <t xml:space="preserve">📷 {outletName}からグラビア撮影の依頼</t>
         </is>
       </c>
     </row>
     <row r="346" ht="40" customHeight="1">
       <c r="A346" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].detail</t>
         </is>
       </c>
       <c r="B346" t="inlineStr" s="2">
@@ -9869,19 +9869,19 @@
       </c>
       <c r="D346" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety[1].detail</t>
+          <t xml:space="preserve">B4_gravure[1].detail</t>
         </is>
       </c>
       <c r="G346" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「プロレスラーがゲスト出演するコーナーを作りたい」と打診してきた。</t>
+          <t xml:space="preserve">{outletName}が「プロレスラーの魅力をグラビアで届けたい」と申し出てきた。</t>
         </is>
       </c>
     </row>
     <row r="347" ht="40" customHeight="1">
       <c r="A347" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].text</t>
         </is>
       </c>
       <c r="B347" t="inlineStr" s="2">
@@ -9896,19 +9896,19 @@
       </c>
       <c r="D347" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety[2].text</t>
+          <t xml:space="preserve">B4_gravure[2].text</t>
         </is>
       </c>
       <c r="G347" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}がゲスト出演の候補を探している</t>
+          <t xml:space="preserve">📷 {outletName}がグラビア特集企画を検討</t>
         </is>
       </c>
     </row>
     <row r="348" ht="40" customHeight="1">
       <c r="A348" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].detail</t>
         </is>
       </c>
       <c r="B348" t="inlineStr" s="2">
@@ -9923,19 +9923,19 @@
       </c>
       <c r="D348" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety[2].detail</t>
+          <t xml:space="preserve">B4_gravure[2].detail</t>
         </is>
       </c>
       <c r="G348" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「面白いキャラクターのプロレスラーを探している」——{outletName}からそんな依頼が届いた。</t>
+          <t xml:space="preserve">「女子プロレスラーの素顔に迫りたい」——{outletName}からそんな企画の打診が来た。</t>
         </is>
       </c>
     </row>
     <row r="349" ht="40" customHeight="1">
       <c r="A349" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].text</t>
         </is>
       </c>
       <c r="B349" t="inlineStr" s="2">
@@ -9950,19 +9950,19 @@
       </c>
       <c r="D349" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety[3].text</t>
+          <t xml:space="preserve">B4_gravure[3].text</t>
         </is>
       </c>
       <c r="G349" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">📺 {outletName}のトーク番組に出演依頼</t>
+          <t xml:space="preserve">📷 {outletName}からグラビア出演のオファー</t>
         </is>
       </c>
     </row>
     <row r="350" ht="40" customHeight="1">
       <c r="A350" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].detail</t>
         </is>
       </c>
       <c r="B350" t="inlineStr" s="2">
@@ -9977,19 +9977,19 @@
       </c>
       <c r="D350" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_variety[3].detail</t>
+          <t xml:space="preserve">B4_gravure[3].detail</t>
         </is>
       </c>
       <c r="G350" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}のディレクターが来訪。「選手のキャラクターを全国に届けたい」とのこと。</t>
+          <t xml:space="preserve">{outletName}の編集長から直接連絡が入った。「ぜひ選手を誌面に起用したい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="351" ht="40" customHeight="1">
       <c r="A351" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].text</t>
         </is>
       </c>
       <c r="B351" t="inlineStr" s="2">
@@ -10004,19 +10004,19 @@
       </c>
       <c r="D351" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand[1].text</t>
+          <t xml:space="preserve">B4_variety[1].text</t>
         </is>
       </c>
       <c r="G351" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🤝 {outletName}からコラボ商品の提案</t>
+          <t xml:space="preserve">📺 {outletName}からバラエティ出演のオファー</t>
         </is>
       </c>
     </row>
     <row r="352" ht="40" customHeight="1">
       <c r="A352" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].detail</t>
         </is>
       </c>
       <c r="B352" t="inlineStr" s="2">
@@ -10031,19 +10031,19 @@
       </c>
       <c r="D352" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand[1].detail</t>
+          <t xml:space="preserve">B4_variety[1].detail</t>
         </is>
       </c>
       <c r="G352" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「選手とのコラボ商品を作りたい」と申し出てきた。</t>
+          <t xml:space="preserve">{outletName}が「プロレスラーがゲスト出演するコーナーを作りたい」と打診してきた。</t>
         </is>
       </c>
     </row>
     <row r="353" ht="40" customHeight="1">
       <c r="A353" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].text</t>
         </is>
       </c>
       <c r="B353" t="inlineStr" s="2">
@@ -10058,19 +10058,19 @@
       </c>
       <c r="D353" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand[2].text</t>
+          <t xml:space="preserve">B4_variety[2].text</t>
         </is>
       </c>
       <c r="G353" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🤝 {outletName}がコラボパートナーを探している</t>
+          <t xml:space="preserve">📺 {outletName}がゲスト出演の候補を探している</t>
         </is>
       </c>
     </row>
     <row r="354" ht="40" customHeight="1">
       <c r="A354" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].detail</t>
         </is>
       </c>
       <c r="B354" t="inlineStr" s="2">
@@ -10085,19 +10085,19 @@
       </c>
       <c r="D354" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand[2].detail</t>
+          <t xml:space="preserve">B4_variety[2].detail</t>
         </is>
       </c>
       <c r="G354" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「プロレスのパワーとブランドのスタイルを組み合わせたい」——{outletName}からそんな話が来た。</t>
+          <t xml:space="preserve">「面白いキャラクターのプロレスラーを探している」——{outletName}からそんな依頼が届いた。</t>
         </is>
       </c>
     </row>
     <row r="355" ht="40" customHeight="1">
       <c r="A355" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].text</t>
         </is>
       </c>
       <c r="B355" t="inlineStr" s="2">
@@ -10112,19 +10112,19 @@
       </c>
       <c r="D355" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand[3].text</t>
+          <t xml:space="preserve">B4_variety[3].text</t>
         </is>
       </c>
       <c r="G355" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🤝 {outletName}とのコラボ企画の打診</t>
+          <t xml:space="preserve">📺 {outletName}のトーク番組に出演依頼</t>
         </is>
       </c>
     </row>
     <row r="356" ht="40" customHeight="1">
       <c r="A356" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].detail</t>
         </is>
       </c>
       <c r="B356" t="inlineStr" s="2">
@@ -10139,19 +10139,19 @@
       </c>
       <c r="D356" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_brand[3].detail</t>
+          <t xml:space="preserve">B4_variety[3].detail</t>
         </is>
       </c>
       <c r="G356" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}の担当者が来訪。「選手のイメージを商品に落とし込みたい」とのこと。</t>
+          <t xml:space="preserve">{outletName}のディレクターが来訪。「選手のキャラクターを全国に届けたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="357" ht="40" customHeight="1">
       <c r="A357" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].text</t>
         </is>
       </c>
       <c r="B357" t="inlineStr" s="2">
@@ -10166,19 +10166,19 @@
       </c>
       <c r="D357" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion[1].text</t>
+          <t xml:space="preserve">B4_brand[1].text</t>
         </is>
       </c>
       <c r="G357" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👗 {outletName}のランウェイ出演オファー</t>
+          <t xml:space="preserve">🤝 {outletName}からコラボ商品の提案</t>
         </is>
       </c>
     </row>
     <row r="358" ht="40" customHeight="1">
       <c r="A358" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].detail</t>
         </is>
       </c>
       <c r="B358" t="inlineStr" s="2">
@@ -10193,19 +10193,19 @@
       </c>
       <c r="D358" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion[1].detail</t>
+          <t xml:space="preserve">B4_brand[1].detail</t>
         </is>
       </c>
       <c r="G358" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}が「アスリートのランウェイ参加を企画している」と打診してきた。</t>
+          <t xml:space="preserve">{outletName}が「選手とのコラボ商品を作りたい」と申し出てきた。</t>
         </is>
       </c>
     </row>
     <row r="359" ht="40" customHeight="1">
       <c r="A359" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].text</t>
         </is>
       </c>
       <c r="B359" t="inlineStr" s="2">
@@ -10220,19 +10220,19 @@
       </c>
       <c r="D359" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion[2].text</t>
+          <t xml:space="preserve">B4_brand[2].text</t>
         </is>
       </c>
       <c r="G359" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👗 {outletName}がファッションショー出演者を募集</t>
+          <t xml:space="preserve">🤝 {outletName}がコラボパートナーを探している</t>
         </is>
       </c>
     </row>
     <row r="360" ht="40" customHeight="1">
       <c r="A360" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].detail</t>
         </is>
       </c>
       <c r="B360" t="inlineStr" s="2">
@@ -10247,19 +10247,19 @@
       </c>
       <c r="D360" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion[2].detail</t>
+          <t xml:space="preserve">B4_brand[2].detail</t>
         </is>
       </c>
       <c r="G360" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「プロレスラーの迫力をランウェイで表現したい」——{outletName}からそんな話が届いた。</t>
+          <t xml:space="preserve">「プロレスのパワーとブランドのスタイルを組み合わせたい」——{outletName}からそんな話が来た。</t>
         </is>
       </c>
     </row>
     <row r="361" ht="40" customHeight="1">
       <c r="A361" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].text</t>
         </is>
       </c>
       <c r="B361" t="inlineStr" s="2">
@@ -10274,19 +10274,19 @@
       </c>
       <c r="D361" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion[3].text</t>
+          <t xml:space="preserve">B4_brand[3].text</t>
         </is>
       </c>
       <c r="G361" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">👗 {outletName}のコレクションへの参加依頼</t>
+          <t xml:space="preserve">🤝 {outletName}とのコラボ企画の打診</t>
         </is>
       </c>
     </row>
     <row r="362" ht="40" customHeight="1">
       <c r="A362" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].detail</t>
         </is>
       </c>
       <c r="B362" t="inlineStr" s="2">
@@ -10301,19 +10301,19 @@
       </c>
       <c r="D362" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fashion[3].detail</t>
+          <t xml:space="preserve">B4_brand[3].detail</t>
         </is>
       </c>
       <c r="G362" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{outletName}のデザイナーが来訪。「ぜひ選手にランウェイを歩いてほしい」とのこと。</t>
+          <t xml:space="preserve">{outletName}の担当者が来訪。「選手のイメージを商品に落とし込みたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="363" ht="40" customHeight="1">
       <c r="A363" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].text</t>
         </is>
       </c>
       <c r="B363" t="inlineStr" s="2">
@@ -10328,19 +10328,19 @@
       </c>
       <c r="D363" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan[1].text</t>
+          <t xml:space="preserve">B4_fashion[1].text</t>
         </is>
       </c>
       <c r="G363" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🎤 ファンイベント開催の打診</t>
+          <t xml:space="preserve">👗 {outletName}のランウェイ出演オファー</t>
         </is>
       </c>
     </row>
     <row r="364" ht="40" customHeight="1">
       <c r="A364" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].detail</t>
         </is>
       </c>
       <c r="B364" t="inlineStr" s="2">
@@ -10355,19 +10355,19 @@
       </c>
       <c r="D364" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan[1].detail</t>
+          <t xml:space="preserve">B4_fashion[1].detail</t>
         </is>
       </c>
       <c r="G364" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">主催者から「選手とファンが直接交流できるイベントを開きたい」と相談が来た。</t>
+          <t xml:space="preserve">{outletName}が「アスリートのランウェイ参加を企画している」と打診してきた。</t>
         </is>
       </c>
     </row>
     <row r="365" ht="40" customHeight="1">
       <c r="A365" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].text</t>
         </is>
       </c>
       <c r="B365" t="inlineStr" s="2">
@@ -10382,19 +10382,19 @@
       </c>
       <c r="D365" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan[2].text</t>
+          <t xml:space="preserve">B4_fashion[2].text</t>
         </is>
       </c>
       <c r="G365" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🎤 サイン会・トークショーの開催依頼</t>
+          <t xml:space="preserve">👗 {outletName}がファッションショー出演者を募集</t>
         </is>
       </c>
     </row>
     <row r="366" ht="40" customHeight="1">
       <c r="A366" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].detail</t>
         </is>
       </c>
       <c r="B366" t="inlineStr" s="2">
@@ -10409,19 +10409,19 @@
       </c>
       <c r="D366" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan[2].detail</t>
+          <t xml:space="preserve">B4_fashion[2].detail</t>
         </is>
       </c>
       <c r="G366" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">「ファンと選手が触れ合える機会を作りたい」——イベント会社からそんな提案が届いた。</t>
+          <t xml:space="preserve">「プロレスラーの迫力をランウェイで表現したい」——{outletName}からそんな話が届いた。</t>
         </is>
       </c>
     </row>
     <row r="367" ht="40" customHeight="1">
       <c r="A367" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].text</t>
         </is>
       </c>
       <c r="B367" t="inlineStr" s="2">
@@ -10436,44 +10436,206 @@
       </c>
       <c r="D367" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B4_fan[3].text</t>
+          <t xml:space="preserve">B4_fashion[3].text</t>
         </is>
       </c>
       <c r="G367" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">🎤 ファンミーティングの企画提案</t>
+          <t xml:space="preserve">👗 {outletName}のコレクションへの参加依頼</t>
         </is>
       </c>
     </row>
     <row r="368" ht="40" customHeight="1">
       <c r="A368" t="inlineStr" s="15">
         <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].detail</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B4_fashion[3].detail</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">{outletName}のデザイナーが来訪。「ぜひ選手にランウェイを歩いてほしい」とのこと。</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="40" customHeight="1">
+      <c r="A369" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].text</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B4_fan[1].text</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">🎤 ファンイベント開催の打診</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="40" customHeight="1">
+      <c r="A370" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].detail</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B4_fan[1].detail</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">主催者から「選手とファンが直接交流できるイベントを開きたい」と相談が来た。</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="40" customHeight="1">
+      <c r="A371" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].text</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B4_fan[2].text</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">🎤 サイン会・トークショーの開催依頼</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="40" customHeight="1">
+      <c r="A372" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].detail</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B4_fan[2].detail</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">「ファンと選手が触れ合える機会を作りたい」——イベント会社からそんな提案が届いた。</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="40" customHeight="1">
+      <c r="A373" t="inlineStr" s="15">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[3].text</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr" s="12">
+        <is>
+          <t xml:space="preserve">B4_fan[3].text</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr" s="3">
+        <is>
+          <t xml:space="preserve">🎤 ファンミーティングの企画提案</t>
+        </is>
+      </c>
+    </row>
+    <row r="374" ht="40" customHeight="1">
+      <c r="A374" t="inlineStr" s="15">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[3].detail</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr" s="2">
+      <c r="B374" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr" s="12">
+      <c r="D374" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fan[3].detail</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr" s="3">
+      <c r="G374" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「選手の素顔をファンに見せる場を作りたい」と主催者から打診があった。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I368"/>
+  <autoFilter ref="A1:I374"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
+++ b/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
@@ -3091,7 +3091,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal._default[1]</t>
+          <t xml:space="preserve">G1.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F107" t="inlineStr" s="5">
@@ -3123,7 +3123,7 @@
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.normal._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.normal[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.normal._default[2]</t>
+          <t xml:space="preserve">G1.voice._default.normal[2]</t>
         </is>
       </c>
       <c r="F108" t="inlineStr" s="5">
@@ -3155,7 +3155,7 @@
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.bold._default[1]</t>
+          <t xml:space="preserve">G1.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F109" t="inlineStr" s="6">
@@ -3187,7 +3187,7 @@
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.bold._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.bold._default[2]</t>
+          <t xml:space="preserve">G1.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="F110" t="inlineStr" s="6">
@@ -3219,7 +3219,7 @@
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.earnest._default[1]</t>
+          <t xml:space="preserve">G1.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F111" t="inlineStr" s="10">
@@ -3251,7 +3251,7 @@
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.earnest._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.earnest[2]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.earnest._default[2]</t>
+          <t xml:space="preserve">G1.voice._default.earnest[2]</t>
         </is>
       </c>
       <c r="F112" t="inlineStr" s="10">
@@ -3283,7 +3283,7 @@
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.emotional._default[1]</t>
+          <t xml:space="preserve">G1.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F113" t="inlineStr" s="10">
@@ -3315,7 +3315,7 @@
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice.emotional._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice.emotional._default[2]</t>
+          <t xml:space="preserve">G1.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="F114" t="inlineStr" s="10">
@@ -3401,7 +3401,7 @@
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.normal._default[1]</t>
+          <t xml:space="preserve">G2.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F117" t="inlineStr" s="5">
@@ -3433,7 +3433,7 @@
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.normal._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.normal[2]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.normal._default[2]</t>
+          <t xml:space="preserve">G2.voice._default.normal[2]</t>
         </is>
       </c>
       <c r="F118" t="inlineStr" s="5">
@@ -3465,7 +3465,7 @@
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.bold._default[1]</t>
+          <t xml:space="preserve">G2.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F119" t="inlineStr" s="6">
@@ -3497,7 +3497,7 @@
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.bold._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.bold._default[2]</t>
+          <t xml:space="preserve">G2.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="F120" t="inlineStr" s="6">
@@ -3529,7 +3529,7 @@
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.earnest._default[1]</t>
+          <t xml:space="preserve">G2.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F121" t="inlineStr" s="10">
@@ -3561,7 +3561,7 @@
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.emotional._default[1]</t>
+          <t xml:space="preserve">G2.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F122" t="inlineStr" s="10">
@@ -3593,7 +3593,7 @@
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice.emotional._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice.emotional._default[2]</t>
+          <t xml:space="preserve">G2.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="F123" t="inlineStr" s="10">
@@ -3706,7 +3706,7 @@
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.normal._default[1]</t>
+          <t xml:space="preserve">G3.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F127" t="inlineStr" s="5">
@@ -3738,7 +3738,7 @@
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.bold._default[1]</t>
+          <t xml:space="preserve">G3.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F128" t="inlineStr" s="6">
@@ -3770,7 +3770,7 @@
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.bold._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.bold._default[2]</t>
+          <t xml:space="preserve">G3.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr" s="6">
@@ -3802,7 +3802,7 @@
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.earnest._default[1]</t>
+          <t xml:space="preserve">G3.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F130" t="inlineStr" s="10">
@@ -3834,7 +3834,7 @@
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.earnest._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.earnest[2]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -3849,7 +3849,7 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.earnest._default[2]</t>
+          <t xml:space="preserve">G3.voice._default.earnest[2]</t>
         </is>
       </c>
       <c r="F131" t="inlineStr" s="10">
@@ -3866,7 +3866,7 @@
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.emotional._default[1]</t>
+          <t xml:space="preserve">G3.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F132" t="inlineStr" s="10">
@@ -3898,7 +3898,7 @@
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice.emotional._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -3913,7 +3913,7 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice.emotional._default[2]</t>
+          <t xml:space="preserve">G3.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="F133" t="inlineStr" s="10">
@@ -4011,7 +4011,7 @@
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.normal._default[1]</t>
+          <t xml:space="preserve">G4.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F137" t="inlineStr" s="5">
@@ -4043,7 +4043,7 @@
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.bold._default[1]</t>
+          <t xml:space="preserve">G4.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F138" t="inlineStr" s="6">
@@ -4075,7 +4075,7 @@
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.bold._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.bold._default[2]</t>
+          <t xml:space="preserve">G4.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="F139" t="inlineStr" s="6">
@@ -4107,7 +4107,7 @@
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.earnest._default[1]</t>
+          <t xml:space="preserve">G4.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F140" t="inlineStr" s="10">
@@ -4139,7 +4139,7 @@
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice.emotional._default[1]</t>
+          <t xml:space="preserve">G4.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F141" t="inlineStr" s="10">
@@ -4360,7 +4360,7 @@
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.normal._default[1]</t>
+          <t xml:space="preserve">R2.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F149" t="inlineStr" s="5">
@@ -4392,7 +4392,7 @@
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4407,7 +4407,7 @@
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.bold._default[1]</t>
+          <t xml:space="preserve">R2.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F150" t="inlineStr" s="6">
@@ -4424,7 +4424,7 @@
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.earnest._default[1]</t>
+          <t xml:space="preserve">R2.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F151" t="inlineStr" s="10">
@@ -4456,7 +4456,7 @@
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.emotional._default[1]</t>
+          <t xml:space="preserve">R2.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F152" t="inlineStr" s="10">
@@ -4488,7 +4488,7 @@
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice.emotional._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice.emotional._default[2]</t>
+          <t xml:space="preserve">R2.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="F153" t="inlineStr" s="10">
@@ -4574,7 +4574,7 @@
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.normal[1]</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.normal._default[1]</t>
+          <t xml:space="preserve">R3.modal._default.normal[1]</t>
         </is>
       </c>
       <c r="F156" t="inlineStr" s="5">
@@ -4606,7 +4606,7 @@
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.normal._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.normal[2]</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.normal._default[2]</t>
+          <t xml:space="preserve">R3.modal._default.normal[2]</t>
         </is>
       </c>
       <c r="F157" t="inlineStr" s="5">
@@ -4638,7 +4638,7 @@
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.bold[1]</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.bold._default[1]</t>
+          <t xml:space="preserve">R3.modal._default.bold[1]</t>
         </is>
       </c>
       <c r="F158" t="inlineStr" s="6">
@@ -4670,7 +4670,7 @@
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.bold._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.bold[2]</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.bold._default[2]</t>
+          <t xml:space="preserve">R3.modal._default.bold[2]</t>
         </is>
       </c>
       <c r="F159" t="inlineStr" s="6">
@@ -4702,7 +4702,7 @@
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.earnest[1]</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.earnest._default[1]</t>
+          <t xml:space="preserve">R3.modal._default.earnest[1]</t>
         </is>
       </c>
       <c r="F160" t="inlineStr" s="10">
@@ -4734,7 +4734,7 @@
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.earnest._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.earnest[2]</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.earnest._default[2]</t>
+          <t xml:space="preserve">R3.modal._default.earnest[2]</t>
         </is>
       </c>
       <c r="F161" t="inlineStr" s="10">
@@ -4766,7 +4766,7 @@
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.emotional[1]</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.emotional._default[1]</t>
+          <t xml:space="preserve">R3.modal._default.emotional[1]</t>
         </is>
       </c>
       <c r="F162" t="inlineStr" s="10">
@@ -4798,7 +4798,7 @@
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal.emotional._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.emotional[2]</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal.emotional._default[2]</t>
+          <t xml:space="preserve">R3.modal._default.emotional[2]</t>
         </is>
       </c>
       <c r="F163" t="inlineStr" s="10">
@@ -4884,7 +4884,7 @@
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.normal._default[1]</t>
+          <t xml:space="preserve">R4.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F166" t="inlineStr" s="5">
@@ -4916,7 +4916,7 @@
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.bold._default[1]</t>
+          <t xml:space="preserve">R4.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F167" t="inlineStr" s="6">
@@ -4948,7 +4948,7 @@
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.bold._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.bold._default[2]</t>
+          <t xml:space="preserve">R4.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="F168" t="inlineStr" s="6">
@@ -4980,7 +4980,7 @@
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.earnest._default[1]</t>
+          <t xml:space="preserve">R4.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F169" t="inlineStr" s="10">
@@ -5012,7 +5012,7 @@
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.emotional._default[1]</t>
+          <t xml:space="preserve">R4.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F170" t="inlineStr" s="10">
@@ -5044,7 +5044,7 @@
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice.emotional._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice.emotional._default[2]</t>
+          <t xml:space="preserve">R4.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="F171" t="inlineStr" s="10">
@@ -5157,7 +5157,7 @@
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5172,7 +5172,7 @@
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.normal._default[1]</t>
+          <t xml:space="preserve">R5.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F175" t="inlineStr" s="5">
@@ -5189,7 +5189,7 @@
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.normal._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.normal[2]</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.normal._default[2]</t>
+          <t xml:space="preserve">R5.voice._default.normal[2]</t>
         </is>
       </c>
       <c r="F176" t="inlineStr" s="5">
@@ -5221,7 +5221,7 @@
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.bold._default[1]</t>
+          <t xml:space="preserve">R5.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F177" t="inlineStr" s="6">
@@ -5253,7 +5253,7 @@
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.bold._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.bold._default[2]</t>
+          <t xml:space="preserve">R5.voice._default.bold[2]</t>
         </is>
       </c>
       <c r="F178" t="inlineStr" s="6">
@@ -5285,7 +5285,7 @@
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.earnest._default[1]</t>
+          <t xml:space="preserve">R5.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F179" t="inlineStr" s="10">
@@ -5317,7 +5317,7 @@
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.earnest._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.earnest[2]</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.earnest._default[2]</t>
+          <t xml:space="preserve">R5.voice._default.earnest[2]</t>
         </is>
       </c>
       <c r="F180" t="inlineStr" s="10">
@@ -5349,7 +5349,7 @@
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.emotional._default[1]</t>
+          <t xml:space="preserve">R5.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F181" t="inlineStr" s="10">
@@ -5381,7 +5381,7 @@
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice.emotional._default[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice.emotional._default[2]</t>
+          <t xml:space="preserve">R5.voice._default.emotional[2]</t>
         </is>
       </c>
       <c r="F182" t="inlineStr" s="10">
@@ -5737,7 +5737,7 @@
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.normal._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.normal._default[1]</t>
+          <t xml:space="preserve">breakthrough.voice._default.normal[1]</t>
         </is>
       </c>
       <c r="F195" t="inlineStr" s="5">
@@ -5769,7 +5769,7 @@
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.bold._default[1]</t>
+          <t xml:space="preserve">breakthrough.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F196" t="inlineStr" s="6">
@@ -5801,7 +5801,7 @@
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.quiet._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.quiet[1]</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.quiet._default[1]</t>
+          <t xml:space="preserve">breakthrough.voice._default.quiet[1]</t>
         </is>
       </c>
       <c r="F197" t="inlineStr" s="7">
@@ -5833,7 +5833,7 @@
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.earnest._default[1]</t>
+          <t xml:space="preserve">breakthrough.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F198" t="inlineStr" s="10">
@@ -5865,7 +5865,7 @@
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -5880,7 +5880,7 @@
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice.emotional._default[1]</t>
+          <t xml:space="preserve">breakthrough.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F199" t="inlineStr" s="10">
@@ -5924,7 +5924,7 @@
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.bold._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.bold._default[1]</t>
+          <t xml:space="preserve">warVictory.voice._default.bold[1]</t>
         </is>
       </c>
       <c r="F201" t="inlineStr" s="6">
@@ -5956,7 +5956,7 @@
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.earnest._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.earnest._default[1]</t>
+          <t xml:space="preserve">warVictory.voice._default.earnest[1]</t>
         </is>
       </c>
       <c r="F202" t="inlineStr" s="10">
@@ -5988,7 +5988,7 @@
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice.emotional._default[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice.emotional._default[1]</t>
+          <t xml:space="preserve">warVictory.voice._default.emotional[1]</t>
         </is>
       </c>
       <c r="F203" t="inlineStr" s="10">

--- a/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
+++ b/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
@@ -192,7 +192,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I374"/>
+  <dimension ref="A1:I312"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3091,7 +3091,7 @@
     <row r="107" ht="40" customHeight="1">
       <c r="A107" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.scene[1]</t>
         </is>
       </c>
       <c r="B107" t="inlineStr" s="2">
@@ -3106,24 +3106,19 @@
       </c>
       <c r="D107" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">G2.scene[1]</t>
         </is>
       </c>
       <c r="G107" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、こんなもんか</t>
+          <t xml:space="preserve">{name}が後輩の{name2}の試合を腕を組んで見ていた。複雑な表情だ</t>
         </is>
       </c>
     </row>
     <row r="108" ht="40" customHeight="1">
       <c r="A108" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.normal[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.scene[2]</t>
         </is>
       </c>
       <c r="B108" t="inlineStr" s="2">
@@ -3138,24 +3133,19 @@
       </c>
       <c r="D108" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">G2.scene[2]</t>
         </is>
       </c>
       <c r="G108" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…頑張ってるのにな</t>
+          <t xml:space="preserve">{name}が{name2}に技を教えている。だが、その目にどこか翳りがある</t>
         </is>
       </c>
     </row>
     <row r="109" ht="40" customHeight="1">
       <c r="A109" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.scene[1]</t>
         </is>
       </c>
       <c r="B109" t="inlineStr" s="2">
@@ -3170,24 +3160,19 @@
       </c>
       <c r="D109" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">G3.scene[1]</t>
         </is>
       </c>
       <c r="G109" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんであの子と同じ扱いなわけ？</t>
+          <t xml:space="preserve">{name}がタイトルマッチのポスターの前で足を止めていた</t>
         </is>
       </c>
     </row>
     <row r="110" ht="40" customHeight="1">
       <c r="A110" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.scene[2]</t>
         </is>
       </c>
       <c r="B110" t="inlineStr" s="2">
@@ -3202,24 +3187,19 @@
       </c>
       <c r="D110" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">G3.scene[2]</t>
         </is>
       </c>
       <c r="G110" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…納得いかない</t>
+          <t xml:space="preserve">{name}が練習中、いつもより打ち込みが荒い。何かを持て余している</t>
         </is>
       </c>
     </row>
     <row r="111" ht="40" customHeight="1">
       <c r="A111" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.scene[3]</t>
         </is>
       </c>
       <c r="B111" t="inlineStr" s="2">
@@ -3234,24 +3214,19 @@
       </c>
       <c r="D111" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">G3.scene[3]</t>
         </is>
       </c>
       <c r="G111" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと結果を出せばいいだけの話、だよね</t>
+          <t xml:space="preserve">タイトル戦の話題が出た時、{name}だけが黙っていた</t>
         </is>
       </c>
     </row>
     <row r="112" ht="40" customHeight="1">
       <c r="A112" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.earnest[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.scene[1]</t>
         </is>
       </c>
       <c r="B112" t="inlineStr" s="2">
@@ -3266,24 +3241,19 @@
       </c>
       <c r="D112" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">G4.scene[1]</t>
         </is>
       </c>
       <c r="G112" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…自分の力不足かな</t>
+          <t xml:space="preserve">{name}が試合のない週末を持て余しているようだ</t>
         </is>
       </c>
     </row>
     <row r="113" ht="40" customHeight="1">
       <c r="A113" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.scene[2]</t>
         </is>
       </c>
       <c r="B113" t="inlineStr" s="2">
@@ -3298,24 +3268,19 @@
       </c>
       <c r="D113" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">G4.scene[2]</t>
         </is>
       </c>
       <c r="G113" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんで…なんでだろ</t>
+          <t xml:space="preserve">控え室の隅で、{name}がストレッチをしている。出番を待つ背中に焦りが見える</t>
         </is>
       </c>
     </row>
     <row r="114" ht="40" customHeight="1">
       <c r="A114" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G1.voice._default.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.scene[3]</t>
         </is>
       </c>
       <c r="B114" t="inlineStr" s="2">
@@ -3330,24 +3295,19 @@
       </c>
       <c r="D114" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G1.voice._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">G4.scene[3]</t>
         </is>
       </c>
       <c r="G114" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しいな</t>
+          <t xml:space="preserve">{name}が自主練の後、一人でリングを見つめていた</t>
         </is>
       </c>
     </row>
     <row r="115" ht="40" customHeight="1">
       <c r="A115" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.scene[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.scene[1]</t>
         </is>
       </c>
       <c r="B115" t="inlineStr" s="2">
@@ -3362,19 +3322,19 @@
       </c>
       <c r="D115" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.scene[1]</t>
+          <t xml:space="preserve">R1.scene[1]</t>
         </is>
       </c>
       <c r="G115" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が後輩の{name2}の試合を腕を組んで見ていた。複雑な表情だ</t>
+          <t xml:space="preserve">{name}と{name2}が控え室で目を合わせなかった</t>
         </is>
       </c>
     </row>
     <row r="116" ht="40" customHeight="1">
       <c r="A116" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.scene[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.scene[2]</t>
         </is>
       </c>
       <c r="B116" t="inlineStr" s="2">
@@ -3389,19 +3349,19 @@
       </c>
       <c r="D116" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.scene[2]</t>
+          <t xml:space="preserve">R1.scene[2]</t>
         </is>
       </c>
       <c r="G116" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が{name2}に技を教えている。だが、その目にどこか翳りがある</t>
+          <t xml:space="preserve">{name}と{name2}の間に、見えない壁がある。周りもそれを感じている</t>
         </is>
       </c>
     </row>
     <row r="117" ht="40" customHeight="1">
       <c r="A117" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.scene[3]</t>
         </is>
       </c>
       <c r="B117" t="inlineStr" s="2">
@@ -3416,24 +3376,19 @@
       </c>
       <c r="D117" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">R1.scene[3]</t>
         </is>
       </c>
       <c r="G117" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの子、伸びたな</t>
+          <t xml:space="preserve">{name}と{name2}が同じテーブルに座ることを避けていた</t>
         </is>
       </c>
     </row>
     <row r="118" ht="40" customHeight="1">
       <c r="A118" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.normal[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.staff[1]</t>
         </is>
       </c>
       <c r="B118" t="inlineStr" s="2">
@@ -3448,24 +3403,19 @@
       </c>
       <c r="D118" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice._default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">R1.staff[1]</t>
         </is>
       </c>
       <c r="G118" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…先輩としてちゃんと見てるよ。…でもね</t>
+          <t xml:space="preserve">スタッフから: {name}と{name2}、最近どうも空気がピリついてまして…</t>
         </is>
       </c>
     </row>
     <row r="119" ht="40" customHeight="1">
       <c r="A119" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.scene[1]</t>
         </is>
       </c>
       <c r="B119" t="inlineStr" s="2">
@@ -3480,24 +3430,19 @@
       </c>
       <c r="D119" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">R2.scene[1]</t>
         </is>
       </c>
       <c r="G119" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…年功序列なんて古い。分かってる。分かってるけど</t>
+          <t xml:space="preserve">昼休み。他の選手たちが談笑する中、{name}だけが離れた場所にいた</t>
         </is>
       </c>
     </row>
     <row r="120" ht="40" customHeight="1">
       <c r="A120" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.scene[2]</t>
         </is>
       </c>
       <c r="B120" t="inlineStr" s="2">
@@ -3512,24 +3457,19 @@
       </c>
       <c r="D120" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">R2.scene[2]</t>
         </is>
       </c>
       <c r="G120" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしだって負けてない</t>
+          <t xml:space="preserve">{name}が一人でリングの片付けをしている。手伝う者はいない</t>
         </is>
       </c>
     </row>
     <row r="121" ht="40" customHeight="1">
       <c r="A121" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.scene[3]</t>
         </is>
       </c>
       <c r="B121" t="inlineStr" s="2">
@@ -3544,24 +3484,19 @@
       </c>
       <c r="D121" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">R2.scene[3]</t>
         </is>
       </c>
       <c r="G121" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの子が評価されるのは正しいと思う。思うんだけど</t>
+          <t xml:space="preserve">練習後の更衣室。{name}のロッカーの周りだけ、少し空間が空いている</t>
         </is>
       </c>
     </row>
     <row r="122" ht="40" customHeight="1">
       <c r="A122" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.scene[1]</t>
         </is>
       </c>
       <c r="B122" t="inlineStr" s="2">
@@ -3576,24 +3511,19 @@
       </c>
       <c r="D122" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">R3.scene[1]</t>
         </is>
       </c>
       <c r="G122" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…先に始めたのはあたしなのに</t>
+          <t xml:space="preserve">{name}は{name2}の退団を知り、しばらく言葉を失っていた</t>
         </is>
       </c>
     </row>
     <row r="123" ht="40" customHeight="1">
       <c r="A123" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G2.voice._default.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.scene[2]</t>
         </is>
       </c>
       <c r="B123" t="inlineStr" s="2">
@@ -3608,24 +3538,19 @@
       </c>
       <c r="D123" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G2.voice._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">R3.scene[2]</t>
         </is>
       </c>
       <c r="G123" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…置いていかれてる気がする</t>
+          <t xml:space="preserve">{name2}がいなくなったロッカーの前で、{name}が立ち止まっていた</t>
         </is>
       </c>
     </row>
     <row r="124" ht="40" customHeight="1">
       <c r="A124" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.scene[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.scene[1]</t>
         </is>
       </c>
       <c r="B124" t="inlineStr" s="2">
@@ -3640,19 +3565,19 @@
       </c>
       <c r="D124" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.scene[1]</t>
+          <t xml:space="preserve">R4.scene[1]</t>
         </is>
       </c>
       <c r="G124" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}がタイトルマッチのポスターの前で足を止めていた</t>
+          <t xml:space="preserve">試合後、{name}の目に静かな炎が燃えていた</t>
         </is>
       </c>
     </row>
     <row r="125" ht="40" customHeight="1">
       <c r="A125" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.scene[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.scene[2]</t>
         </is>
       </c>
       <c r="B125" t="inlineStr" s="2">
@@ -3667,19 +3592,19 @@
       </c>
       <c r="D125" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.scene[2]</t>
+          <t xml:space="preserve">R4.scene[2]</t>
         </is>
       </c>
       <c r="G125" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が練習中、いつもより打ち込みが荒い。何かを持て余している</t>
+          <t xml:space="preserve">{name}がリングを降りる時、一瞬だけ{name2}のほうを振り返った。満足げに</t>
         </is>
       </c>
     </row>
     <row r="126" ht="40" customHeight="1">
       <c r="A126" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.scene[3]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.scene[1]</t>
         </is>
       </c>
       <c r="B126" t="inlineStr" s="2">
@@ -3694,19 +3619,19 @@
       </c>
       <c r="D126" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.scene[3]</t>
+          <t xml:space="preserve">R5.scene[1]</t>
         </is>
       </c>
       <c r="G126" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">タイトル戦の話題が出た時、{name}だけが黙っていた</t>
+          <t xml:space="preserve">{name}は無言でリングを降りた。その拳だけが震えていた</t>
         </is>
       </c>
     </row>
     <row r="127" ht="40" customHeight="1">
       <c r="A127" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.scene[2]</t>
         </is>
       </c>
       <c r="B127" t="inlineStr" s="2">
@@ -3721,24 +3646,19 @@
       </c>
       <c r="D127" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">R5.scene[2]</t>
         </is>
       </c>
       <c r="G127" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつになったら</t>
+          <t xml:space="preserve">{name}が帰り際、振り返って{name2}のほうを一瞬だけ見た</t>
         </is>
       </c>
     </row>
     <row r="128" ht="40" customHeight="1">
       <c r="A128" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.scene[3]</t>
         </is>
       </c>
       <c r="B128" t="inlineStr" s="2">
@@ -3753,24 +3673,19 @@
       </c>
       <c r="D128" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">R5.scene[3]</t>
         </is>
       </c>
       <c r="G128" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いつになったらあたしの番が来るの？</t>
+          <t xml:space="preserve">試合後の通路で、{name}が壁を叩く音がした</t>
         </is>
       </c>
     </row>
     <row r="129" ht="40" customHeight="1">
       <c r="A129" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.scene[1]</t>
         </is>
       </c>
       <c r="B129" t="inlineStr" s="2">
@@ -3785,24 +3700,19 @@
       </c>
       <c r="D129" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">friction.scene[1]</t>
         </is>
       </c>
       <c r="G129" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…待つのは好きじゃないな</t>
+          <t xml:space="preserve">{name}と{name2}が練習メニューの順番で揉めていた。些細なことだが</t>
         </is>
       </c>
     </row>
     <row r="130" ht="40" customHeight="1">
       <c r="A130" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.scene[2]</t>
         </is>
       </c>
       <c r="B130" t="inlineStr" s="2">
@@ -3817,24 +3727,19 @@
       </c>
       <c r="D130" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">friction.scene[2]</t>
         </is>
       </c>
       <c r="G130" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…実力が足りないから？ それとも…</t>
+          <t xml:space="preserve">{name}が{name2}の練習態度について、小声で何か言っていた</t>
         </is>
       </c>
     </row>
     <row r="131" ht="40" customHeight="1">
       <c r="A131" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.earnest[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.scene[3]</t>
         </is>
       </c>
       <c r="B131" t="inlineStr" s="2">
@@ -3849,24 +3754,19 @@
       </c>
       <c r="D131" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice._default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">friction.scene[3]</t>
         </is>
       </c>
       <c r="G131" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もう少し、待てばいいのかな</t>
+          <t xml:space="preserve">{name}と{name2}が同時に控え室に入った瞬間、空気が変わった</t>
         </is>
       </c>
     </row>
     <row r="132" ht="40" customHeight="1">
       <c r="A132" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.staff[1]</t>
         </is>
       </c>
       <c r="B132" t="inlineStr" s="2">
@@ -3881,24 +3781,19 @@
       </c>
       <c r="D132" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">friction.staff[1]</t>
         </is>
       </c>
       <c r="G132" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しくないって言ったら嘘になる</t>
+          <t xml:space="preserve">スタッフから: {name}と{name2}、ちょっと相性が良くないみたいで…</t>
         </is>
       </c>
     </row>
     <row r="133" ht="40" customHeight="1">
       <c r="A133" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G3.voice._default.emotional[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[1]</t>
         </is>
       </c>
       <c r="B133" t="inlineStr" s="2">
@@ -3913,24 +3808,19 @@
       </c>
       <c r="D133" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G3.voice._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">generation.scene[1]</t>
         </is>
       </c>
       <c r="G133" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしも、あそこに立ちたい</t>
+          <t xml:space="preserve">{name}と{name2}が一緒に帰っていく姿が見えた。同世代の気安さがある</t>
         </is>
       </c>
     </row>
     <row r="134" ht="40" customHeight="1">
       <c r="A134" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.scene[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[2]</t>
         </is>
       </c>
       <c r="B134" t="inlineStr" s="2">
@@ -3945,19 +3835,19 @@
       </c>
       <c r="D134" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.scene[1]</t>
+          <t xml:space="preserve">generation.scene[2]</t>
         </is>
       </c>
       <c r="G134" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が試合のない週末を持て余しているようだ</t>
+          <t xml:space="preserve">{name}と{name2}が自販機の前で笑い合っていた。何が面白いのか、こちらには分からないが</t>
         </is>
       </c>
     </row>
     <row r="135" ht="40" customHeight="1">
       <c r="A135" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.scene[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[3]</t>
         </is>
       </c>
       <c r="B135" t="inlineStr" s="2">
@@ -3972,19 +3862,19 @@
       </c>
       <c r="D135" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.scene[2]</t>
+          <t xml:space="preserve">generation.scene[3]</t>
         </is>
       </c>
       <c r="G135" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">控え室の隅で、{name}がストレッチをしている。出番を待つ背中に焦りが見える</t>
+          <t xml:space="preserve">{name}が{name2}を自主練に誘っている。いい雰囲気だ</t>
         </is>
       </c>
     </row>
     <row r="136" ht="40" customHeight="1">
       <c r="A136" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.scene[3]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[4]</t>
         </is>
       </c>
       <c r="B136" t="inlineStr" s="2">
@@ -3999,19 +3889,19 @@
       </c>
       <c r="D136" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.scene[3]</t>
+          <t xml:space="preserve">generation.scene[4]</t>
         </is>
       </c>
       <c r="G136" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が自主練の後、一人でリングを見つめていた</t>
+          <t xml:space="preserve">{name}と{name2}が昼食を一緒に取っている。どうやら仲がいいらしい</t>
         </is>
       </c>
     </row>
     <row r="137" ht="40" customHeight="1">
       <c r="A137" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.normal[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.rivalryResolved.scene[1]</t>
         </is>
       </c>
       <c r="B137" t="inlineStr" s="2">
@@ -4026,24 +3916,19 @@
       </c>
       <c r="D137" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">rivalryResolved.scene[1]</t>
         </is>
       </c>
       <c r="G137" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…出番、来ないかな</t>
+          <t xml:space="preserve">決着はついた。だが{name}と{name2}が目を合わせた時、そこにはまだ何かがあった</t>
         </is>
       </c>
     </row>
     <row r="138" ht="40" customHeight="1">
       <c r="A138" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.bold[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.rivalryResolved.scene[2]</t>
         </is>
       </c>
       <c r="B138" t="inlineStr" s="2">
@@ -4058,24 +3943,19 @@
       </c>
       <c r="D138" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">rivalryResolved.scene[2]</t>
         </is>
       </c>
       <c r="G138" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…使ってくれなきゃ意味ないじゃん</t>
+          <t xml:space="preserve">因縁は終わった。はずだ。…だが{name}は{name2}の動向を気にしている</t>
         </is>
       </c>
     </row>
     <row r="139" ht="40" customHeight="1">
       <c r="A139" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.bold[2]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.careerBestMQ.scene[1]</t>
         </is>
       </c>
       <c r="B139" t="inlineStr" s="2">
@@ -4090,24 +3970,19 @@
       </c>
       <c r="D139" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">careerBestMQ.scene[1]</t>
         </is>
       </c>
       <c r="G139" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あたしの居場所、あるのかな</t>
+          <t xml:space="preserve">{name}が試合後、自分の両手を見つめていた。何かを掴んだ表情だ</t>
         </is>
       </c>
     </row>
     <row r="140" ht="40" customHeight="1">
       <c r="A140" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.earnest[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.careerBestMQ.scene[2]</t>
         </is>
       </c>
       <c r="B140" t="inlineStr" s="2">
@@ -4122,24 +3997,19 @@
       </c>
       <c r="D140" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">careerBestMQ.scene[2]</t>
         </is>
       </c>
       <c r="G140" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…準備はできてる。いつでも</t>
+          <t xml:space="preserve">{name}の試合が終わった後、先輩たちが小さく頷いていた</t>
         </is>
       </c>
     </row>
     <row r="141" ht="40" customHeight="1">
       <c r="A141" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.G4.voice._default.emotional[1]</t>
+          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.scene[1]</t>
         </is>
       </c>
       <c r="B141" t="inlineStr" s="2">
@@ -4154,24 +4024,19 @@
       </c>
       <c r="D141" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">G4.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">warVictory.scene[1]</t>
         </is>
       </c>
       <c r="G141" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…見てくれてるのかな、あたしのこと</t>
+          <t xml:space="preserve">{name}はチームの勝利に拳を握りしめた。この団体の看板を背負う覚悟が見えた</t>
         </is>
       </c>
     </row>
     <row r="142" ht="40" customHeight="1">
       <c r="A142" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.bonus.label</t>
         </is>
       </c>
       <c r="B142" t="inlineStr" s="2">
@@ -4181,24 +4046,24 @@
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D142" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R1.scene[1]</t>
+          <t xml:space="preserve">bonus.label</t>
         </is>
       </c>
       <c r="G142" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}が控え室で目を合わせなかった</t>
+          <t xml:space="preserve">ボーナス支給願</t>
         </is>
       </c>
     </row>
     <row r="143" ht="40" customHeight="1">
       <c r="A143" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.bonus.categoryLabel</t>
         </is>
       </c>
       <c r="B143" t="inlineStr" s="2">
@@ -4208,24 +4073,24 @@
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R1.scene[2]</t>
+          <t xml:space="preserve">bonus.categoryLabel</t>
         </is>
       </c>
       <c r="G143" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}の間に、見えない壁がある。周りもそれを感じている</t>
+          <t xml:space="preserve">選手ケア</t>
         </is>
       </c>
     </row>
     <row r="144" ht="40" customHeight="1">
       <c r="A144" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.scene[3]</t>
+          <t xml:space="preserve">DECISION_DOCS.bonus.costLabel</t>
         </is>
       </c>
       <c r="B144" t="inlineStr" s="2">
@@ -4235,24 +4100,24 @@
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R1.scene[3]</t>
+          <t xml:space="preserve">bonus.costLabel</t>
         </is>
       </c>
       <c r="G144" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}が同じテーブルに座ることを避けていた</t>
+          <t xml:space="preserve">起案額による</t>
         </is>
       </c>
     </row>
     <row r="145" ht="40" customHeight="1">
       <c r="A145" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R1.staff[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.bonus.body</t>
         </is>
       </c>
       <c r="B145" t="inlineStr" s="2">
@@ -4262,24 +4127,24 @@
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D145" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R1.staff[1]</t>
+          <t xml:space="preserve">bonus.body</t>
         </is>
       </c>
       <c r="G145" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スタッフから: {name}と{name2}、最近どうも空気がピリついてまして…</t>
+          <t xml:space="preserve">対象選手に特別手当を支給し、組織貢献への感謝を示す</t>
         </is>
       </c>
     </row>
     <row r="146" ht="40" customHeight="1">
       <c r="A146" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.bonus.detailText</t>
         </is>
       </c>
       <c r="B146" t="inlineStr" s="2">
@@ -4289,24 +4154,24 @@
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.scene[1]</t>
+          <t xml:space="preserve">bonus.detailText</t>
         </is>
       </c>
       <c r="G146" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">昼休み。他の選手たちが談笑する中、{name}だけが離れた場所にいた</t>
+          <t xml:space="preserve">起案された支給額の中から、いくら積むかを社長が決める。額面が彼女の格に見合ってこそ、誠意は伝わる。安すぎる額は、かえって心を離れさせることもある。</t>
         </is>
       </c>
     </row>
     <row r="147" ht="40" customHeight="1">
       <c r="A147" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.bonus.effectSummary</t>
         </is>
       </c>
       <c r="B147" t="inlineStr" s="2">
@@ -4316,24 +4181,24 @@
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D147" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.scene[2]</t>
+          <t xml:space="preserve">bonus.effectSummary</t>
         </is>
       </c>
       <c r="G147" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が一人でリングの片付けをしている。手伝う者はいない</t>
+          <t xml:space="preserve">支給額しだいで本人の受け止め方が変わる。相場を大きく超える額は深く響く</t>
         </is>
       </c>
     </row>
     <row r="148" ht="40" customHeight="1">
       <c r="A148" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.scene[3]</t>
+          <t xml:space="preserve">DECISION_DOCS.bonus.recommendation</t>
         </is>
       </c>
       <c r="B148" t="inlineStr" s="2">
@@ -4343,24 +4208,24 @@
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.scene[3]</t>
+          <t xml:space="preserve">bonus.recommendation</t>
         </is>
       </c>
       <c r="G148" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習後の更衣室。{name}のロッカーの周りだけ、少し空間が空いている</t>
+          <t xml:space="preserve">団体への気持ちが陰りはじめた選手に、早めに手を打つと効果的。同じ選手への再支給は相場が吊り上がる点に注意。</t>
         </is>
       </c>
     </row>
     <row r="149" ht="40" customHeight="1">
       <c r="A149" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.normal[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.encourage.label</t>
         </is>
       </c>
       <c r="B149" t="inlineStr" s="2">
@@ -4370,29 +4235,24 @@
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D149" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">encourage.label</t>
         </is>
       </c>
       <c r="G149" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まあ、一人のほうが気楽だし</t>
+          <t xml:space="preserve">声かけ</t>
         </is>
       </c>
     </row>
     <row r="150" ht="40" customHeight="1">
       <c r="A150" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.bold[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.encourage.categoryLabel</t>
         </is>
       </c>
       <c r="B150" t="inlineStr" s="2">
@@ -4402,29 +4262,24 @@
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D150" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">encourage.categoryLabel</t>
         </is>
       </c>
       <c r="G150" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…別にいいけど。わたしは一人でやれるし</t>
+          <t xml:space="preserve">選手ケア</t>
         </is>
       </c>
     </row>
     <row r="151" ht="40" customHeight="1">
       <c r="A151" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.earnest[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.encourage.body</t>
         </is>
       </c>
       <c r="B151" t="inlineStr" s="2">
@@ -4434,29 +4289,24 @@
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D151" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">encourage.body</t>
         </is>
       </c>
       <c r="G151" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっとみんなと話した方がいいのかな</t>
+          <t xml:space="preserve">気にかけている選手に社長自ら声をかけに行く</t>
         </is>
       </c>
     </row>
     <row r="152" ht="40" customHeight="1">
       <c r="A152" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.emotional[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.encourage.detailText</t>
         </is>
       </c>
       <c r="B152" t="inlineStr" s="2">
@@ -4466,29 +4316,24 @@
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D152" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">encourage.detailText</t>
         </is>
       </c>
       <c r="G152" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんな、あたしのこと嫌いなのかな</t>
+          <t xml:space="preserve">決裁枠も資金も使わない、社長自らの自発的な行動。スランプ中・モチベ喪失中・最近様子が気になる選手に足を運んで声をかける。</t>
         </is>
       </c>
     </row>
     <row r="153" ht="40" customHeight="1">
       <c r="A153" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R2.voice._default.emotional[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.encourage.effectSummary</t>
         </is>
       </c>
       <c r="B153" t="inlineStr" s="2">
@@ -4498,29 +4343,24 @@
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D153" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R2.voice._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">encourage.effectSummary</t>
         </is>
       </c>
       <c r="G153" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここにいていいのかな</t>
+          <t xml:space="preserve">本人の表情が少し和らぐ（スランプ・モチベ喪失なら回復促進も）</t>
         </is>
       </c>
     </row>
     <row r="154" ht="40" customHeight="1">
       <c r="A154" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.encourage.recommendation</t>
         </is>
       </c>
       <c r="B154" t="inlineStr" s="2">
@@ -4530,24 +4370,24 @@
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D154" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.scene[1]</t>
+          <t xml:space="preserve">encourage.recommendation</t>
         </is>
       </c>
       <c r="G154" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は{name2}の退団を知り、しばらく言葉を失っていた</t>
+          <t xml:space="preserve">気になる選手のポップアップから直接実行する。机には並ばない。</t>
         </is>
       </c>
     </row>
     <row r="155" ht="40" customHeight="1">
       <c r="A155" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.special_treatment.label</t>
         </is>
       </c>
       <c r="B155" t="inlineStr" s="2">
@@ -4557,24 +4397,24 @@
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D155" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.scene[2]</t>
+          <t xml:space="preserve">special_treatment.label</t>
         </is>
       </c>
       <c r="G155" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}がいなくなったロッカーの前で、{name}が立ち止まっていた</t>
+          <t xml:space="preserve">特別治療指示書</t>
         </is>
       </c>
     </row>
     <row r="156" ht="40" customHeight="1">
       <c r="A156" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.normal[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.special_treatment.categoryLabel</t>
         </is>
       </c>
       <c r="B156" t="inlineStr" s="2">
@@ -4584,29 +4424,24 @@
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D156" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">special_treatment.categoryLabel</t>
         </is>
       </c>
       <c r="G156" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…いなくなっちゃうんだ</t>
+          <t xml:space="preserve">選手ケア</t>
         </is>
       </c>
     </row>
     <row r="157" ht="40" customHeight="1">
       <c r="A157" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.normal[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.special_treatment.body</t>
         </is>
       </c>
       <c r="B157" t="inlineStr" s="2">
@@ -4616,29 +4451,24 @@
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D157" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">special_treatment.body</t>
         </is>
       </c>
       <c r="G157" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{name2}がいない控え室なんて想像できない</t>
+          <t xml:space="preserve">離脱中の選手に専門医を手配し、復帰を早める</t>
         </is>
       </c>
     </row>
     <row r="158" ht="40" customHeight="1">
       <c r="A158" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.bold[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.special_treatment.detailText</t>
         </is>
       </c>
       <c r="B158" t="inlineStr" s="2">
@@ -4648,29 +4478,24 @@
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D158" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">special_treatment.detailText</t>
         </is>
       </c>
       <c r="G158" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…バカ。なんで何も言わずに行くのよ</t>
+          <t xml:space="preserve">専門医による集中ケアを正式に発注。怪我からの離脱期間を確率的に短縮する、復帰前倒しの一手。確実な短縮量は治療結果次第。</t>
         </is>
       </c>
     </row>
     <row r="159" ht="40" customHeight="1">
       <c r="A159" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.bold[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.special_treatment.effectSummary</t>
         </is>
       </c>
       <c r="B159" t="inlineStr" s="2">
@@ -4680,29 +4505,24 @@
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">special_treatment.effectSummary</t>
         </is>
       </c>
       <c r="G159" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あいつがいないと、張り合いがないな</t>
+          <t xml:space="preserve">対象選手の離脱期間が1〜4週短縮される</t>
         </is>
       </c>
     </row>
     <row r="160" ht="40" customHeight="1">
       <c r="A160" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.earnest[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.special_treatment.recommendation</t>
         </is>
       </c>
       <c r="B160" t="inlineStr" s="2">
@@ -4712,29 +4532,24 @@
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D160" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">special_treatment.recommendation</t>
         </is>
       </c>
       <c r="G160" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name2}のために、あたしはここで頑張るから</t>
+          <t xml:space="preserve">主力選手や王座挑戦が控えている選手の離脱が痛手なときに。離脱が長引いている怪我ほど短縮量も大きくなりやすい。</t>
         </is>
       </c>
     </row>
     <row r="161" ht="40" customHeight="1">
       <c r="A161" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.earnest[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.refresh_leave.label</t>
         </is>
       </c>
       <c r="B161" t="inlineStr" s="2">
@@ -4744,29 +4559,24 @@
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D161" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">refresh_leave.label</t>
         </is>
       </c>
       <c r="G161" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ありがとう。ずっと支えてくれて</t>
+          <t xml:space="preserve">休暇辞令</t>
         </is>
       </c>
     </row>
     <row r="162" ht="40" customHeight="1">
       <c r="A162" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.emotional[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.refresh_leave.categoryLabel</t>
         </is>
       </c>
       <c r="B162" t="inlineStr" s="2">
@@ -4776,29 +4586,24 @@
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D162" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">refresh_leave.categoryLabel</t>
         </is>
       </c>
       <c r="G162" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やだ。嫌だよ。なんで…</t>
+          <t xml:space="preserve">選手ケア</t>
         </is>
       </c>
     </row>
     <row r="163" ht="40" customHeight="1">
       <c r="A163" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R3.modal._default.emotional[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.refresh_leave.costLabel</t>
         </is>
       </c>
       <c r="B163" t="inlineStr" s="2">
@@ -4808,29 +4613,24 @@
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D163" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R3.modal._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">refresh_leave.costLabel</t>
         </is>
       </c>
       <c r="G163" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…{name2}がいないなんて、あたし…</t>
+          <t xml:space="preserve">週給×週数+50万</t>
         </is>
       </c>
     </row>
     <row r="164" ht="40" customHeight="1">
       <c r="A164" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.refresh_leave.body</t>
         </is>
       </c>
       <c r="B164" t="inlineStr" s="2">
@@ -4840,24 +4640,24 @@
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D164" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.scene[1]</t>
+          <t xml:space="preserve">refresh_leave.body</t>
         </is>
       </c>
       <c r="G164" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合後、{name}の目に静かな炎が燃えていた</t>
+          <t xml:space="preserve">心身の疲弊を察し、一定期間の休養を与える</t>
         </is>
       </c>
     </row>
     <row r="165" ht="40" customHeight="1">
       <c r="A165" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.refresh_leave.detailText</t>
         </is>
       </c>
       <c r="B165" t="inlineStr" s="2">
@@ -4867,24 +4667,24 @@
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D165" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.scene[2]</t>
+          <t xml:space="preserve">refresh_leave.detailText</t>
         </is>
       </c>
       <c r="G165" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}がリングを降りる時、一瞬だけ{name2}のほうを振り返った。満足げに</t>
+          <t xml:space="preserve">1〜4週間の休暇を正式な辞令として発行する。休暇中の試合には欠場するが、そのぶん心身は着実に回復していく。長い休みは、積み重なった消耗までも癒やす。</t>
         </is>
       </c>
     </row>
     <row r="166" ht="40" customHeight="1">
       <c r="A166" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.normal[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.refresh_leave.effectSummary</t>
         </is>
       </c>
       <c r="B166" t="inlineStr" s="2">
@@ -4894,29 +4694,24 @@
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D166" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">refresh_leave.effectSummary</t>
         </is>
       </c>
       <c r="G166" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…やっと、追いついた</t>
+          <t xml:space="preserve">休みの長さに応じて体調が戻り、長期なら蓄積した消耗も癒える。本人にも気遣いが伝わる</t>
         </is>
       </c>
     </row>
     <row r="167" ht="40" customHeight="1">
       <c r="A167" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.bold[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.refresh_leave.recommendation</t>
         </is>
       </c>
       <c r="B167" t="inlineStr" s="2">
@@ -4926,29 +4721,24 @@
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D167" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">refresh_leave.recommendation</t>
         </is>
       </c>
       <c r="G167" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ふん。まだまだこんなもんじゃないけどね</t>
+          <t xml:space="preserve">疲れの見える主力を、大事な興行の前に立て直す疲労管理の要。休暇中の欠場と引き換えになる点は覚悟すること。</t>
         </is>
       </c>
     </row>
     <row r="168" ht="40" customHeight="1">
       <c r="A168" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.bold[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.party.label</t>
         </is>
       </c>
       <c r="B168" t="inlineStr" s="2">
@@ -4958,29 +4748,24 @@
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D168" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">party.label</t>
         </is>
       </c>
       <c r="G168" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った。でも、まだ終わってない</t>
+          <t xml:space="preserve">慰労会開催届</t>
         </is>
       </c>
     </row>
     <row r="169" ht="40" customHeight="1">
       <c r="A169" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.earnest[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.party.categoryLabel</t>
         </is>
       </c>
       <c r="B169" t="inlineStr" s="2">
@@ -4990,29 +4775,24 @@
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D169" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">party.categoryLabel</t>
         </is>
       </c>
       <c r="G169" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…努力は裏切らない。…{name2}、ありがとう</t>
+          <t xml:space="preserve">選手ケア</t>
         </is>
       </c>
     </row>
     <row r="170" ht="40" customHeight="1">
       <c r="A170" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.emotional[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.party.body</t>
         </is>
       </c>
       <c r="B170" t="inlineStr" s="2">
@@ -5022,29 +4802,24 @@
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D170" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">party.body</t>
         </is>
       </c>
       <c r="G170" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った…勝ったよ…！</t>
+          <t xml:space="preserve">団体の雰囲気を立て直すべく、慰労の宴席を設ける</t>
         </is>
       </c>
     </row>
     <row r="171" ht="40" customHeight="1">
       <c r="A171" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R4.voice._default.emotional[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.party.detailText</t>
         </is>
       </c>
       <c r="B171" t="inlineStr" s="2">
@@ -5054,29 +4829,24 @@
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D171" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R4.voice._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">party.detailText</t>
         </is>
       </c>
       <c r="G171" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…泣くな、あたし。まだ先がある</t>
+          <t xml:space="preserve">全選手を集めた慰労の宴席。個別の数値を動かすより、ロッカールームの空気そのものを立て直すのが主目的。</t>
         </is>
       </c>
     </row>
     <row r="172" ht="40" customHeight="1">
       <c r="A172" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.party.effectSummary</t>
         </is>
       </c>
       <c r="B172" t="inlineStr" s="2">
@@ -5086,24 +4856,24 @@
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D172" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.scene[1]</t>
+          <t xml:space="preserve">party.effectSummary</t>
         </is>
       </c>
       <c r="G172" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}は無言でリングを降りた。その拳だけが震えていた</t>
+          <t xml:space="preserve">選手同士の会話が増え、ロッカールームと社長への空気が柔らかくなる</t>
         </is>
       </c>
     </row>
     <row r="173" ht="40" customHeight="1">
       <c r="A173" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.party.recommendation</t>
         </is>
       </c>
       <c r="B173" t="inlineStr" s="2">
@@ -5113,24 +4883,24 @@
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D173" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.scene[2]</t>
+          <t xml:space="preserve">party.recommendation</t>
         </is>
       </c>
       <c r="G173" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が帰り際、振り返って{name2}のほうを一瞬だけ見た</t>
+          <t xml:space="preserve">ロッカールームの空気に少し陰りが見えてきたときの応急処置として。単発では決定打にならない点に留意。</t>
         </is>
       </c>
     </row>
     <row r="174" ht="40" customHeight="1">
       <c r="A174" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.scene[3]</t>
+          <t xml:space="preserve">DECISION_DOCS.trainer.label</t>
         </is>
       </c>
       <c r="B174" t="inlineStr" s="2">
@@ -5140,24 +4910,24 @@
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D174" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.scene[3]</t>
+          <t xml:space="preserve">trainer.label</t>
         </is>
       </c>
       <c r="G174" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">試合後の通路で、{name}が壁を叩く音がした</t>
+          <t xml:space="preserve">外部コーチ招聘状</t>
         </is>
       </c>
     </row>
     <row r="175" ht="40" customHeight="1">
       <c r="A175" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.normal[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.trainer.categoryLabel</t>
         </is>
       </c>
       <c r="B175" t="inlineStr" s="2">
@@ -5167,29 +4937,24 @@
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D175" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">trainer.categoryLabel</t>
         </is>
       </c>
       <c r="G175" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだ、足りないのか</t>
+          <t xml:space="preserve">育成</t>
         </is>
       </c>
     </row>
     <row r="176" ht="40" customHeight="1">
       <c r="A176" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.normal[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.trainer.costLabel</t>
         </is>
       </c>
       <c r="B176" t="inlineStr" s="2">
@@ -5199,29 +4964,24 @@
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D176" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.normal[2]</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">trainer.costLabel</t>
         </is>
       </c>
       <c r="G176" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…くやしい</t>
+          <t xml:space="preserve">コーチの格による</t>
         </is>
       </c>
     </row>
     <row r="177" ht="40" customHeight="1">
       <c r="A177" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.bold[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.trainer.body</t>
         </is>
       </c>
       <c r="B177" t="inlineStr" s="2">
@@ -5231,29 +4991,24 @@
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D177" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">trainer.body</t>
         </is>
       </c>
       <c r="G177" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…次は絶対に負けない</t>
+          <t xml:space="preserve">今期の候補から外部コーチを選び、一人の選手に短期集中で指導を受けさせる</t>
         </is>
       </c>
     </row>
     <row r="178" ht="40" customHeight="1">
       <c r="A178" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.bold[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.trainer.detailText</t>
         </is>
       </c>
       <c r="B178" t="inlineStr" s="2">
@@ -5263,29 +5018,24 @@
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D178" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.bold[2]</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">trainer.detailText</t>
         </is>
       </c>
       <c r="G178" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この借りは必ず返す</t>
+          <t xml:space="preserve">今期市場に出ている外部コーチの中から一人を選び、期間限定で招聘する。指導タイプと選手の相性、得意スタイルの一致が効果を左右する。招聘中は雇用コーチの指導から外れ、そのコーチに専念する。</t>
         </is>
       </c>
     </row>
     <row r="179" ht="40" customHeight="1">
       <c r="A179" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.earnest[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.trainer.effectSummary</t>
         </is>
       </c>
       <c r="B179" t="inlineStr" s="2">
@@ -5295,29 +5045,24 @@
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D179" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">trainer.effectSummary</t>
         </is>
       </c>
       <c r="G179" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…あの人にはまだ勝てない。でも、だからこそ</t>
+          <t xml:space="preserve">4週間のあいだ対象選手の練習効果が上がる。コーチの格・相性・特殊能力しだいで伸び方が変わる</t>
         </is>
       </c>
     </row>
     <row r="180" ht="40" customHeight="1">
       <c r="A180" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.earnest[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.trainer.recommendation</t>
         </is>
       </c>
       <c r="B180" t="inlineStr" s="2">
@@ -5327,29 +5072,24 @@
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D180" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.earnest[2]</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">trainer.recommendation</t>
         </is>
       </c>
       <c r="G180" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…もっと練習する。絶対に</t>
+          <t xml:space="preserve">今期の市場に出た顔ぶれを見て、伸ばしたい選手に合いそうな一人を選ぶ。同時に招聘できるのは1件のみ、同じ選手を続けて詰め込みすぎると効果が鈍る点に注意。</t>
         </is>
       </c>
     </row>
     <row r="181" ht="40" customHeight="1">
       <c r="A181" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.emotional[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.camp.label</t>
         </is>
       </c>
       <c r="B181" t="inlineStr" s="2">
@@ -5359,29 +5099,24 @@
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D181" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">camp.label</t>
         </is>
       </c>
       <c r="G181" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…悔しい…悔しい…！</t>
+          <t xml:space="preserve">合宿実施手配書</t>
         </is>
       </c>
     </row>
     <row r="182" ht="40" customHeight="1">
       <c r="A182" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.R5.voice._default.emotional[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.camp.categoryLabel</t>
         </is>
       </c>
       <c r="B182" t="inlineStr" s="2">
@@ -5391,29 +5126,24 @@
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D182" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">R5.voice._default.emotional[2]</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">camp.categoryLabel</t>
         </is>
       </c>
       <c r="G182" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…なんであたしは勝てないの</t>
+          <t xml:space="preserve">育成</t>
         </is>
       </c>
     </row>
     <row r="183" ht="40" customHeight="1">
       <c r="A183" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.camp.body</t>
         </is>
       </c>
       <c r="B183" t="inlineStr" s="2">
@@ -5423,24 +5153,24 @@
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D183" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">friction.scene[1]</t>
+          <t xml:space="preserve">camp.body</t>
         </is>
       </c>
       <c r="G183" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}が練習メニューの順番で揉めていた。些細なことだが</t>
+          <t xml:space="preserve">全選手を集中的に強化するため、合宿を実施する</t>
         </is>
       </c>
     </row>
     <row r="184" ht="40" customHeight="1">
       <c r="A184" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.camp.detailText</t>
         </is>
       </c>
       <c r="B184" t="inlineStr" s="2">
@@ -5450,24 +5180,24 @@
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D184" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">friction.scene[2]</t>
+          <t xml:space="preserve">camp.detailText</t>
         </is>
       </c>
       <c r="G184" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が{name2}の練習態度について、小声で何か言っていた</t>
+          <t xml:space="preserve">選手全員を合宿地へ送り込み、短期集中で基礎を鍛え直す。ひとり40万×人数ぶんの費用と決裁枠3を消費する重量級書類。</t>
         </is>
       </c>
     </row>
     <row r="185" ht="40" customHeight="1">
       <c r="A185" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.scene[3]</t>
+          <t xml:space="preserve">DECISION_DOCS.camp.effectSummary</t>
         </is>
       </c>
       <c r="B185" t="inlineStr" s="2">
@@ -5477,24 +5207,24 @@
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D185" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">friction.scene[3]</t>
+          <t xml:space="preserve">camp.effectSummary</t>
         </is>
       </c>
       <c r="G185" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}が同時に控え室に入った瞬間、空気が変わった</t>
+          <t xml:space="preserve">2週間のあいだ全員の練習効果が上がり、団体全体に一体感が育つ</t>
         </is>
       </c>
     </row>
     <row r="186" ht="40" customHeight="1">
       <c r="A186" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.friction.staff[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.camp.recommendation</t>
         </is>
       </c>
       <c r="B186" t="inlineStr" s="2">
@@ -5504,24 +5234,24 @@
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D186" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">friction.staff[1]</t>
+          <t xml:space="preserve">camp.recommendation</t>
         </is>
       </c>
       <c r="G186" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スタッフから: {name}と{name2}、ちょっと相性が良くないみたいで…</t>
+          <t xml:space="preserve">資金に余裕があり、オフシーズン前後に全体を底上げしたいとき。年1〜2回が現実的な使用頻度。</t>
         </is>
       </c>
     </row>
     <row r="187" ht="40" customHeight="1">
       <c r="A187" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.media.label</t>
         </is>
       </c>
       <c r="B187" t="inlineStr" s="2">
@@ -5531,24 +5261,24 @@
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D187" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generation.scene[1]</t>
+          <t xml:space="preserve">media.label</t>
         </is>
       </c>
       <c r="G187" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}が一緒に帰っていく姿が見えた。同世代の気安さがある</t>
+          <t xml:space="preserve">メディア露出手配書</t>
         </is>
       </c>
     </row>
     <row r="188" ht="40" customHeight="1">
       <c r="A188" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.media.categoryLabel</t>
         </is>
       </c>
       <c r="B188" t="inlineStr" s="2">
@@ -5558,24 +5288,24 @@
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D188" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generation.scene[2]</t>
+          <t xml:space="preserve">media.categoryLabel</t>
         </is>
       </c>
       <c r="G188" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}が自販機の前で笑い合っていた。何が面白いのか、こちらには分からないが</t>
+          <t xml:space="preserve">広報</t>
         </is>
       </c>
     </row>
     <row r="189" ht="40" customHeight="1">
       <c r="A189" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[3]</t>
+          <t xml:space="preserve">DECISION_DOCS.media.body</t>
         </is>
       </c>
       <c r="B189" t="inlineStr" s="2">
@@ -5585,24 +5315,24 @@
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D189" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generation.scene[3]</t>
+          <t xml:space="preserve">media.body</t>
         </is>
       </c>
       <c r="G189" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が{name2}を自主練に誘っている。いい雰囲気だ</t>
+          <t xml:space="preserve">対象選手を広告塔とし、団体の知名度向上を図る</t>
         </is>
       </c>
     </row>
     <row r="190" ht="40" customHeight="1">
       <c r="A190" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.generation.scene[4]</t>
+          <t xml:space="preserve">DECISION_DOCS.media.detailText</t>
         </is>
       </c>
       <c r="B190" t="inlineStr" s="2">
@@ -5612,24 +5342,24 @@
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D190" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">generation.scene[4]</t>
+          <t xml:space="preserve">media.detailText</t>
         </is>
       </c>
       <c r="G190" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}と{name2}が昼食を一緒に取っている。どうやら仲がいいらしい</t>
+          <t xml:space="preserve">対象選手をメディア露出の広告塔として起用。団体の知名度向上と本人の体調維持を両立させる外向き施策。</t>
         </is>
       </c>
     </row>
     <row r="191" ht="40" customHeight="1">
       <c r="A191" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.rivalryResolved.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.media.effectSummary</t>
         </is>
       </c>
       <c r="B191" t="inlineStr" s="2">
@@ -5639,24 +5369,24 @@
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D191" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalryResolved.scene[1]</t>
+          <t xml:space="preserve">media.effectSummary</t>
         </is>
       </c>
       <c r="G191" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決着はついた。だが{name}と{name2}が目を合わせた時、そこにはまだ何かがあった</t>
+          <t xml:space="preserve">選手人気と団体人気が上がり、体調が整う。本人も起用を前向きに受け止める</t>
         </is>
       </c>
     </row>
     <row r="192" ht="40" customHeight="1">
       <c r="A192" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.rivalryResolved.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.media.recommendation</t>
         </is>
       </c>
       <c r="B192" t="inlineStr" s="2">
@@ -5666,24 +5396,24 @@
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D192" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">rivalryResolved.scene[2]</t>
+          <t xml:space="preserve">media.recommendation</t>
         </is>
       </c>
       <c r="G192" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">因縁は終わった。はずだ。…だが{name}は{name2}の動向を気にしている</t>
+          <t xml:space="preserve">団体人気がある程度育ってから解禁される書類。看板選手の体調管理と兼ねて回すと無駄がない。選手の人気を直接押し上げたい時にも有効。</t>
         </is>
       </c>
     </row>
     <row r="193" ht="40" customHeight="1">
       <c r="A193" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.careerBestMQ.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.relationship_repair.label</t>
         </is>
       </c>
       <c r="B193" t="inlineStr" s="2">
@@ -5693,24 +5423,24 @@
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D193" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">careerBestMQ.scene[1]</t>
+          <t xml:space="preserve">relationship_repair.label</t>
         </is>
       </c>
       <c r="G193" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が試合後、自分の両手を見つめていた。何かを掴んだ表情だ</t>
+          <t xml:space="preserve">関係修復斡旋書</t>
         </is>
       </c>
     </row>
     <row r="194" ht="40" customHeight="1">
       <c r="A194" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.careerBestMQ.scene[2]</t>
+          <t xml:space="preserve">DECISION_DOCS.relationship_repair.categoryLabel</t>
         </is>
       </c>
       <c r="B194" t="inlineStr" s="2">
@@ -5720,24 +5450,24 @@
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D194" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">careerBestMQ.scene[2]</t>
+          <t xml:space="preserve">relationship_repair.categoryLabel</t>
         </is>
       </c>
       <c r="G194" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}の試合が終わった後、先輩たちが小さく頷いていた</t>
+          <t xml:space="preserve">選手ケア</t>
         </is>
       </c>
     </row>
     <row r="195" ht="40" customHeight="1">
       <c r="A195" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.normal[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.relationship_repair.body</t>
         </is>
       </c>
       <c r="B195" t="inlineStr" s="2">
@@ -5747,29 +5477,24 @@
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D195" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice._default.normal[1]</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr" s="5">
-        <is>
-          <t xml:space="preserve">ノーマル</t>
+          <t xml:space="preserve">relationship_repair.body</t>
         </is>
       </c>
       <c r="G195" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…ここで頑張ってきてよかった</t>
+          <t xml:space="preserve">長期的な険悪関係にあるペアの間に立ち、関係改善を図る</t>
         </is>
       </c>
     </row>
     <row r="196" ht="40" customHeight="1">
       <c r="A196" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.bold[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.relationship_repair.detailText</t>
         </is>
       </c>
       <c r="B196" t="inlineStr" s="2">
@@ -5779,29 +5504,24 @@
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D196" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F196" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">relationship_repair.detailText</t>
         </is>
       </c>
       <c r="G196" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…まだまだ強くなれる！この団体でなら</t>
+          <t xml:space="preserve">勝負の世界では険悪な関係も時に武器になる。だが限度を超えると組織全体を蝕む。社長が間に立ち、最悪の事態を避ける。成功率は約70%。失敗しても関係はそのまま。</t>
         </is>
       </c>
     </row>
     <row r="197" ht="40" customHeight="1">
       <c r="A197" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.quiet[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.relationship_repair.effectSummary</t>
         </is>
       </c>
       <c r="B197" t="inlineStr" s="2">
@@ -5811,29 +5531,24 @@
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D197" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice._default.quiet[1]</t>
-        </is>
-      </c>
-      <c r="F197" t="inlineStr" s="7">
-        <is>
-          <t xml:space="preserve">寡黙</t>
+          <t xml:space="preserve">relationship_repair.effectSummary</t>
         </is>
       </c>
       <c r="G197" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…この場所に感謝している</t>
+          <t xml:space="preserve">成功時、双方向 bond +5〜+10。失敗時は据え置き。</t>
         </is>
       </c>
     </row>
     <row r="198" ht="40" customHeight="1">
       <c r="A198" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.earnest[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.relationship_repair.recommendation</t>
         </is>
       </c>
       <c r="B198" t="inlineStr" s="2">
@@ -5843,29 +5558,24 @@
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D198" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F198" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">relationship_repair.recommendation</t>
         </is>
       </c>
       <c r="G198" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなのおかげです。もっと恩返しがしたい</t>
+          <t xml:space="preserve">W-1（憎い敵ゾーン）が累計4回以上発火したペアに対して使用できる。慢性化する前に手を打てば、亀裂が修復可能になることもある。</t>
         </is>
       </c>
     </row>
     <row r="199" ht="40" customHeight="1">
       <c r="A199" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.breakthrough.voice._default.emotional[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.label</t>
         </is>
       </c>
       <c r="B199" t="inlineStr" s="2">
@@ -5875,29 +5585,24 @@
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D199" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">breakthrough.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F199" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">faction_decree.label</t>
         </is>
       </c>
       <c r="G199" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…うれしい…ここにいてよかった</t>
+          <t xml:space="preserve">派閥解散命令</t>
         </is>
       </c>
     </row>
     <row r="200" ht="40" customHeight="1">
       <c r="A200" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.scene[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.categoryLabel</t>
         </is>
       </c>
       <c r="B200" t="inlineStr" s="2">
@@ -5907,24 +5612,24 @@
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D200" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.scene[1]</t>
+          <t xml:space="preserve">faction_decree.categoryLabel</t>
         </is>
       </c>
       <c r="G200" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}はチームの勝利に拳を握りしめた。この団体の看板を背負う覚悟が見えた</t>
+          <t xml:space="preserve">人事</t>
         </is>
       </c>
     </row>
     <row r="201" ht="40" customHeight="1">
       <c r="A201" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice._default.bold[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.body</t>
         </is>
       </c>
       <c r="B201" t="inlineStr" s="2">
@@ -5934,29 +5639,24 @@
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D201" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice._default.bold[1]</t>
-        </is>
-      </c>
-      <c r="F201" t="inlineStr" s="6">
-        <is>
-          <t xml:space="preserve">強気</t>
+          <t xml:space="preserve">faction_decree.body</t>
         </is>
       </c>
       <c r="G201" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…わたしが勝つに決まってるでしょ。この団体を背負ってるんだから！</t>
+          <t xml:space="preserve">団体内の派閥を社長命令で解散させ、以後の結成を認めるかどうかを決める</t>
         </is>
       </c>
     </row>
     <row r="202" ht="40" customHeight="1">
       <c r="A202" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice._default.earnest[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.detailText</t>
         </is>
       </c>
       <c r="B202" t="inlineStr" s="2">
@@ -5966,29 +5666,24 @@
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D202" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice._default.earnest[1]</t>
-        </is>
-      </c>
-      <c r="F202" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">真面目</t>
+          <t xml:space="preserve">faction_decree.detailText</t>
         </is>
       </c>
       <c r="G202" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…みんなの想いを背負って戦えて光栄です</t>
+          <t xml:space="preserve">選手たちが自然に作った群れを、上から畳む。畳まれた側は当然おもしろくない。とくに束ねていた本人には深く残る。勢いに乗っていた派閥ほど、その傷は深い。</t>
         </is>
       </c>
     </row>
     <row r="203" ht="40" customHeight="1">
       <c r="A203" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS.warVictory.voice._default.emotional[1]</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.effectSummary</t>
         </is>
       </c>
       <c r="B203" t="inlineStr" s="2">
@@ -5998,29 +5693,24 @@
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">SNAPSHOT_TEXTS</t>
+          <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
       <c r="D203" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">warVictory.voice._default.emotional[1]</t>
-        </is>
-      </c>
-      <c r="F203" t="inlineStr" s="10">
-        <is>
-          <t xml:space="preserve">感情的</t>
+          <t xml:space="preserve">faction_decree.effectSummary</t>
         </is>
       </c>
       <c r="G203" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">…勝った…！ みんなのおかげだよ…！</t>
+          <t xml:space="preserve">選択した内容によって、解散のみ／解散して以後禁止／禁止の解除 が実行される</t>
         </is>
       </c>
     </row>
     <row r="204" ht="40" customHeight="1">
       <c r="A204" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.bonus.label</t>
+          <t xml:space="preserve">DECISION_DOCS.faction_decree.recommendation</t>
         </is>
       </c>
       <c r="B204" t="inlineStr" s="2">
@@ -6035,19 +5725,19 @@
       </c>
       <c r="D204" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.label</t>
+          <t xml:space="preserve">faction_decree.recommendation</t>
         </is>
       </c>
       <c r="G204" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ボーナス支給願</t>
+          <t xml:space="preserve">派閥の揉め事を団体から切り離したいときに。まだ派閥が生まれていないうちに禁止しておけば、誰の信頼も損なわずに済む。</t>
         </is>
       </c>
     </row>
     <row r="205" ht="40" customHeight="1">
       <c r="A205" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.bonus.categoryLabel</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.label</t>
         </is>
       </c>
       <c r="B205" t="inlineStr" s="2">
@@ -6062,19 +5752,19 @@
       </c>
       <c r="D205" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.categoryLabel</t>
+          <t xml:space="preserve">hireCoach.label</t>
         </is>
       </c>
       <c r="G205" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手ケア</t>
+          <t xml:space="preserve">コーチ雇用決裁書</t>
         </is>
       </c>
     </row>
     <row r="206" ht="40" customHeight="1">
       <c r="A206" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.bonus.costLabel</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.categoryLabel</t>
         </is>
       </c>
       <c r="B206" t="inlineStr" s="2">
@@ -6089,19 +5779,19 @@
       </c>
       <c r="D206" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.costLabel</t>
+          <t xml:space="preserve">hireCoach.categoryLabel</t>
         </is>
       </c>
       <c r="G206" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">起案額による</t>
+          <t xml:space="preserve">人事</t>
         </is>
       </c>
     </row>
     <row r="207" ht="40" customHeight="1">
       <c r="A207" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.bonus.body</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.body</t>
         </is>
       </c>
       <c r="B207" t="inlineStr" s="2">
@@ -6116,19 +5806,19 @@
       </c>
       <c r="D207" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.body</t>
+          <t xml:space="preserve">hireCoach.body</t>
         </is>
       </c>
       <c r="G207" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対象選手に特別手当を支給し、組織貢献への感謝を示す</t>
+          <t xml:space="preserve">新たなスタッフを招聘し、団体の指導体制を強化する</t>
         </is>
       </c>
     </row>
     <row r="208" ht="40" customHeight="1">
       <c r="A208" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.bonus.detailText</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.detailText</t>
         </is>
       </c>
       <c r="B208" t="inlineStr" s="2">
@@ -6143,19 +5833,19 @@
       </c>
       <c r="D208" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.detailText</t>
+          <t xml:space="preserve">hireCoach.detailText</t>
         </is>
       </c>
       <c r="G208" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">起案された支給額の中から、いくら積むかを社長が決める。額面が彼女の格に見合ってこそ、誠意は伝わる。安すぎる額は、かえって心を離れさせることもある。</t>
+          <t xml:space="preserve">新たなコーチを招聘し、指導体制を強化する。机には並ばず、コーチ画面から実行する特殊書類。</t>
         </is>
       </c>
     </row>
     <row r="209" ht="40" customHeight="1">
       <c r="A209" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.bonus.effectSummary</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.effectSummary</t>
         </is>
       </c>
       <c r="B209" t="inlineStr" s="2">
@@ -6170,19 +5860,19 @@
       </c>
       <c r="D209" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.effectSummary</t>
+          <t xml:space="preserve">hireCoach.effectSummary</t>
         </is>
       </c>
       <c r="G209" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">支給額しだいで本人の受け止め方が変わる。相場を大きく超える額は深く響く</t>
+          <t xml:space="preserve">コーチを1名新しく迎える(決裁枠を2消費)</t>
         </is>
       </c>
     </row>
     <row r="210" ht="40" customHeight="1">
       <c r="A210" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.bonus.recommendation</t>
+          <t xml:space="preserve">DECISION_DOCS.hireCoach.recommendation</t>
         </is>
       </c>
       <c r="B210" t="inlineStr" s="2">
@@ -6197,19 +5887,19 @@
       </c>
       <c r="D210" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">bonus.recommendation</t>
+          <t xml:space="preserve">hireCoach.recommendation</t>
         </is>
       </c>
       <c r="G210" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体への気持ちが陰りはじめた選手に、早めに手を打つと効果的。同じ選手への再支給は相場が吊り上がる点に注意。</t>
+          <t xml:space="preserve">コーチ枠に空きがあり、新規雇用を検討している週に。机に書類として表示されない点に注意。</t>
         </is>
       </c>
     </row>
     <row r="211" ht="40" customHeight="1">
       <c r="A211" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.encourage.label</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[1]</t>
         </is>
       </c>
       <c r="B211" t="inlineStr" s="2">
@@ -6219,24 +5909,24 @@
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D211" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.label</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G211" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">声かけ</t>
+          <t xml:space="preserve">無難な線です。ただ、響くかどうかは相手次第かと。</t>
         </is>
       </c>
     </row>
     <row r="212" ht="40" customHeight="1">
       <c r="A212" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.encourage.categoryLabel</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[2]</t>
         </is>
       </c>
       <c r="B212" t="inlineStr" s="2">
@@ -6246,24 +5936,24 @@
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D212" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.categoryLabel</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G212" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手ケア</t>
+          <t xml:space="preserve">彼女の格に見合った額かと存じます。</t>
         </is>
       </c>
     </row>
     <row r="213" ht="40" customHeight="1">
       <c r="A213" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.encourage.body</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[3]</t>
         </is>
       </c>
       <c r="B213" t="inlineStr" s="2">
@@ -6273,24 +5963,24 @@
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D213" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.body</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G213" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気にかけている選手に社長自ら声をかけに行く</t>
+          <t xml:space="preserve">相場を超えています。誠意は伝わるはずです。</t>
         </is>
       </c>
     </row>
     <row r="214" ht="40" customHeight="1">
       <c r="A214" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.encourage.detailText</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[4]</t>
         </is>
       </c>
       <c r="B214" t="inlineStr" s="2">
@@ -6300,24 +5990,24 @@
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
       <c r="D214" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.detailText</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G214" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">決裁枠も資金も使わない、社長自らの自発的な行動。スランプ中・モチベ喪失中・最近様子が気になる選手に足を運んで声をかける。</t>
+          <t xml:space="preserve">……思い切りましたな。ここまで出す団体は他にありません。</t>
         </is>
       </c>
     </row>
     <row r="215" ht="40" customHeight="1">
       <c r="A215" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.encourage.effectSummary</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[1]</t>
         </is>
       </c>
       <c r="B215" t="inlineStr" s="2">
@@ -6327,24 +6017,24 @@
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D215" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.effectSummary</t>
+          <t xml:space="preserve">[1]</t>
         </is>
       </c>
       <c r="G215" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本人の表情が少し和らぐ（スランプ・モチベ喪失なら回復促進も）</t>
+          <t xml:space="preserve">{name1}と{name2}が朝から激しいスパーリングを繰り広げている…！</t>
         </is>
       </c>
     </row>
     <row r="216" ht="40" customHeight="1">
       <c r="A216" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.encourage.recommendation</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[2]</t>
         </is>
       </c>
       <c r="B216" t="inlineStr" s="2">
@@ -6354,24 +6044,24 @@
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D216" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">encourage.recommendation</t>
+          <t xml:space="preserve">[2]</t>
         </is>
       </c>
       <c r="G216" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">気になる選手のポップアップから直接実行する。机には並ばない。</t>
+          <t xml:space="preserve">夜の自主練で{name1}が黙々とスクワットをしている…</t>
         </is>
       </c>
     </row>
     <row r="217" ht="40" customHeight="1">
       <c r="A217" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.special_treatment.label</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[3]</t>
         </is>
       </c>
       <c r="B217" t="inlineStr" s="2">
@@ -6381,24 +6071,24 @@
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D217" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.label</t>
+          <t xml:space="preserve">[3]</t>
         </is>
       </c>
       <c r="G217" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">特別治療指示書</t>
+          <t xml:space="preserve">{name1}が{name2}に技の受け身を教えている場面が見られた</t>
         </is>
       </c>
     </row>
     <row r="218" ht="40" customHeight="1">
       <c r="A218" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.special_treatment.categoryLabel</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[4]</t>
         </is>
       </c>
       <c r="B218" t="inlineStr" s="2">
@@ -6408,24 +6098,24 @@
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D218" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.categoryLabel</t>
+          <t xml:space="preserve">[4]</t>
         </is>
       </c>
       <c r="G218" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手ケア</t>
+          <t xml:space="preserve">合宿の食事は{name1}が率先して準備していた</t>
         </is>
       </c>
     </row>
     <row r="219" ht="40" customHeight="1">
       <c r="A219" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.special_treatment.body</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[5]</t>
         </is>
       </c>
       <c r="B219" t="inlineStr" s="2">
@@ -6435,24 +6125,24 @@
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D219" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.body</t>
+          <t xml:space="preserve">[5]</t>
         </is>
       </c>
       <c r="G219" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">離脱中の選手に専門医を手配し、復帰を早める</t>
+          <t xml:space="preserve">{name1}と{name2}が夕食後のランニングで競い合っている</t>
         </is>
       </c>
     </row>
     <row r="220" ht="40" customHeight="1">
       <c r="A220" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.special_treatment.detailText</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[6]</t>
         </is>
       </c>
       <c r="B220" t="inlineStr" s="2">
@@ -6462,24 +6152,24 @@
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D220" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.detailText</t>
+          <t xml:space="preserve">[6]</t>
         </is>
       </c>
       <c r="G220" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">専門医による集中ケアを正式に発注。怪我からの離脱期間を確率的に短縮する、復帰前倒しの一手。確実な短縮量は治療結果次第。</t>
+          <t xml:space="preserve">早朝の海辺で{name1}が一人、基礎練習に励んでいた</t>
         </is>
       </c>
     </row>
     <row r="221" ht="40" customHeight="1">
       <c r="A221" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.special_treatment.effectSummary</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[7]</t>
         </is>
       </c>
       <c r="B221" t="inlineStr" s="2">
@@ -6489,24 +6179,24 @@
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D221" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.effectSummary</t>
+          <t xml:space="preserve">[7]</t>
         </is>
       </c>
       <c r="G221" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対象選手の離脱期間が1〜4週短縮される</t>
+          <t xml:space="preserve">{name1}が新技の研究に没頭している姿が印象的だった</t>
         </is>
       </c>
     </row>
     <row r="222" ht="40" customHeight="1">
       <c r="A222" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.special_treatment.recommendation</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[8]</t>
         </is>
       </c>
       <c r="B222" t="inlineStr" s="2">
@@ -6516,24 +6206,24 @@
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D222" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">special_treatment.recommendation</t>
+          <t xml:space="preserve">[8]</t>
         </is>
       </c>
       <c r="G222" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">主力選手や王座挑戦が控えている選手の離脱が痛手なときに。離脱が長引いている怪我ほど短縮量も大きくなりやすい。</t>
+          <t xml:space="preserve">消灯後も{name1}と{name2}がリングで語り合っていた</t>
         </is>
       </c>
     </row>
     <row r="223" ht="40" customHeight="1">
       <c r="A223" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.refresh_leave.label</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[9]</t>
         </is>
       </c>
       <c r="B223" t="inlineStr" s="2">
@@ -6543,24 +6233,24 @@
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D223" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.label</t>
+          <t xml:space="preserve">[9]</t>
         </is>
       </c>
       <c r="G223" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">休暇辞令</t>
+          <t xml:space="preserve">{name1}が合宿の記念写真を撮ろうとみんなを集めていた</t>
         </is>
       </c>
     </row>
     <row r="224" ht="40" customHeight="1">
       <c r="A224" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.refresh_leave.categoryLabel</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[10]</t>
         </is>
       </c>
       <c r="B224" t="inlineStr" s="2">
@@ -6570,24 +6260,24 @@
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D224" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.categoryLabel</t>
+          <t xml:space="preserve">[10]</t>
         </is>
       </c>
       <c r="G224" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手ケア</t>
+          <t xml:space="preserve">全員で浜辺を走るメニューに{name1}が一番乗りでゴールした</t>
         </is>
       </c>
     </row>
     <row r="225" ht="40" customHeight="1">
       <c r="A225" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.refresh_leave.costLabel</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[11]</t>
         </is>
       </c>
       <c r="B225" t="inlineStr" s="2">
@@ -6597,24 +6287,24 @@
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D225" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.costLabel</t>
+          <t xml:space="preserve">[11]</t>
         </is>
       </c>
       <c r="G225" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">週給×週数+50万</t>
+          <t xml:space="preserve">{name1}のムードメーカーぶりで合宿の雰囲気がぐっと明るくなった</t>
         </is>
       </c>
     </row>
     <row r="226" ht="40" customHeight="1">
       <c r="A226" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.refresh_leave.body</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[12]</t>
         </is>
       </c>
       <c r="B226" t="inlineStr" s="2">
@@ -6624,24 +6314,24 @@
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
       <c r="D226" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.body</t>
+          <t xml:space="preserve">[12]</t>
         </is>
       </c>
       <c r="G226" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">心身の疲弊を察し、一定期間の休養を与える</t>
+          <t xml:space="preserve">練習後の大浴場で{name1}と{name2}が今後の抱負を語り合っていた</t>
         </is>
       </c>
     </row>
     <row r="227" ht="40" customHeight="1">
       <c r="A227" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.refresh_leave.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].text</t>
         </is>
       </c>
       <c r="B227" t="inlineStr" s="2">
@@ -6651,24 +6341,24 @@
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D227" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.detailText</t>
+          <t xml:space="preserve">B1[1].text</t>
         </is>
       </c>
       <c r="G227" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">1〜4週間の休暇を正式な辞令として発行する。休暇中の試合には欠場するが、そのぶん心身は着実に回復していく。長い休みは、積み重なった消耗までも癒やす。</t>
+          <t xml:space="preserve">⚠️ {name}が練習中にアクシデント</t>
         </is>
       </c>
     </row>
     <row r="228" ht="40" customHeight="1">
       <c r="A228" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.refresh_leave.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].detail</t>
         </is>
       </c>
       <c r="B228" t="inlineStr" s="2">
@@ -6678,24 +6368,24 @@
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D228" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.effectSummary</t>
+          <t xml:space="preserve">B1[1].detail</t>
         </is>
       </c>
       <c r="G228" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">休みの長さに応じて体調が戻り、長期なら蓄積した消耗も癒える。本人にも気遣いが伝わる</t>
+          <t xml:space="preserve">{name}が練習中に技を受けた際にバランスを崩し、負傷してしまった。</t>
         </is>
       </c>
     </row>
     <row r="229" ht="40" customHeight="1">
       <c r="A229" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.refresh_leave.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].text</t>
         </is>
       </c>
       <c r="B229" t="inlineStr" s="2">
@@ -6705,24 +6395,24 @@
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D229" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">refresh_leave.recommendation</t>
+          <t xml:space="preserve">B1[2].text</t>
         </is>
       </c>
       <c r="G229" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">疲れの見える主力を、大事な興行の前に立て直す疲労管理の要。休暇中の欠場と引き換えになる点は覚悟すること。</t>
+          <t xml:space="preserve">⚠️ {name}が練習で負傷</t>
         </is>
       </c>
     </row>
     <row r="230" ht="40" customHeight="1">
       <c r="A230" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.party.label</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].detail</t>
         </is>
       </c>
       <c r="B230" t="inlineStr" s="2">
@@ -6732,24 +6422,24 @@
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D230" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.label</t>
+          <t xml:space="preserve">B1[2].detail</t>
         </is>
       </c>
       <c r="G230" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">慰労会開催届</t>
+          <t xml:space="preserve">スパーリング中に{name}が相手の技を受け損ね、マットに叩きつけられた。</t>
         </is>
       </c>
     </row>
     <row r="231" ht="40" customHeight="1">
       <c r="A231" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.party.categoryLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].text</t>
         </is>
       </c>
       <c r="B231" t="inlineStr" s="2">
@@ -6759,24 +6449,24 @@
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D231" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.categoryLabel</t>
+          <t xml:space="preserve">B1[3].text</t>
         </is>
       </c>
       <c r="G231" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手ケア</t>
+          <t xml:space="preserve">⚠️ {name}に練習中のトラブル</t>
         </is>
       </c>
     </row>
     <row r="232" ht="40" customHeight="1">
       <c r="A232" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.party.body</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].detail</t>
         </is>
       </c>
       <c r="B232" t="inlineStr" s="2">
@@ -6786,24 +6476,24 @@
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D232" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.body</t>
+          <t xml:space="preserve">B1[3].detail</t>
         </is>
       </c>
       <c r="G232" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体の雰囲気を立て直すべく、慰労の宴席を設ける</t>
+          <t xml:space="preserve">{name}が新技の練習中に着地に失敗。痛みを訴えている。</t>
         </is>
       </c>
     </row>
     <row r="233" ht="40" customHeight="1">
       <c r="A233" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.party.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].text</t>
         </is>
       </c>
       <c r="B233" t="inlineStr" s="2">
@@ -6813,24 +6503,24 @@
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D233" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.detailText</t>
+          <t xml:space="preserve">B1[4].text</t>
         </is>
       </c>
       <c r="G233" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全選手を集めた慰労の宴席。個別の数値を動かすより、ロッカールームの空気そのものを立て直すのが主目的。</t>
+          <t xml:space="preserve">⚠️ {name}がロープワーク中に負傷</t>
         </is>
       </c>
     </row>
     <row r="234" ht="40" customHeight="1">
       <c r="A234" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.party.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].detail</t>
         </is>
       </c>
       <c r="B234" t="inlineStr" s="2">
@@ -6840,24 +6530,24 @@
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D234" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.effectSummary</t>
+          <t xml:space="preserve">B1[4].detail</t>
         </is>
       </c>
       <c r="G234" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手同士の会話が増え、ロッカールームと社長への空気が柔らかくなる</t>
+          <t xml:space="preserve">ロープの反動を利用した連続技の練習中、{name}の足がロープに絡まり転倒。すぐには立ち上がれなかった。</t>
         </is>
       </c>
     </row>
     <row r="235" ht="40" customHeight="1">
       <c r="A235" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.party.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].text</t>
         </is>
       </c>
       <c r="B235" t="inlineStr" s="2">
@@ -6867,24 +6557,24 @@
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D235" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">party.recommendation</t>
+          <t xml:space="preserve">B1[5].text</t>
         </is>
       </c>
       <c r="G235" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ロッカールームの空気に少し陰りが見えてきたときの応急処置として。単発では決定打にならない点に留意。</t>
+          <t xml:space="preserve">⚠️ {name}がスパーリング中に痛みを訴えた</t>
         </is>
       </c>
     </row>
     <row r="236" ht="40" customHeight="1">
       <c r="A236" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.trainer.label</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].detail</t>
         </is>
       </c>
       <c r="B236" t="inlineStr" s="2">
@@ -6894,24 +6584,24 @@
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D236" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.label</t>
+          <t xml:space="preserve">B1[5].detail</t>
         </is>
       </c>
       <c r="G236" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">外部コーチ招聘状</t>
+          <t xml:space="preserve">練習パートナーとのスパーリングで{name}が技を受けた直後、顔をしかめて膝をついた。本人は続けられると言うが…</t>
         </is>
       </c>
     </row>
     <row r="237" ht="40" customHeight="1">
       <c r="A237" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.trainer.categoryLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].text</t>
         </is>
       </c>
       <c r="B237" t="inlineStr" s="2">
@@ -6921,24 +6611,24 @@
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D237" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.categoryLabel</t>
+          <t xml:space="preserve">B1[6].text</t>
         </is>
       </c>
       <c r="G237" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">育成</t>
+          <t xml:space="preserve">⚠️ {name}が練習後に体の異変を報告</t>
         </is>
       </c>
     </row>
     <row r="238" ht="40" customHeight="1">
       <c r="A238" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.trainer.costLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].detail</t>
         </is>
       </c>
       <c r="B238" t="inlineStr" s="2">
@@ -6948,24 +6638,24 @@
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D238" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.costLabel</t>
+          <t xml:space="preserve">B1[6].detail</t>
         </is>
       </c>
       <c r="G238" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コーチの格による</t>
+          <t xml:space="preserve">練習を終えた{name}が、動かすと痛む箇所があると申告。無理をしていた可能性がある。</t>
         </is>
       </c>
     </row>
     <row r="239" ht="40" customHeight="1">
       <c r="A239" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.trainer.body</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].text</t>
         </is>
       </c>
       <c r="B239" t="inlineStr" s="2">
@@ -6975,24 +6665,24 @@
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D239" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.body</t>
+          <t xml:space="preserve">B2[1].text</t>
         </is>
       </c>
       <c r="G239" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今期の候補から外部コーチを選び、一人の選手に短期集中で指導を受けさせる</t>
+          <t xml:space="preserve">💥 {name1}と{name2}が衝突</t>
         </is>
       </c>
     </row>
     <row r="240" ht="40" customHeight="1">
       <c r="A240" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.trainer.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].detail</t>
         </is>
       </c>
       <c r="B240" t="inlineStr" s="2">
@@ -7002,24 +6692,24 @@
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.detailText</t>
+          <t xml:space="preserve">B2[1].detail</t>
         </is>
       </c>
       <c r="G240" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今期市場に出ている外部コーチの中から一人を選び、期間限定で招聘する。指導タイプと選手の相性、得意スタイルの一致が効果を左右する。招聘中は雇用コーチの指導から外れ、そのコーチに専念する。</t>
+          <t xml:space="preserve">控室で{name1}と{name2}の間に激しい口論が発生。周囲の制止も聞かず一触即発の状態になっている。</t>
         </is>
       </c>
     </row>
     <row r="241" ht="40" customHeight="1">
       <c r="A241" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.trainer.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].text</t>
         </is>
       </c>
       <c r="B241" t="inlineStr" s="2">
@@ -7029,24 +6719,24 @@
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D241" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.effectSummary</t>
+          <t xml:space="preserve">B2[2].text</t>
         </is>
       </c>
       <c r="G241" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">4週間のあいだ対象選手の練習効果が上がる。コーチの格・相性・特殊能力しだいで伸び方が変わる</t>
+          <t xml:space="preserve">💥 {name1}と{name2}の対立が深刻化</t>
         </is>
       </c>
     </row>
     <row r="242" ht="40" customHeight="1">
       <c r="A242" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.trainer.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].detail</t>
         </is>
       </c>
       <c r="B242" t="inlineStr" s="2">
@@ -7056,24 +6746,24 @@
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D242" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">trainer.recommendation</t>
+          <t xml:space="preserve">B2[2].detail</t>
         </is>
       </c>
       <c r="G242" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">今期の市場に出た顔ぶれを見て、伸ばしたい選手に合いそうな一人を選ぶ。同時に招聘できるのは1件のみ、同じ選手を続けて詰め込みすぎると効果が鈍る点に注意。</t>
+          <t xml:space="preserve">以前から不穏な空気があった{name1}と{name2}の関係がついに破綻。練習にも支障が出始めている。</t>
         </is>
       </c>
     </row>
     <row r="243" ht="40" customHeight="1">
       <c r="A243" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.camp.label</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].text</t>
         </is>
       </c>
       <c r="B243" t="inlineStr" s="2">
@@ -7083,24 +6773,24 @@
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D243" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.label</t>
+          <t xml:space="preserve">B2[3].text</t>
         </is>
       </c>
       <c r="G243" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿実施手配書</t>
+          <t xml:space="preserve">💥 {name1}と{name2}がスパーリングでエスカレート</t>
         </is>
       </c>
     </row>
     <row r="244" ht="40" customHeight="1">
       <c r="A244" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.camp.categoryLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].detail</t>
         </is>
       </c>
       <c r="B244" t="inlineStr" s="2">
@@ -7110,24 +6800,24 @@
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D244" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.categoryLabel</t>
+          <t xml:space="preserve">B2[3].detail</t>
         </is>
       </c>
       <c r="G244" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">育成</t>
+          <t xml:space="preserve">本来は軽い打ち合いのはずが、{name1}と{name2}のスパーリングが本気のぶつかり合いに発展。コーチが間に割って入る事態となった。</t>
         </is>
       </c>
     </row>
     <row r="245" ht="40" customHeight="1">
       <c r="A245" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.camp.body</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].text</t>
         </is>
       </c>
       <c r="B245" t="inlineStr" s="2">
@@ -7137,24 +6827,24 @@
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D245" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.body</t>
+          <t xml:space="preserve">B2[4].text</t>
         </is>
       </c>
       <c r="G245" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全選手を集中的に強化するため、合宿を実施する</t>
+          <t xml:space="preserve">💥 {name1}と{name2}の間に亀裂</t>
         </is>
       </c>
     </row>
     <row r="246" ht="40" customHeight="1">
       <c r="A246" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.camp.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].detail</t>
         </is>
       </c>
       <c r="B246" t="inlineStr" s="2">
@@ -7164,24 +6854,24 @@
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D246" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.detailText</t>
+          <t xml:space="preserve">B2[4].detail</t>
         </is>
       </c>
       <c r="G246" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手全員を合宿地へ送り込み、短期集中で基礎を鍛え直す。ひとり40万×人数ぶんの費用と決裁枠3を消費する重量級書類。</t>
+          <t xml:space="preserve">{name1}がSNSに意味深な投稿をしたことで{name2}が激怒。控室で怒鳴り合う二人の声が外まで漏れていた。</t>
         </is>
       </c>
     </row>
     <row r="247" ht="40" customHeight="1">
       <c r="A247" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.camp.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].text</t>
         </is>
       </c>
       <c r="B247" t="inlineStr" s="2">
@@ -7191,24 +6881,24 @@
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D247" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.effectSummary</t>
+          <t xml:space="preserve">B2[5].text</t>
         </is>
       </c>
       <c r="G247" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">2週間のあいだ全員の練習効果が上がり、団体全体に一体感が育つ</t>
+          <t xml:space="preserve">💥 {name1}と{name2}の関係が限界に</t>
         </is>
       </c>
     </row>
     <row r="248" ht="40" customHeight="1">
       <c r="A248" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.camp.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].detail</t>
         </is>
       </c>
       <c r="B248" t="inlineStr" s="2">
@@ -7218,24 +6908,24 @@
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D248" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">camp.recommendation</t>
+          <t xml:space="preserve">B2[5].detail</t>
         </is>
       </c>
       <c r="G248" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">資金に余裕があり、オフシーズン前後に全体を底上げしたいとき。年1〜2回が現実的な使用頻度。</t>
+          <t xml:space="preserve">合同練習中、{name1}が{name2}への不満を公然と口にした。全員の前での出来事に、チーム全体が凍りついた。</t>
         </is>
       </c>
     </row>
     <row r="249" ht="40" customHeight="1">
       <c r="A249" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.media.label</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].text</t>
         </is>
       </c>
       <c r="B249" t="inlineStr" s="2">
@@ -7245,24 +6935,24 @@
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D249" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.label</t>
+          <t xml:space="preserve">B3[1].text</t>
         </is>
       </c>
       <c r="G249" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">メディア露出手配書</t>
+          <t xml:space="preserve">⚔️ {orgName}から挑戦状</t>
         </is>
       </c>
     </row>
     <row r="250" ht="40" customHeight="1">
       <c r="A250" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.media.categoryLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].detail</t>
         </is>
       </c>
       <c r="B250" t="inlineStr" s="2">
@@ -7272,24 +6962,24 @@
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D250" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.categoryLabel</t>
+          <t xml:space="preserve">B3[1].detail</t>
         </is>
       </c>
       <c r="G250" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">広報</t>
+          <t xml:space="preserve">{orgName}が「実力を見せてやる」と挑戦状を叩きつけてきた。</t>
         </is>
       </c>
     </row>
     <row r="251" ht="40" customHeight="1">
       <c r="A251" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.media.body</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].text</t>
         </is>
       </c>
       <c r="B251" t="inlineStr" s="2">
@@ -7299,24 +6989,24 @@
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D251" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.body</t>
+          <t xml:space="preserve">B3[2].text</t>
         </is>
       </c>
       <c r="G251" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対象選手を広告塔とし、団体の知名度向上を図る</t>
+          <t xml:space="preserve">⚔️ {orgName}が宣戦布告</t>
         </is>
       </c>
     </row>
     <row r="252" ht="40" customHeight="1">
       <c r="A252" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.media.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].detail</t>
         </is>
       </c>
       <c r="B252" t="inlineStr" s="2">
@@ -7326,24 +7016,24 @@
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D252" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.detailText</t>
+          <t xml:space="preserve">B3[2].detail</t>
         </is>
       </c>
       <c r="G252" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">対象選手をメディア露出の広告塔として起用。団体の知名度向上と本人の体調維持を両立させる外向き施策。</t>
+          <t xml:space="preserve">{orgName}の代表が公の場でこちらの団体を挑発。挑戦状で決着をつけようと迫ってきた。</t>
         </is>
       </c>
     </row>
     <row r="253" ht="40" customHeight="1">
       <c r="A253" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.media.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].text</t>
         </is>
       </c>
       <c r="B253" t="inlineStr" s="2">
@@ -7353,24 +7043,24 @@
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D253" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.effectSummary</t>
+          <t xml:space="preserve">B3[3].text</t>
         </is>
       </c>
       <c r="G253" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手人気と団体人気が上がり、体調が整う。本人も起用を前向きに受け止める</t>
+          <t xml:space="preserve">⚔️ {orgName}の選手が記者会見で挑発</t>
         </is>
       </c>
     </row>
     <row r="254" ht="40" customHeight="1">
       <c r="A254" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.media.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].detail</t>
         </is>
       </c>
       <c r="B254" t="inlineStr" s="2">
@@ -7380,24 +7070,24 @@
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">media.recommendation</t>
+          <t xml:space="preserve">B3[3].detail</t>
         </is>
       </c>
       <c r="G254" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体人気がある程度育ってから解禁される書類。看板選手の体調管理と兼ねて回すと無駄がない。選手の人気を直接押し上げたい時にも有効。</t>
+          <t xml:space="preserve">{orgName}の選手がメディアの前でこちらの団体名を出し、「いつでも受けて立つ」と公開挑戦状を叩きつけた。</t>
         </is>
       </c>
     </row>
     <row r="255" ht="40" customHeight="1">
       <c r="A255" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.relationship_repair.label</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].text</t>
         </is>
       </c>
       <c r="B255" t="inlineStr" s="2">
@@ -7407,24 +7097,24 @@
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D255" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">relationship_repair.label</t>
+          <t xml:space="preserve">B3[4].text</t>
         </is>
       </c>
       <c r="G255" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">関係修復斡旋書</t>
+          <t xml:space="preserve">⚔️ {orgName}から果たし状が届いた</t>
         </is>
       </c>
     </row>
     <row r="256" ht="40" customHeight="1">
       <c r="A256" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.relationship_repair.categoryLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].detail</t>
         </is>
       </c>
       <c r="B256" t="inlineStr" s="2">
@@ -7434,24 +7124,24 @@
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">relationship_repair.categoryLabel</t>
+          <t xml:space="preserve">B3[4].detail</t>
         </is>
       </c>
       <c r="G256" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手ケア</t>
+          <t xml:space="preserve">{orgName}から正式な書面が届いた。「団体の威信をかけて一騎打ちを行いたい」——無視するわけにはいかない雰囲気だ。</t>
         </is>
       </c>
     </row>
     <row r="257" ht="40" customHeight="1">
       <c r="A257" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.relationship_repair.body</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].text</t>
         </is>
       </c>
       <c r="B257" t="inlineStr" s="2">
@@ -7461,24 +7151,24 @@
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D257" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">relationship_repair.body</t>
+          <t xml:space="preserve">B3[5].text</t>
         </is>
       </c>
       <c r="G257" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">長期的な険悪関係にあるペアの間に立ち、関係改善を図る</t>
+          <t xml:space="preserve">⚔️ {orgName}が興行に乗り込んできた</t>
         </is>
       </c>
     </row>
     <row r="258" ht="40" customHeight="1">
       <c r="A258" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.relationship_repair.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].detail</t>
         </is>
       </c>
       <c r="B258" t="inlineStr" s="2">
@@ -7488,24 +7178,24 @@
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D258" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">relationship_repair.detailText</t>
+          <t xml:space="preserve">B3[5].detail</t>
         </is>
       </c>
       <c r="G258" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">勝負の世界では険悪な関係も時に武器になる。だが限度を超えると組織全体を蝕む。社長が間に立ち、最悪の事態を避ける。成功率は約70%。失敗しても関係はそのまま。</t>
+          <t xml:space="preserve">こちらの興行会場に{orgName}の関係者が姿を見せ、「リングで語り合おう」と挑戦状を突きつけてきた。</t>
         </is>
       </c>
     </row>
     <row r="259" ht="40" customHeight="1">
       <c r="A259" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.relationship_repair.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].text</t>
         </is>
       </c>
       <c r="B259" t="inlineStr" s="2">
@@ -7515,24 +7205,24 @@
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">relationship_repair.effectSummary</t>
+          <t xml:space="preserve">B4.youngStar[1].text</t>
         </is>
       </c>
       <c r="G259" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">成功時、双方向 bond +5〜+10。失敗時は据え置き。</t>
+          <t xml:space="preserve">📺 {outletName}から若手特集の申し入れ</t>
         </is>
       </c>
     </row>
     <row r="260" ht="40" customHeight="1">
       <c r="A260" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.relationship_repair.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].detail</t>
         </is>
       </c>
       <c r="B260" t="inlineStr" s="2">
@@ -7542,24 +7232,24 @@
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">relationship_repair.recommendation</t>
+          <t xml:space="preserve">B4.youngStar[1].detail</t>
         </is>
       </c>
       <c r="G260" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">W-1（憎い敵ゾーン）が累計4回以上発火したペアに対して使用できる。慢性化する前に手を打てば、亀裂が修復可能になることもある。</t>
+          <t xml:space="preserve">{outletName}が「次世代のスターを追いかけたい」と密着取材を申し出ている。</t>
         </is>
       </c>
     </row>
     <row r="261" ht="40" customHeight="1">
       <c r="A261" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.faction_decree.label</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].text</t>
         </is>
       </c>
       <c r="B261" t="inlineStr" s="2">
@@ -7569,24 +7259,24 @@
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.label</t>
+          <t xml:space="preserve">B4.youngStar[2].text</t>
         </is>
       </c>
       <c r="G261" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">派閥解散命令</t>
+          <t xml:space="preserve">📺 {outletName}が注目の新星を追いたいと打診</t>
         </is>
       </c>
     </row>
     <row r="262" ht="40" customHeight="1">
       <c r="A262" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.faction_decree.categoryLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].detail</t>
         </is>
       </c>
       <c r="B262" t="inlineStr" s="2">
@@ -7596,24 +7286,24 @@
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D262" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.categoryLabel</t>
+          <t xml:space="preserve">B4.youngStar[2].detail</t>
         </is>
       </c>
       <c r="G262" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">人事</t>
+          <t xml:space="preserve">{outletName}のディレクターが「若い才能に密着したい」と話を持ちかけてきた。</t>
         </is>
       </c>
     </row>
     <row r="263" ht="40" customHeight="1">
       <c r="A263" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.faction_decree.body</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].text</t>
         </is>
       </c>
       <c r="B263" t="inlineStr" s="2">
@@ -7623,24 +7313,24 @@
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D263" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.body</t>
+          <t xml:space="preserve">B4.youngStar[3].text</t>
         </is>
       </c>
       <c r="G263" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">団体内の派閥を社長命令で解散させ、以後の結成を認めるかどうかを決める</t>
+          <t xml:space="preserve">📺 {outletName}の「若手発掘」企画にうちの選手が候補に</t>
         </is>
       </c>
     </row>
     <row r="264" ht="40" customHeight="1">
       <c r="A264" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.faction_decree.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].detail</t>
         </is>
       </c>
       <c r="B264" t="inlineStr" s="2">
@@ -7650,24 +7340,24 @@
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D264" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.detailText</t>
+          <t xml:space="preserve">B4.youngStar[3].detail</t>
         </is>
       </c>
       <c r="G264" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選手たちが自然に作った群れを、上から畳む。畳まれた側は当然おもしろくない。とくに束ねていた本人には深く残る。勢いに乗っていた派閥ほど、その傷は深い。</t>
+          <t xml:space="preserve">「プロレス界の未来を担う若手を追う」——{outletName}からそんな企画の依頼が来た。</t>
         </is>
       </c>
     </row>
     <row r="265" ht="40" customHeight="1">
       <c r="A265" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.faction_decree.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].text</t>
         </is>
       </c>
       <c r="B265" t="inlineStr" s="2">
@@ -7677,24 +7367,24 @@
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D265" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.effectSummary</t>
+          <t xml:space="preserve">B4.ace[1].text</t>
         </is>
       </c>
       <c r="G265" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">選択した内容によって、解散のみ／解散して以後禁止／禁止の解除 が実行される</t>
+          <t xml:space="preserve">📺 {outletName}がエース密着企画を提案</t>
         </is>
       </c>
     </row>
     <row r="266" ht="40" customHeight="1">
       <c r="A266" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.faction_decree.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].detail</t>
         </is>
       </c>
       <c r="B266" t="inlineStr" s="2">
@@ -7704,24 +7394,24 @@
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D266" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">faction_decree.recommendation</t>
+          <t xml:space="preserve">B4.ace[1].detail</t>
         </is>
       </c>
       <c r="G266" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">派閥の揉め事を団体から切り離したいときに。まだ派閥が生まれていないうちに禁止しておけば、誰の信頼も損なわずに済む。</t>
+          <t xml:space="preserve">{outletName}が「団体の顔に密着したい」とドキュメンタリー企画を持ち込んできた。</t>
         </is>
       </c>
     </row>
     <row r="267" ht="40" customHeight="1">
       <c r="A267" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.label</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].text</t>
         </is>
       </c>
       <c r="B267" t="inlineStr" s="2">
@@ -7731,24 +7421,24 @@
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D267" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.label</t>
+          <t xml:space="preserve">B4.ace[2].text</t>
         </is>
       </c>
       <c r="G267" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コーチ雇用決裁書</t>
+          <t xml:space="preserve">📺 {outletName}から「頂点の景色」取材オファー</t>
         </is>
       </c>
     </row>
     <row r="268" ht="40" customHeight="1">
       <c r="A268" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.categoryLabel</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].detail</t>
         </is>
       </c>
       <c r="B268" t="inlineStr" s="2">
@@ -7758,24 +7448,24 @@
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D268" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.categoryLabel</t>
+          <t xml:space="preserve">B4.ace[2].detail</t>
         </is>
       </c>
       <c r="G268" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">人事</t>
+          <t xml:space="preserve">{outletName}が「頂点に立つ選手の日常を追いたい」と密着取材を打診してきた。</t>
         </is>
       </c>
     </row>
     <row r="269" ht="40" customHeight="1">
       <c r="A269" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.body</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].text</t>
         </is>
       </c>
       <c r="B269" t="inlineStr" s="2">
@@ -7785,24 +7475,24 @@
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D269" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.body</t>
+          <t xml:space="preserve">B4.ace[3].text</t>
         </is>
       </c>
       <c r="G269" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新たなスタッフを招聘し、団体の指導体制を強化する</t>
+          <t xml:space="preserve">📺 {outletName}がトップ選手の特集を企画中</t>
         </is>
       </c>
     </row>
     <row r="270" ht="40" customHeight="1">
       <c r="A270" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.detailText</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].detail</t>
         </is>
       </c>
       <c r="B270" t="inlineStr" s="2">
@@ -7812,24 +7502,24 @@
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D270" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.detailText</t>
+          <t xml:space="preserve">B4.ace[3].detail</t>
         </is>
       </c>
       <c r="G270" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">新たなコーチを招聘し、指導体制を強化する。机には並ばず、コーチ画面から実行する特殊書類。</t>
+          <t xml:space="preserve">「団体を背負うエースに迫る」——{outletName}からそんなオファーが届いた。推薦する選手を選んでほしいという。</t>
         </is>
       </c>
     </row>
     <row r="271" ht="40" customHeight="1">
       <c r="A271" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.effectSummary</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].text</t>
         </is>
       </c>
       <c r="B271" t="inlineStr" s="2">
@@ -7839,24 +7529,24 @@
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D271" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.effectSummary</t>
+          <t xml:space="preserve">B4.veteran[1].text</t>
         </is>
       </c>
       <c r="G271" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コーチを1名新しく迎える(決裁枠を2消費)</t>
+          <t xml:space="preserve">📺 {outletName}がベテラン特集を企画</t>
         </is>
       </c>
     </row>
     <row r="272" ht="40" customHeight="1">
       <c r="A272" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">DECISION_DOCS.hireCoach.recommendation</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].detail</t>
         </is>
       </c>
       <c r="B272" t="inlineStr" s="2">
@@ -7866,24 +7556,24 @@
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">DECISION_DOCS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D272" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">hireCoach.recommendation</t>
+          <t xml:space="preserve">B4.veteran[1].detail</t>
         </is>
       </c>
       <c r="G272" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">コーチ枠に空きがあり、新規雇用を検討している週に。机に書類として表示されない点に注意。</t>
+          <t xml:space="preserve">{outletName}が「長く戦い続ける選手の矜持に迫りたい」と密着取材を申し出ている。</t>
         </is>
       </c>
     </row>
     <row r="273" ht="40" customHeight="1">
       <c r="A273" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].text</t>
         </is>
       </c>
       <c r="B273" t="inlineStr" s="2">
@@ -7893,24 +7583,24 @@
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D273" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">B4.veteran[2].text</t>
         </is>
       </c>
       <c r="G273" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">無難な線です。ただ、響くかどうかは相手次第かと。</t>
+          <t xml:space="preserve">📺 {outletName}から「キャリアの深み」取材依頼</t>
         </is>
       </c>
     </row>
     <row r="274" ht="40" customHeight="1">
       <c r="A274" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].detail</t>
         </is>
       </c>
       <c r="B274" t="inlineStr" s="2">
@@ -7920,24 +7610,24 @@
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D274" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">B4.veteran[2].detail</t>
         </is>
       </c>
       <c r="G274" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">彼女の格に見合った額かと存じます。</t>
+          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「経験豊富な選手の素顔を追いたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="275" ht="40" customHeight="1">
       <c r="A275" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[3]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].text</t>
         </is>
       </c>
       <c r="B275" t="inlineStr" s="2">
@@ -7947,24 +7637,24 @@
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D275" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">B4.veteran[3].text</t>
         </is>
       </c>
       <c r="G275" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">相場を超えています。誠意は伝わるはずです。</t>
+          <t xml:space="preserve">📺 {outletName}が「円熟の技」ドキュメントを提案</t>
         </is>
       </c>
     </row>
     <row r="276" ht="40" customHeight="1">
       <c r="A276" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS[4]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].detail</t>
         </is>
       </c>
       <c r="B276" t="inlineStr" s="2">
@@ -7974,24 +7664,24 @@
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D276" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">B4.veteran[3].detail</t>
         </is>
       </c>
       <c r="G276" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">……思い切りましたな。ここまで出す団体は他にありません。</t>
+          <t xml:space="preserve">「ベテランだからこそ見える景色がある」——{outletName}からそんなテーマの企画が持ち込まれた。</t>
         </is>
       </c>
     </row>
     <row r="277" ht="40" customHeight="1">
       <c r="A277" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[1]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].text</t>
         </is>
       </c>
       <c r="B277" t="inlineStr" s="2">
@@ -8001,24 +7691,24 @@
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D277" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[1]</t>
+          <t xml:space="preserve">B4_cm[1].text</t>
         </is>
       </c>
       <c r="G277" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}と{name2}が朝から激しいスパーリングを繰り広げている…！</t>
+          <t xml:space="preserve">📸 {outletName}からCM出演の打診</t>
         </is>
       </c>
     </row>
     <row r="278" ht="40" customHeight="1">
       <c r="A278" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[2]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].detail</t>
         </is>
       </c>
       <c r="B278" t="inlineStr" s="2">
@@ -8028,24 +7718,24 @@
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D278" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[2]</t>
+          <t xml:space="preserve">B4_cm[1].detail</t>
         </is>
       </c>
       <c r="G278" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">夜の自主練で{name1}が黙々とスクワットをしている…</t>
+          <t xml:space="preserve">{outletName}から「選手をCMの顔として起用したい」と打診が来た。</t>
         </is>
       </c>
     </row>
     <row r="279" ht="40" customHeight="1">
       <c r="A279" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[3]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].text</t>
         </is>
       </c>
       <c r="B279" t="inlineStr" s="2">
@@ -8055,24 +7745,24 @@
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[3]</t>
+          <t xml:space="preserve">B4_cm[2].text</t>
         </is>
       </c>
       <c r="G279" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}が{name2}に技の受け身を教えている場面が見られた</t>
+          <t xml:space="preserve">📸 {outletName}がCMキャストを探している</t>
         </is>
       </c>
     </row>
     <row r="280" ht="40" customHeight="1">
       <c r="A280" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[4]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].detail</t>
         </is>
       </c>
       <c r="B280" t="inlineStr" s="2">
@@ -8082,24 +7772,24 @@
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D280" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[4]</t>
+          <t xml:space="preserve">B4_cm[2].detail</t>
         </is>
       </c>
       <c r="G280" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合宿の食事は{name1}が率先して準備していた</t>
+          <t xml:space="preserve">「プロレスラーのカッコよさをCMで表現したい」——{outletName}からそんな依頼が届いた。</t>
         </is>
       </c>
     </row>
     <row r="281" ht="40" customHeight="1">
       <c r="A281" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[5]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].text</t>
         </is>
       </c>
       <c r="B281" t="inlineStr" s="2">
@@ -8109,24 +7799,24 @@
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D281" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[5]</t>
+          <t xml:space="preserve">B4_cm[3].text</t>
         </is>
       </c>
       <c r="G281" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}と{name2}が夕食後のランニングで競い合っている</t>
+          <t xml:space="preserve">📸 {outletName}のCM出演オファー</t>
         </is>
       </c>
     </row>
     <row r="282" ht="40" customHeight="1">
       <c r="A282" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[6]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].detail</t>
         </is>
       </c>
       <c r="B282" t="inlineStr" s="2">
@@ -8136,24 +7826,24 @@
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D282" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[6]</t>
+          <t xml:space="preserve">B4_cm[3].detail</t>
         </is>
       </c>
       <c r="G282" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">早朝の海辺で{name1}が一人、基礎練習に励んでいた</t>
+          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「うちの団体の選手を広告塔に使いたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="283" ht="40" customHeight="1">
       <c r="A283" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[7]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].text</t>
         </is>
       </c>
       <c r="B283" t="inlineStr" s="2">
@@ -8163,24 +7853,24 @@
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D283" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[7]</t>
+          <t xml:space="preserve">B4_gravure[1].text</t>
         </is>
       </c>
       <c r="G283" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}が新技の研究に没頭している姿が印象的だった</t>
+          <t xml:space="preserve">📷 {outletName}からグラビア撮影の依頼</t>
         </is>
       </c>
     </row>
     <row r="284" ht="40" customHeight="1">
       <c r="A284" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[8]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].detail</t>
         </is>
       </c>
       <c r="B284" t="inlineStr" s="2">
@@ -8190,24 +7880,24 @@
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D284" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[8]</t>
+          <t xml:space="preserve">B4_gravure[1].detail</t>
         </is>
       </c>
       <c r="G284" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">消灯後も{name1}と{name2}がリングで語り合っていた</t>
+          <t xml:space="preserve">{outletName}が「プロレスラーの魅力をグラビアで届けたい」と申し出てきた。</t>
         </is>
       </c>
     </row>
     <row r="285" ht="40" customHeight="1">
       <c r="A285" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[9]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].text</t>
         </is>
       </c>
       <c r="B285" t="inlineStr" s="2">
@@ -8217,24 +7907,24 @@
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D285" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[9]</t>
+          <t xml:space="preserve">B4_gravure[2].text</t>
         </is>
       </c>
       <c r="G285" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}が合宿の記念写真を撮ろうとみんなを集めていた</t>
+          <t xml:space="preserve">📷 {outletName}がグラビア特集企画を検討</t>
         </is>
       </c>
     </row>
     <row r="286" ht="40" customHeight="1">
       <c r="A286" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[10]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].detail</t>
         </is>
       </c>
       <c r="B286" t="inlineStr" s="2">
@@ -8244,24 +7934,24 @@
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D286" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[10]</t>
+          <t xml:space="preserve">B4_gravure[2].detail</t>
         </is>
       </c>
       <c r="G286" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">全員で浜辺を走るメニューに{name1}が一番乗りでゴールした</t>
+          <t xml:space="preserve">「女子プロレスラーの素顔に迫りたい」——{outletName}からそんな企画の打診が来た。</t>
         </is>
       </c>
     </row>
     <row r="287" ht="40" customHeight="1">
       <c r="A287" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[11]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].text</t>
         </is>
       </c>
       <c r="B287" t="inlineStr" s="2">
@@ -8271,24 +7961,24 @@
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D287" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[11]</t>
+          <t xml:space="preserve">B4_gravure[3].text</t>
         </is>
       </c>
       <c r="G287" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}のムードメーカーぶりで合宿の雰囲気がぐっと明るくなった</t>
+          <t xml:space="preserve">📷 {outletName}からグラビア出演のオファー</t>
         </is>
       </c>
     </row>
     <row r="288" ht="40" customHeight="1">
       <c r="A288" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS[12]</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].detail</t>
         </is>
       </c>
       <c r="B288" t="inlineStr" s="2">
@@ -8298,24 +7988,24 @@
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
       <c r="D288" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">[12]</t>
+          <t xml:space="preserve">B4_gravure[3].detail</t>
         </is>
       </c>
       <c r="G288" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習後の大浴場で{name1}と{name2}が今後の抱負を語り合っていた</t>
+          <t xml:space="preserve">{outletName}の編集長から直接連絡が入った。「ぜひ選手を誌面に起用したい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="289" ht="40" customHeight="1">
       <c r="A289" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].text</t>
         </is>
       </c>
       <c r="B289" t="inlineStr" s="2">
@@ -8330,19 +8020,19 @@
       </c>
       <c r="D289" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[1].text</t>
+          <t xml:space="preserve">B4_variety[1].text</t>
         </is>
       </c>
       <c r="G289" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}が練習中にアクシデント</t>
+          <t xml:space="preserve">📺 {outletName}からバラエティ出演のオファー</t>
         </is>
       </c>
     </row>
     <row r="290" ht="40" customHeight="1">
       <c r="A290" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].detail</t>
         </is>
       </c>
       <c r="B290" t="inlineStr" s="2">
@@ -8357,19 +8047,19 @@
       </c>
       <c r="D290" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[1].detail</t>
+          <t xml:space="preserve">B4_variety[1].detail</t>
         </is>
       </c>
       <c r="G290" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が練習中に技を受けた際にバランスを崩し、負傷してしまった。</t>
+          <t xml:space="preserve">{outletName}が「プロレスラーがゲスト出演するコーナーを作りたい」と打診してきた。</t>
         </is>
       </c>
     </row>
     <row r="291" ht="40" customHeight="1">
       <c r="A291" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].text</t>
         </is>
       </c>
       <c r="B291" t="inlineStr" s="2">
@@ -8384,19 +8074,19 @@
       </c>
       <c r="D291" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[2].text</t>
+          <t xml:space="preserve">B4_variety[2].text</t>
         </is>
       </c>
       <c r="G291" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}が練習で負傷</t>
+          <t xml:space="preserve">📺 {outletName}がゲスト出演の候補を探している</t>
         </is>
       </c>
     </row>
     <row r="292" ht="40" customHeight="1">
       <c r="A292" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].detail</t>
         </is>
       </c>
       <c r="B292" t="inlineStr" s="2">
@@ -8411,19 +8101,19 @@
       </c>
       <c r="D292" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[2].detail</t>
+          <t xml:space="preserve">B4_variety[2].detail</t>
         </is>
       </c>
       <c r="G292" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">スパーリング中に{name}が相手の技を受け損ね、マットに叩きつけられた。</t>
+          <t xml:space="preserve">「面白いキャラクターのプロレスラーを探している」——{outletName}からそんな依頼が届いた。</t>
         </is>
       </c>
     </row>
     <row r="293" ht="40" customHeight="1">
       <c r="A293" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].text</t>
         </is>
       </c>
       <c r="B293" t="inlineStr" s="2">
@@ -8438,19 +8128,19 @@
       </c>
       <c r="D293" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[3].text</t>
+          <t xml:space="preserve">B4_variety[3].text</t>
         </is>
       </c>
       <c r="G293" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}に練習中のトラブル</t>
+          <t xml:space="preserve">📺 {outletName}のトーク番組に出演依頼</t>
         </is>
       </c>
     </row>
     <row r="294" ht="40" customHeight="1">
       <c r="A294" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].detail</t>
         </is>
       </c>
       <c r="B294" t="inlineStr" s="2">
@@ -8465,19 +8155,19 @@
       </c>
       <c r="D294" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[3].detail</t>
+          <t xml:space="preserve">B4_variety[3].detail</t>
         </is>
       </c>
       <c r="G294" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name}が新技の練習中に着地に失敗。痛みを訴えている。</t>
+          <t xml:space="preserve">{outletName}のディレクターが来訪。「選手のキャラクターを全国に届けたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="295" ht="40" customHeight="1">
       <c r="A295" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].text</t>
         </is>
       </c>
       <c r="B295" t="inlineStr" s="2">
@@ -8492,19 +8182,19 @@
       </c>
       <c r="D295" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[4].text</t>
+          <t xml:space="preserve">B4_brand[1].text</t>
         </is>
       </c>
       <c r="G295" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}がロープワーク中に負傷</t>
+          <t xml:space="preserve">🤝 {outletName}からコラボ商品の提案</t>
         </is>
       </c>
     </row>
     <row r="296" ht="40" customHeight="1">
       <c r="A296" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[4].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].detail</t>
         </is>
       </c>
       <c r="B296" t="inlineStr" s="2">
@@ -8519,19 +8209,19 @@
       </c>
       <c r="D296" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[4].detail</t>
+          <t xml:space="preserve">B4_brand[1].detail</t>
         </is>
       </c>
       <c r="G296" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">ロープの反動を利用した連続技の練習中、{name}の足がロープに絡まり転倒。すぐには立ち上がれなかった。</t>
+          <t xml:space="preserve">{outletName}が「選手とのコラボ商品を作りたい」と申し出てきた。</t>
         </is>
       </c>
     </row>
     <row r="297" ht="40" customHeight="1">
       <c r="A297" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].text</t>
         </is>
       </c>
       <c r="B297" t="inlineStr" s="2">
@@ -8546,19 +8236,19 @@
       </c>
       <c r="D297" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[5].text</t>
+          <t xml:space="preserve">B4_brand[2].text</t>
         </is>
       </c>
       <c r="G297" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}がスパーリング中に痛みを訴えた</t>
+          <t xml:space="preserve">🤝 {outletName}がコラボパートナーを探している</t>
         </is>
       </c>
     </row>
     <row r="298" ht="40" customHeight="1">
       <c r="A298" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[5].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].detail</t>
         </is>
       </c>
       <c r="B298" t="inlineStr" s="2">
@@ -8573,19 +8263,19 @@
       </c>
       <c r="D298" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[5].detail</t>
+          <t xml:space="preserve">B4_brand[2].detail</t>
         </is>
       </c>
       <c r="G298" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習パートナーとのスパーリングで{name}が技を受けた直後、顔をしかめて膝をついた。本人は続けられると言うが…</t>
+          <t xml:space="preserve">「プロレスのパワーとブランドのスタイルを組み合わせたい」——{outletName}からそんな話が来た。</t>
         </is>
       </c>
     </row>
     <row r="299" ht="40" customHeight="1">
       <c r="A299" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].text</t>
         </is>
       </c>
       <c r="B299" t="inlineStr" s="2">
@@ -8600,19 +8290,19 @@
       </c>
       <c r="D299" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[6].text</t>
+          <t xml:space="preserve">B4_brand[3].text</t>
         </is>
       </c>
       <c r="G299" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚠️ {name}が練習後に体の異変を報告</t>
+          <t xml:space="preserve">🤝 {outletName}とのコラボ企画の打診</t>
         </is>
       </c>
     </row>
     <row r="300" ht="40" customHeight="1">
       <c r="A300" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B1[6].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].detail</t>
         </is>
       </c>
       <c r="B300" t="inlineStr" s="2">
@@ -8627,19 +8317,19 @@
       </c>
       <c r="D300" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B1[6].detail</t>
+          <t xml:space="preserve">B4_brand[3].detail</t>
         </is>
       </c>
       <c r="G300" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">練習を終えた{name}が、動かすと痛む箇所があると申告。無理をしていた可能性がある。</t>
+          <t xml:space="preserve">{outletName}の担当者が来訪。「選手のイメージを商品に落とし込みたい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="301" ht="40" customHeight="1">
       <c r="A301" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].text</t>
         </is>
       </c>
       <c r="B301" t="inlineStr" s="2">
@@ -8654,19 +8344,19 @@
       </c>
       <c r="D301" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[1].text</t>
+          <t xml:space="preserve">B4_fashion[1].text</t>
         </is>
       </c>
       <c r="G301" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}が衝突</t>
+          <t xml:space="preserve">👗 {outletName}のランウェイ出演オファー</t>
         </is>
       </c>
     </row>
     <row r="302" ht="40" customHeight="1">
       <c r="A302" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].detail</t>
         </is>
       </c>
       <c r="B302" t="inlineStr" s="2">
@@ -8681,19 +8371,19 @@
       </c>
       <c r="D302" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[1].detail</t>
+          <t xml:space="preserve">B4_fashion[1].detail</t>
         </is>
       </c>
       <c r="G302" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">控室で{name1}と{name2}の間に激しい口論が発生。周囲の制止も聞かず一触即発の状態になっている。</t>
+          <t xml:space="preserve">{outletName}が「アスリートのランウェイ参加を企画している」と打診してきた。</t>
         </is>
       </c>
     </row>
     <row r="303" ht="40" customHeight="1">
       <c r="A303" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].text</t>
         </is>
       </c>
       <c r="B303" t="inlineStr" s="2">
@@ -8708,19 +8398,19 @@
       </c>
       <c r="D303" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[2].text</t>
+          <t xml:space="preserve">B4_fashion[2].text</t>
         </is>
       </c>
       <c r="G303" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}の対立が深刻化</t>
+          <t xml:space="preserve">👗 {outletName}がファッションショー出演者を募集</t>
         </is>
       </c>
     </row>
     <row r="304" ht="40" customHeight="1">
       <c r="A304" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[2].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].detail</t>
         </is>
       </c>
       <c r="B304" t="inlineStr" s="2">
@@ -8735,19 +8425,19 @@
       </c>
       <c r="D304" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[2].detail</t>
+          <t xml:space="preserve">B4_fashion[2].detail</t>
         </is>
       </c>
       <c r="G304" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">以前から不穏な空気があった{name1}と{name2}の関係がついに破綻。練習にも支障が出始めている。</t>
+          <t xml:space="preserve">「プロレスラーの迫力をランウェイで表現したい」——{outletName}からそんな話が届いた。</t>
         </is>
       </c>
     </row>
     <row r="305" ht="40" customHeight="1">
       <c r="A305" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].text</t>
         </is>
       </c>
       <c r="B305" t="inlineStr" s="2">
@@ -8762,19 +8452,19 @@
       </c>
       <c r="D305" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[3].text</t>
+          <t xml:space="preserve">B4_fashion[3].text</t>
         </is>
       </c>
       <c r="G305" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}がスパーリングでエスカレート</t>
+          <t xml:space="preserve">👗 {outletName}のコレクションへの参加依頼</t>
         </is>
       </c>
     </row>
     <row r="306" ht="40" customHeight="1">
       <c r="A306" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[3].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].detail</t>
         </is>
       </c>
       <c r="B306" t="inlineStr" s="2">
@@ -8789,19 +8479,19 @@
       </c>
       <c r="D306" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[3].detail</t>
+          <t xml:space="preserve">B4_fashion[3].detail</t>
         </is>
       </c>
       <c r="G306" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">本来は軽い打ち合いのはずが、{name1}と{name2}のスパーリングが本気のぶつかり合いに発展。コーチが間に割って入る事態となった。</t>
+          <t xml:space="preserve">{outletName}のデザイナーが来訪。「ぜひ選手にランウェイを歩いてほしい」とのこと。</t>
         </is>
       </c>
     </row>
     <row r="307" ht="40" customHeight="1">
       <c r="A307" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].text</t>
         </is>
       </c>
       <c r="B307" t="inlineStr" s="2">
@@ -8816,19 +8506,19 @@
       </c>
       <c r="D307" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[4].text</t>
+          <t xml:space="preserve">B4_fan[1].text</t>
         </is>
       </c>
       <c r="G307" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}の間に亀裂</t>
+          <t xml:space="preserve">🎤 ファンイベント開催の打診</t>
         </is>
       </c>
     </row>
     <row r="308" ht="40" customHeight="1">
       <c r="A308" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[4].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].detail</t>
         </is>
       </c>
       <c r="B308" t="inlineStr" s="2">
@@ -8843,19 +8533,19 @@
       </c>
       <c r="D308" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[4].detail</t>
+          <t xml:space="preserve">B4_fan[1].detail</t>
         </is>
       </c>
       <c r="G308" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{name1}がSNSに意味深な投稿をしたことで{name2}が激怒。控室で怒鳴り合う二人の声が外まで漏れていた。</t>
+          <t xml:space="preserve">主催者から「選手とファンが直接交流できるイベントを開きたい」と相談が来た。</t>
         </is>
       </c>
     </row>
     <row r="309" ht="40" customHeight="1">
       <c r="A309" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].text</t>
         </is>
       </c>
       <c r="B309" t="inlineStr" s="2">
@@ -8870,19 +8560,19 @@
       </c>
       <c r="D309" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[5].text</t>
+          <t xml:space="preserve">B4_fan[2].text</t>
         </is>
       </c>
       <c r="G309" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">💥 {name1}と{name2}の関係が限界に</t>
+          <t xml:space="preserve">🎤 サイン会・トークショーの開催依頼</t>
         </is>
       </c>
     </row>
     <row r="310" ht="40" customHeight="1">
       <c r="A310" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B2[5].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].detail</t>
         </is>
       </c>
       <c r="B310" t="inlineStr" s="2">
@@ -8897,19 +8587,19 @@
       </c>
       <c r="D310" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B2[5].detail</t>
+          <t xml:space="preserve">B4_fan[2].detail</t>
         </is>
       </c>
       <c r="G310" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">合同練習中、{name1}が{name2}への不満を公然と口にした。全員の前での出来事に、チーム全体が凍りついた。</t>
+          <t xml:space="preserve">「ファンと選手が触れ合える機会を作りたい」——イベント会社からそんな提案が届いた。</t>
         </is>
       </c>
     </row>
     <row r="311" ht="40" customHeight="1">
       <c r="A311" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].text</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[3].text</t>
         </is>
       </c>
       <c r="B311" t="inlineStr" s="2">
@@ -8924,19 +8614,19 @@
       </c>
       <c r="D311" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[1].text</t>
+          <t xml:space="preserve">B4_fan[3].text</t>
         </is>
       </c>
       <c r="G311" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">⚔️ {orgName}から挑戦状</t>
+          <t xml:space="preserve">🎤 ファンミーティングの企画提案</t>
         </is>
       </c>
     </row>
     <row r="312" ht="40" customHeight="1">
       <c r="A312" t="inlineStr" s="15">
         <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[1].detail</t>
+          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[3].detail</t>
         </is>
       </c>
       <c r="B312" t="inlineStr" s="2">
@@ -8951,1691 +8641,17 @@
       </c>
       <c r="D312" t="inlineStr" s="12">
         <is>
-          <t xml:space="preserve">B3[1].detail</t>
+          <t xml:space="preserve">B4_fan[3].detail</t>
         </is>
       </c>
       <c r="G312" t="inlineStr" s="3">
         <is>
-          <t xml:space="preserve">{orgName}が「実力を見せてやる」と挑戦状を叩きつけてきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="313" ht="40" customHeight="1">
-      <c r="A313" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].text</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C313" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D313" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[2].text</t>
-        </is>
-      </c>
-      <c r="G313" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">⚔️ {orgName}が宣戦布告</t>
-        </is>
-      </c>
-    </row>
-    <row r="314" ht="40" customHeight="1">
-      <c r="A314" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[2].detail</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C314" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[2].detail</t>
-        </is>
-      </c>
-      <c r="G314" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{orgName}の代表が公の場でこちらの団体を挑発。挑戦状で決着をつけようと迫ってきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="315" ht="40" customHeight="1">
-      <c r="A315" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].text</t>
-        </is>
-      </c>
-      <c r="B315" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C315" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[3].text</t>
-        </is>
-      </c>
-      <c r="G315" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">⚔️ {orgName}の選手が記者会見で挑発</t>
-        </is>
-      </c>
-    </row>
-    <row r="316" ht="40" customHeight="1">
-      <c r="A316" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[3].detail</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C316" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D316" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[3].detail</t>
-        </is>
-      </c>
-      <c r="G316" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{orgName}の選手がメディアの前でこちらの団体名を出し、「いつでも受けて立つ」と公開挑戦状を叩きつけた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="317" ht="40" customHeight="1">
-      <c r="A317" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].text</t>
-        </is>
-      </c>
-      <c r="B317" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C317" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[4].text</t>
-        </is>
-      </c>
-      <c r="G317" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">⚔️ {orgName}から果たし状が届いた</t>
-        </is>
-      </c>
-    </row>
-    <row r="318" ht="40" customHeight="1">
-      <c r="A318" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[4].detail</t>
-        </is>
-      </c>
-      <c r="B318" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C318" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[4].detail</t>
-        </is>
-      </c>
-      <c r="G318" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{orgName}から正式な書面が届いた。「団体の威信をかけて一騎打ちを行いたい」——無視するわけにはいかない雰囲気だ。</t>
-        </is>
-      </c>
-    </row>
-    <row r="319" ht="40" customHeight="1">
-      <c r="A319" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].text</t>
-        </is>
-      </c>
-      <c r="B319" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C319" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D319" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[5].text</t>
-        </is>
-      </c>
-      <c r="G319" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">⚔️ {orgName}が興行に乗り込んできた</t>
-        </is>
-      </c>
-    </row>
-    <row r="320" ht="40" customHeight="1">
-      <c r="A320" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B3[5].detail</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B3[5].detail</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">こちらの興行会場に{orgName}の関係者が姿を見せ、「リングで語り合おう」と挑戦状を突きつけてきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="321" ht="40" customHeight="1">
-      <c r="A321" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].text</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.youngStar[1].text</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}から若手特集の申し入れ</t>
-        </is>
-      </c>
-    </row>
-    <row r="322" ht="40" customHeight="1">
-      <c r="A322" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[1].detail</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.youngStar[1].detail</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「次世代のスターを追いかけたい」と密着取材を申し出ている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="323" ht="40" customHeight="1">
-      <c r="A323" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].text</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.youngStar[2].text</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}が注目の新星を追いたいと打診</t>
-        </is>
-      </c>
-    </row>
-    <row r="324" ht="40" customHeight="1">
-      <c r="A324" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[2].detail</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.youngStar[2].detail</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}のディレクターが「若い才能に密着したい」と話を持ちかけてきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="325" ht="40" customHeight="1">
-      <c r="A325" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].text</t>
-        </is>
-      </c>
-      <c r="B325" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C325" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.youngStar[3].text</t>
-        </is>
-      </c>
-      <c r="G325" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}の「若手発掘」企画にうちの選手が候補に</t>
-        </is>
-      </c>
-    </row>
-    <row r="326" ht="40" customHeight="1">
-      <c r="A326" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.youngStar[3].detail</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C326" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.youngStar[3].detail</t>
-        </is>
-      </c>
-      <c r="G326" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「プロレス界の未来を担う若手を追う」——{outletName}からそんな企画の依頼が来た。</t>
-        </is>
-      </c>
-    </row>
-    <row r="327" ht="40" customHeight="1">
-      <c r="A327" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].text</t>
-        </is>
-      </c>
-      <c r="B327" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C327" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.ace[1].text</t>
-        </is>
-      </c>
-      <c r="G327" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}がエース密着企画を提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="328" ht="40" customHeight="1">
-      <c r="A328" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[1].detail</t>
-        </is>
-      </c>
-      <c r="B328" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C328" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.ace[1].detail</t>
-        </is>
-      </c>
-      <c r="G328" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「団体の顔に密着したい」とドキュメンタリー企画を持ち込んできた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="329" ht="40" customHeight="1">
-      <c r="A329" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].text</t>
-        </is>
-      </c>
-      <c r="B329" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C329" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.ace[2].text</t>
-        </is>
-      </c>
-      <c r="G329" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}から「頂点の景色」取材オファー</t>
-        </is>
-      </c>
-    </row>
-    <row r="330" ht="40" customHeight="1">
-      <c r="A330" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[2].detail</t>
-        </is>
-      </c>
-      <c r="B330" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C330" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.ace[2].detail</t>
-        </is>
-      </c>
-      <c r="G330" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「頂点に立つ選手の日常を追いたい」と密着取材を打診してきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="331" ht="40" customHeight="1">
-      <c r="A331" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].text</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C331" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.ace[3].text</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}がトップ選手の特集を企画中</t>
-        </is>
-      </c>
-    </row>
-    <row r="332" ht="40" customHeight="1">
-      <c r="A332" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.ace[3].detail</t>
-        </is>
-      </c>
-      <c r="B332" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C332" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.ace[3].detail</t>
-        </is>
-      </c>
-      <c r="G332" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「団体を背負うエースに迫る」——{outletName}からそんなオファーが届いた。推薦する選手を選んでほしいという。</t>
-        </is>
-      </c>
-    </row>
-    <row r="333" ht="40" customHeight="1">
-      <c r="A333" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].text</t>
-        </is>
-      </c>
-      <c r="B333" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C333" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.veteran[1].text</t>
-        </is>
-      </c>
-      <c r="G333" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}がベテラン特集を企画</t>
-        </is>
-      </c>
-    </row>
-    <row r="334" ht="40" customHeight="1">
-      <c r="A334" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[1].detail</t>
-        </is>
-      </c>
-      <c r="B334" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C334" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.veteran[1].detail</t>
-        </is>
-      </c>
-      <c r="G334" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「長く戦い続ける選手の矜持に迫りたい」と密着取材を申し出ている。</t>
-        </is>
-      </c>
-    </row>
-    <row r="335" ht="40" customHeight="1">
-      <c r="A335" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].text</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C335" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.veteran[2].text</t>
-        </is>
-      </c>
-      <c r="G335" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}から「キャリアの深み」取材依頼</t>
-        </is>
-      </c>
-    </row>
-    <row r="336" ht="40" customHeight="1">
-      <c r="A336" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[2].detail</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C336" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.veteran[2].detail</t>
-        </is>
-      </c>
-      <c r="G336" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「経験豊富な選手の素顔を追いたい」とのこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="337" ht="40" customHeight="1">
-      <c r="A337" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].text</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C337" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.veteran[3].text</t>
-        </is>
-      </c>
-      <c r="G337" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}が「円熟の技」ドキュメントを提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="338" ht="40" customHeight="1">
-      <c r="A338" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4.veteran[3].detail</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C338" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4.veteran[3].detail</t>
-        </is>
-      </c>
-      <c r="G338" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「ベテランだからこそ見える景色がある」——{outletName}からそんなテーマの企画が持ち込まれた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="339" ht="40" customHeight="1">
-      <c r="A339" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].text</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_cm[1].text</t>
-        </is>
-      </c>
-      <c r="G339" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📸 {outletName}からCM出演の打診</t>
-        </is>
-      </c>
-    </row>
-    <row r="340" ht="40" customHeight="1">
-      <c r="A340" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[1].detail</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C340" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_cm[1].detail</t>
-        </is>
-      </c>
-      <c r="G340" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}から「選手をCMの顔として起用したい」と打診が来た。</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" ht="40" customHeight="1">
-      <c r="A341" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].text</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C341" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_cm[2].text</t>
-        </is>
-      </c>
-      <c r="G341" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📸 {outletName}がCMキャストを探している</t>
-        </is>
-      </c>
-    </row>
-    <row r="342" ht="40" customHeight="1">
-      <c r="A342" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[2].detail</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C342" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_cm[2].detail</t>
-        </is>
-      </c>
-      <c r="G342" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「プロレスラーのカッコよさをCMで表現したい」——{outletName}からそんな依頼が届いた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="343" ht="40" customHeight="1">
-      <c r="A343" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].text</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C343" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_cm[3].text</t>
-        </is>
-      </c>
-      <c r="G343" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📸 {outletName}のCM出演オファー</t>
-        </is>
-      </c>
-    </row>
-    <row r="344" ht="40" customHeight="1">
-      <c r="A344" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_cm[3].detail</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C344" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_cm[3].detail</t>
-        </is>
-      </c>
-      <c r="G344" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}のプロデューサーが来訪。「うちの団体の選手を広告塔に使いたい」とのこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="345" ht="40" customHeight="1">
-      <c r="A345" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].text</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C345" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_gravure[1].text</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📷 {outletName}からグラビア撮影の依頼</t>
-        </is>
-      </c>
-    </row>
-    <row r="346" ht="40" customHeight="1">
-      <c r="A346" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[1].detail</t>
-        </is>
-      </c>
-      <c r="B346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C346" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_gravure[1].detail</t>
-        </is>
-      </c>
-      <c r="G346" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「プロレスラーの魅力をグラビアで届けたい」と申し出てきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="347" ht="40" customHeight="1">
-      <c r="A347" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].text</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C347" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_gravure[2].text</t>
-        </is>
-      </c>
-      <c r="G347" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📷 {outletName}がグラビア特集企画を検討</t>
-        </is>
-      </c>
-    </row>
-    <row r="348" ht="40" customHeight="1">
-      <c r="A348" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[2].detail</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C348" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_gravure[2].detail</t>
-        </is>
-      </c>
-      <c r="G348" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「女子プロレスラーの素顔に迫りたい」——{outletName}からそんな企画の打診が来た。</t>
-        </is>
-      </c>
-    </row>
-    <row r="349" ht="40" customHeight="1">
-      <c r="A349" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].text</t>
-        </is>
-      </c>
-      <c r="B349" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C349" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_gravure[3].text</t>
-        </is>
-      </c>
-      <c r="G349" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📷 {outletName}からグラビア出演のオファー</t>
-        </is>
-      </c>
-    </row>
-    <row r="350" ht="40" customHeight="1">
-      <c r="A350" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_gravure[3].detail</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C350" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_gravure[3].detail</t>
-        </is>
-      </c>
-      <c r="G350" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}の編集長から直接連絡が入った。「ぜひ選手を誌面に起用したい」とのこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="351" ht="40" customHeight="1">
-      <c r="A351" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].text</t>
-        </is>
-      </c>
-      <c r="B351" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C351" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_variety[1].text</t>
-        </is>
-      </c>
-      <c r="G351" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}からバラエティ出演のオファー</t>
-        </is>
-      </c>
-    </row>
-    <row r="352" ht="40" customHeight="1">
-      <c r="A352" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[1].detail</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C352" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_variety[1].detail</t>
-        </is>
-      </c>
-      <c r="G352" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「プロレスラーがゲスト出演するコーナーを作りたい」と打診してきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="353" ht="40" customHeight="1">
-      <c r="A353" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].text</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C353" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_variety[2].text</t>
-        </is>
-      </c>
-      <c r="G353" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}がゲスト出演の候補を探している</t>
-        </is>
-      </c>
-    </row>
-    <row r="354" ht="40" customHeight="1">
-      <c r="A354" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[2].detail</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C354" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_variety[2].detail</t>
-        </is>
-      </c>
-      <c r="G354" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「面白いキャラクターのプロレスラーを探している」——{outletName}からそんな依頼が届いた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="355" ht="40" customHeight="1">
-      <c r="A355" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].text</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C355" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_variety[3].text</t>
-        </is>
-      </c>
-      <c r="G355" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">📺 {outletName}のトーク番組に出演依頼</t>
-        </is>
-      </c>
-    </row>
-    <row r="356" ht="40" customHeight="1">
-      <c r="A356" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_variety[3].detail</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C356" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_variety[3].detail</t>
-        </is>
-      </c>
-      <c r="G356" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}のディレクターが来訪。「選手のキャラクターを全国に届けたい」とのこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="357" ht="40" customHeight="1">
-      <c r="A357" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].text</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_brand[1].text</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">🤝 {outletName}からコラボ商品の提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="358" ht="40" customHeight="1">
-      <c r="A358" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[1].detail</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_brand[1].detail</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「選手とのコラボ商品を作りたい」と申し出てきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="359" ht="40" customHeight="1">
-      <c r="A359" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].text</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C359" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_brand[2].text</t>
-        </is>
-      </c>
-      <c r="G359" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">🤝 {outletName}がコラボパートナーを探している</t>
-        </is>
-      </c>
-    </row>
-    <row r="360" ht="40" customHeight="1">
-      <c r="A360" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[2].detail</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C360" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_brand[2].detail</t>
-        </is>
-      </c>
-      <c r="G360" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「プロレスのパワーとブランドのスタイルを組み合わせたい」——{outletName}からそんな話が来た。</t>
-        </is>
-      </c>
-    </row>
-    <row r="361" ht="40" customHeight="1">
-      <c r="A361" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].text</t>
-        </is>
-      </c>
-      <c r="B361" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C361" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_brand[3].text</t>
-        </is>
-      </c>
-      <c r="G361" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">🤝 {outletName}とのコラボ企画の打診</t>
-        </is>
-      </c>
-    </row>
-    <row r="362" ht="40" customHeight="1">
-      <c r="A362" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_brand[3].detail</t>
-        </is>
-      </c>
-      <c r="B362" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C362" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_brand[3].detail</t>
-        </is>
-      </c>
-      <c r="G362" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}の担当者が来訪。「選手のイメージを商品に落とし込みたい」とのこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="363" ht="40" customHeight="1">
-      <c r="A363" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].text</t>
-        </is>
-      </c>
-      <c r="B363" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fashion[1].text</t>
-        </is>
-      </c>
-      <c r="G363" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">👗 {outletName}のランウェイ出演オファー</t>
-        </is>
-      </c>
-    </row>
-    <row r="364" ht="40" customHeight="1">
-      <c r="A364" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[1].detail</t>
-        </is>
-      </c>
-      <c r="B364" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C364" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fashion[1].detail</t>
-        </is>
-      </c>
-      <c r="G364" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}が「アスリートのランウェイ参加を企画している」と打診してきた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="365" ht="40" customHeight="1">
-      <c r="A365" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].text</t>
-        </is>
-      </c>
-      <c r="B365" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C365" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fashion[2].text</t>
-        </is>
-      </c>
-      <c r="G365" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">👗 {outletName}がファッションショー出演者を募集</t>
-        </is>
-      </c>
-    </row>
-    <row r="366" ht="40" customHeight="1">
-      <c r="A366" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[2].detail</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C366" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fashion[2].detail</t>
-        </is>
-      </c>
-      <c r="G366" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「プロレスラーの迫力をランウェイで表現したい」——{outletName}からそんな話が届いた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="367" ht="40" customHeight="1">
-      <c r="A367" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].text</t>
-        </is>
-      </c>
-      <c r="B367" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C367" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fashion[3].text</t>
-        </is>
-      </c>
-      <c r="G367" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">👗 {outletName}のコレクションへの参加依頼</t>
-        </is>
-      </c>
-    </row>
-    <row r="368" ht="40" customHeight="1">
-      <c r="A368" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fashion[3].detail</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C368" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fashion[3].detail</t>
-        </is>
-      </c>
-      <c r="G368" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">{outletName}のデザイナーが来訪。「ぜひ選手にランウェイを歩いてほしい」とのこと。</t>
-        </is>
-      </c>
-    </row>
-    <row r="369" ht="40" customHeight="1">
-      <c r="A369" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].text</t>
-        </is>
-      </c>
-      <c r="B369" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C369" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D369" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fan[1].text</t>
-        </is>
-      </c>
-      <c r="G369" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">🎤 ファンイベント開催の打診</t>
-        </is>
-      </c>
-    </row>
-    <row r="370" ht="40" customHeight="1">
-      <c r="A370" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[1].detail</t>
-        </is>
-      </c>
-      <c r="B370" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C370" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D370" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fan[1].detail</t>
-        </is>
-      </c>
-      <c r="G370" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">主催者から「選手とファンが直接交流できるイベントを開きたい」と相談が来た。</t>
-        </is>
-      </c>
-    </row>
-    <row r="371" ht="40" customHeight="1">
-      <c r="A371" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].text</t>
-        </is>
-      </c>
-      <c r="B371" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C371" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D371" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fan[2].text</t>
-        </is>
-      </c>
-      <c r="G371" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">🎤 サイン会・トークショーの開催依頼</t>
-        </is>
-      </c>
-    </row>
-    <row r="372" ht="40" customHeight="1">
-      <c r="A372" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[2].detail</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C372" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D372" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fan[2].detail</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">「ファンと選手が触れ合える機会を作りたい」——イベント会社からそんな提案が届いた。</t>
-        </is>
-      </c>
-    </row>
-    <row r="373" ht="40" customHeight="1">
-      <c r="A373" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[3].text</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C373" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D373" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fan[3].text</t>
-        </is>
-      </c>
-      <c r="G373" t="inlineStr" s="3">
-        <is>
-          <t xml:space="preserve">🎤 ファンミーティングの企画提案</t>
-        </is>
-      </c>
-    </row>
-    <row r="374" ht="40" customHeight="1">
-      <c r="A374" t="inlineStr" s="15">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS.B4_fan[3].detail</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">src/data.js</t>
-        </is>
-      </c>
-      <c r="C374" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr" s="12">
-        <is>
-          <t xml:space="preserve">B4_fan[3].detail</t>
-        </is>
-      </c>
-      <c r="G374" t="inlineStr" s="3">
-        <is>
           <t xml:space="preserve">「選手の素顔をファンに見せる場を作りたい」と主催者から打診があった。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I374"/>
+  <autoFilter ref="A1:I312"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>

--- a/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
+++ b/セリフ編集/ナレーション・記事/通知・スナップショット系.xlsx
@@ -192,18 +192,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I312"/>
+  <dimension ref="A1:J312"/>
   <sheetFormatPr defaultRowHeight="20"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="26" customWidth="1"/>
     <col min="6" max="6" width="10" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
     <col min="8" max="8" width="50" customWidth="1"/>
-    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="9" max="9" width="50" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -214,40 +215,45 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">カテゴリ</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">出典</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">テーブル</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">パス</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">archetype</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">personality</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">現在</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">改訂</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">備考</t>
         </is>
@@ -261,20 +267,25 @@
       </c>
       <c r="B2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr" s="12">
+      <c r="E2" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[1].text</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr" s="3">
+      <c r="H2" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💪 {name}が自主トレで手応えを掴んだ</t>
         </is>
@@ -288,20 +299,25 @@
       </c>
       <c r="B3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr" s="12">
+      <c r="E3" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[1].detail</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr" s="3">
+      <c r="H3" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が誰もいない道場で汗を流していた。基礎をひとつひとつ確認しながら、何度も繰り返す姿が印象的だ。</t>
         </is>
@@ -315,20 +331,25 @@
       </c>
       <c r="B4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr" s="12">
+      <c r="E4" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[2].text</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr" s="3">
+      <c r="H4" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🌟 {name}の努力が実を結びつつある</t>
         </is>
@@ -342,20 +363,25 @@
       </c>
       <c r="B5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr" s="12">
+      <c r="E5" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[2].detail</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr" s="3">
+      <c r="H5" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">毎朝の早出練習が続いている{name}。最近はスパーリング相手からも「動きが変わった」と言われることが増えてきた。</t>
         </is>
@@ -369,20 +395,25 @@
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr" s="12">
+      <c r="E6" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[3].text</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr" s="3">
+      <c r="H6" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">✨ {name}が練習で目を引く動きを見せた</t>
         </is>
@@ -396,20 +427,25 @@
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr" s="12">
+      <c r="E7" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[3].detail</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr" s="3">
+      <c r="H7" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今日の合同練習で、{name}が以前はできなかった動きを難なくこなしてみせた。コーチも思わず足を止めて見入っていた。</t>
         </is>
@@ -423,20 +459,25 @@
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr" s="12">
+      <c r="E8" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[4].text</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr" s="3">
+      <c r="H8" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📈 {name}の動きが明らかに良くなっている</t>
         </is>
@@ -450,20 +491,25 @@
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr" s="12">
+      <c r="E9" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[4].detail</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr" s="3">
+      <c r="H9" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">先月の試合映像と見比べると、{name}の動作に無駄がなくなっているのが分かる。地道な積み重ねが形になってきた。</t>
         </is>
@@ -477,20 +523,25 @@
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr" s="12">
+      <c r="E10" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[5].text</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr" s="3">
+      <c r="H10" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🏋️ {name}がフィジカルトレーニングで成果を見せた</t>
         </is>
@@ -504,20 +555,25 @@
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr" s="12">
+      <c r="E11" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[5].detail</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr" s="3">
+      <c r="H11" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が自主的に取り組んでいる体幹トレーニングの効果が出始めている。受け身の安定感が格段に上がった。</t>
         </is>
@@ -531,20 +587,25 @@
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr" s="12">
+      <c r="E12" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[6].text</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr" s="3">
+      <c r="H12" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🎯 {name}が技の精度を上げてきた</t>
         </is>
@@ -558,20 +619,25 @@
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr" s="12">
+      <c r="E13" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N1[6].detail</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr" s="3">
+      <c r="H13" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">繰り返し練習してきた連携技が、{name}の体に馴染んできたようだ。実戦でも使えるレベルに仕上がりつつある。</t>
         </is>
@@ -585,20 +651,25 @@
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr" s="12">
+      <c r="E14" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[1].text</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr" s="3">
+      <c r="H14" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🤝 {name}と{name2}が練習後に話し込んでいた</t>
         </is>
@@ -612,20 +683,25 @@
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr" s="12">
+      <c r="E15" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[1].detail</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr" s="3">
+      <c r="H15" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習が終わってもロッカールームを離れようとしない二人。お互いの技や試合のことを真剣に語り合っているようだった。</t>
         </is>
@@ -639,20 +715,25 @@
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr" s="12">
+      <c r="E16" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[2].text</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr" s="3">
+      <c r="H16" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💬 {name}が{name2}に技のコツを教えていた</t>
         </is>
@@ -666,20 +747,25 @@
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr" s="12">
+      <c r="E17" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[2].detail</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr" s="3">
+      <c r="H17" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習後、{name}が{name2}の動きを見て自ら声をかけた。2時間近く付き合って、丁寧に手ほどきしていたそうだ。</t>
         </is>
@@ -693,20 +779,25 @@
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr" s="12">
+      <c r="E18" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[3].text</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr" s="3">
+      <c r="H18" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🌸 {name}と{name2}の仲が深まってきた</t>
         </is>
@@ -720,20 +811,25 @@
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr" s="12">
+      <c r="E19" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[3].detail</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr" s="3">
+      <c r="H19" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最近、{name}と{name2}がよく行動を共にしているのが目につく。ランチを一緒にとったり、移動中も話し合っていることが増えた。</t>
         </is>
@@ -747,20 +843,25 @@
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr" s="12">
+      <c r="E20" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[4].text</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr" s="3">
+      <c r="H20" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👊 {name}と{name2}が激しく語り合っていた</t>
         </is>
@@ -774,20 +875,25 @@
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr" s="12">
+      <c r="E21" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[4].detail</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr" s="3">
+      <c r="H21" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">プロレスの哲学について、{name}と{name2}が火花を散らすような議論を繰り広げた。二人とも目を輝かせていた。</t>
         </is>
@@ -801,20 +907,25 @@
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr" s="12">
+      <c r="E22" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[5].text</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr" s="3">
+      <c r="H22" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🍙 {name}と{name2}が一緒に食事をとっていた</t>
         </is>
@@ -828,20 +939,25 @@
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr" s="12">
+      <c r="E23" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[5].detail</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr" s="3">
+      <c r="H23" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習後、{name}と{name2}が近所の定食屋で向かい合って談笑している姿が目撃された。チームの結束が深まっているようだ。</t>
         </is>
@@ -855,20 +971,25 @@
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr" s="12">
+      <c r="E24" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[6].text</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr" s="3">
+      <c r="H24" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🤜 {name}と{name2}が互いを高め合っている</t>
         </is>
@@ -882,20 +1003,25 @@
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr" s="12">
+      <c r="E25" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N2[6].detail</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr" s="3">
+      <c r="H25" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が自主的にスパーリングを重ねている。好敵手として切磋琢磨する関係が生まれつつある。</t>
         </is>
@@ -909,20 +1035,25 @@
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr" s="12">
+      <c r="E26" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[1].text</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr" s="3">
+      <c r="H26" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😓 {name}が少し疲れ気味のようだ…</t>
         </is>
@@ -936,20 +1067,25 @@
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr" s="12">
+      <c r="E27" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[1].detail</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr" s="3">
+      <c r="H27" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">試合が続いたせいか、{name}の動きにいつもの切れが見られない。練習後もすぐに休むことが多くなっている。</t>
         </is>
@@ -963,20 +1099,25 @@
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr" s="12">
+      <c r="E28" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[2].text</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr" s="3">
+      <c r="H28" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🌡️ {name}のコンディションが優れない</t>
         </is>
@@ -990,20 +1131,25 @@
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr" s="12">
+      <c r="E29" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[2].detail</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr" s="3">
+      <c r="H29" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が今週の練習を短縮するよう申し出た。本人は問題ないと言っているが、顔色が優れないのが気になる。</t>
         </is>
@@ -1017,20 +1163,25 @@
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr" s="12">
+      <c r="E30" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[3].text</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr" s="3">
+      <c r="H30" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💤 {name}の練習に覇気がない日があった</t>
         </is>
@@ -1044,20 +1195,25 @@
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr" s="12">
+      <c r="E31" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[3].detail</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr" s="3">
+      <c r="H31" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今日の{name}はルーティンをこなしているだけといった印象で、いつもの集中力がなかった。疲れか、それとも悩みがあるのか。</t>
         </is>
@@ -1071,20 +1227,25 @@
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr" s="12">
+      <c r="E32" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[4].text</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr" s="3">
+      <c r="H32" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😔 {name}が練習量を落としているようだ</t>
         </is>
@@ -1098,20 +1259,25 @@
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr" s="12">
+      <c r="E33" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[4].detail</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr" s="3">
+      <c r="H33" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">先月と比べると、{name}の練習時間が目に見えて減っている。怪我を抱えているわけではないだけに、少し心配だ。</t>
         </is>
@@ -1125,20 +1291,25 @@
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr" s="12">
+      <c r="E34" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[5].text</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr" s="3">
+      <c r="H34" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😩 {name}が連戦の疲れを引きずっている</t>
         </is>
@@ -1152,20 +1323,25 @@
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr" s="12">
+      <c r="E35" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[5].detail</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr" s="3">
+      <c r="H35" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最近の連戦のダメージが{name}の体に残っているようだ。練習でも動きが鈍く、いつもの切れ味がない。</t>
         </is>
@@ -1179,20 +1355,25 @@
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr" s="12">
+      <c r="E36" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[6].text</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr" s="3">
+      <c r="H36" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🩹 {name}の体に疲労が溜まっているようだ</t>
         </is>
@@ -1206,20 +1387,25 @@
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr" s="12">
+      <c r="E37" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N3[6].detail</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr" s="3">
+      <c r="H37" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習後に{name}がストレッチに普段の倍の時間をかけていた。本人は何も言わないが、体が悲鳴を上げているのかもしれない。</t>
         </is>
@@ -1233,20 +1419,25 @@
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr" s="12">
+      <c r="E38" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[1].text</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr" s="3">
+      <c r="H38" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📣 ファンから{name}への応援の声が増えている！</t>
         </is>
@@ -1260,20 +1451,25 @@
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr" s="12">
+      <c r="E39" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[1].detail</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr" s="3">
+      <c r="H39" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">会場の外でも{name}を待つファンの姿が増えてきた。試合を見て初めてプロレスを好きになったと語るファンも現れはじめている。</t>
         </is>
@@ -1287,20 +1483,25 @@
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr" s="12">
+      <c r="E40" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[2].text</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr" s="3">
+      <c r="H40" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🎉 SNSで{name}が話題になっている！</t>
         </is>
@@ -1314,20 +1515,25 @@
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr" s="12">
+      <c r="E41" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[2].detail</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr" s="3">
+      <c r="H41" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">先週の試合でのハイライトが拡散されて、{name}のSNSフォロワー数が急増している。知名度が着実に上がってきた。</t>
         </is>
@@ -1341,20 +1547,25 @@
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr" s="12">
+      <c r="E42" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[3].text</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr" s="3">
+      <c r="H42" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💖 {name}目当てのファンが増えてきた！</t>
         </is>
@@ -1368,20 +1579,25 @@
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr" s="12">
+      <c r="E43" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[3].detail</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr" s="3">
+      <c r="H43" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">チケット購入時に「{name}が見たくて来た」と声に出してくれるファンが増えている。地道に積み重ねてきた試合が実を結んでいる。</t>
         </is>
@@ -1395,20 +1611,25 @@
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr" s="12">
+      <c r="E44" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[4].text</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr" s="3">
+      <c r="H44" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🔥 {name}の人気が上り調子だ！</t>
         </is>
@@ -1422,20 +1643,25 @@
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr" s="12">
+      <c r="E45" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[4].detail</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr" s="3">
+      <c r="H45" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">観客の入りを見ていると、{name}が出る試合は明らかに人が多い。ファンが友人を誘って来場するというケースも報告されている。</t>
         </is>
@@ -1449,20 +1675,25 @@
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr" s="12">
+      <c r="E46" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[5].text</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr" s="3">
+      <c r="H46" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🛍️ {name}のグッズが売れ行き好調！</t>
         </is>
@@ -1476,20 +1707,25 @@
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr" s="12">
+      <c r="E47" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[5].detail</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr" s="3">
+      <c r="H47" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}のTシャツやタオルが会場で飛ぶように売れている。追加発注を検討してもいいかもしれない。</t>
         </is>
@@ -1503,20 +1739,25 @@
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr" s="12">
+      <c r="E48" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[6].text</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr" s="3">
+      <c r="H48" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📱 {name}のファンアートがSNSで拡散中！</t>
         </is>
@@ -1530,20 +1771,25 @@
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr" s="12">
+      <c r="E49" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N4[6].detail</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr" s="3">
+      <c r="H49" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ファンが{name}のイラストや応援動画をSNSに投稿し、それが大きな話題を呼んでいる。知名度がじわじわと上昇中だ。</t>
         </is>
@@ -1557,20 +1803,25 @@
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr" s="12">
+      <c r="E50" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[1].text</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr" s="3">
+      <c r="H50" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😶 {name}が最近どことなく元気がないようだ…</t>
         </is>
@@ -1584,20 +1835,25 @@
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr" s="12">
+      <c r="E51" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[1].detail</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr" s="3">
+      <c r="H51" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">いつもは積極的に話しかけてくる{name}が、最近は静かに練習をこなして帰るだけになっている。何か気になることがあるのかもしれない。</t>
         </is>
@@ -1611,20 +1867,25 @@
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr" s="12">
+      <c r="E52" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[2].text</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr" s="3">
+      <c r="H52" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💭 {name}の様子が少し気になる</t>
         </is>
@@ -1638,20 +1899,25 @@
       </c>
       <c r="B53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C53" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr" s="12">
+      <c r="E53" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[2].detail</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr" s="3">
+      <c r="H53" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習中の{name}の目が、どこか遠くを見ているような瞬間が増えた。試合への集中は保てているが、何かを抱えているように見える。</t>
         </is>
@@ -1665,20 +1931,25 @@
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr" s="12">
+      <c r="E54" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[3].text</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr" s="3">
+      <c r="H54" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🤔 {name}が浮かない顔をしていた</t>
         </is>
@@ -1692,20 +1963,25 @@
       </c>
       <c r="B55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C55" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr" s="12">
+      <c r="E55" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[3].detail</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr" s="3">
+      <c r="H55" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今日の{name}は朝から表情が暗かった。何か聞こうとしたが、やんわりと遮られてしまった。様子を見ておく必要がありそうだ。</t>
         </is>
@@ -1719,20 +1995,25 @@
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr" s="12">
+      <c r="E56" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[4].text</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr" s="3">
+      <c r="H56" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😑 {name}が練習中に何かを考えているようだった</t>
         </is>
@@ -1746,20 +2027,25 @@
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr" s="12">
+      <c r="E57" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[4].detail</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr" s="3">
+      <c r="H57" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スパーリング中に{name}が一瞬だけ動きを止めることがあった。何か重いものを抱えているように見えた。</t>
         </is>
@@ -1773,20 +2059,25 @@
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr" s="12">
+      <c r="E58" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[5].text</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr" s="3">
+      <c r="H58" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🫥 {name}が自主練を欠席する日があった</t>
         </is>
@@ -1800,20 +2091,25 @@
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr" s="12">
+      <c r="E59" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[5].detail</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr" s="3">
+      <c r="H59" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">以前は必ず参加していた自主練に{name}が来なかった。体調不良ではないらしいが…声をかけてみるか、ケアアクションで気にかけてみてもいいかもしれない。</t>
         </is>
@@ -1827,20 +2123,25 @@
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr" s="12">
+      <c r="E60" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[6].text</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr" s="3">
+      <c r="H60" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😐 {name}がチームメイトと距離を置き始めた</t>
         </is>
@@ -1854,20 +2155,25 @@
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr" s="12">
+      <c r="E61" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_warning[6].detail</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr" s="3">
+      <c r="H61" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が休憩時間に一人で過ごすことが増えた。まだ深刻な段階ではなさそうだが、試合に出して活躍の場を作ることで変わるかもしれない。</t>
         </is>
@@ -1881,20 +2187,25 @@
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr" s="12">
+      <c r="E62" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[1].text</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr" s="3">
+      <c r="H62" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😤 {name}が最近不満そうにしている…</t>
         </is>
@@ -1908,20 +2219,25 @@
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr" s="12">
+      <c r="E63" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[1].detail</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr" s="3">
+      <c r="H63" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習後のミーティングで、{name}の受け答えがぶっきらぼうになってきた。チームとの何らかの摩擦が生じているかもしれない。</t>
         </is>
@@ -1935,20 +2251,25 @@
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr" s="12">
+      <c r="E64" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[2].text</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr" s="3">
+      <c r="H64" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😟 {name}から笑顔が消えてきた気がする</t>
         </is>
@@ -1962,20 +2283,25 @@
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr" s="12">
+      <c r="E65" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[2].detail</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr" s="3">
+      <c r="H65" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">以前は練習後もチームメイトと談笑していた{name}が、最近は黙って着替えて帰ることが増えた。チームの雰囲気にも影響が出てきそうだ。</t>
         </is>
@@ -1989,20 +2315,25 @@
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr" s="12">
+      <c r="E66" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[3].text</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr" s="3">
+      <c r="H66" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💢 {name}が何かに苛立っている様子だ</t>
         </is>
@@ -2016,20 +2347,25 @@
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr" s="12">
+      <c r="E67" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[3].detail</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr" s="3">
+      <c r="H67" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">小さなことで感情が出やすくなっている{name}。直接の原因は不明だが、現状への不満が積み重なっているようだ。早めに話を聞いた方がいいかもしれない。</t>
         </is>
@@ -2043,20 +2379,25 @@
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr" s="12">
+      <c r="E68" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[4].text</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr" s="3">
+      <c r="H68" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😶‍🌫️ {name}…大丈夫だろうか</t>
         </is>
@@ -2070,20 +2411,25 @@
       </c>
       <c r="B69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C69" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr" s="12">
+      <c r="E69" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[4].detail</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr" s="3">
+      <c r="H69" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">最近の{name}は何を考えているのか読めない。返事はするが目が合わない、笑顔が一切見られない——チームの誰もが心配している。</t>
         </is>
@@ -2097,20 +2443,25 @@
       </c>
       <c r="B70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C70" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr" s="12">
+      <c r="E70" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[5].text</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr" s="3">
+      <c r="H70" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🚪 {name}が一人で練習場を出ていった</t>
         </is>
@@ -2124,20 +2475,25 @@
       </c>
       <c r="B71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C71" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr" s="12">
+      <c r="E71" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[5].detail</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr" s="3">
+      <c r="H71" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">全体練習の終了前に、{name}が黙って荷物をまとめて帰っていった。ケアアクションでボーナスを支給するか、試合で活躍の場を与えることで状況を改善できるかもしれない。</t>
         </is>
@@ -2151,20 +2507,25 @@
       </c>
       <c r="B72" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C72" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr" s="12">
+      <c r="E72" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[6].text</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr" s="3">
+      <c r="H72" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚡ {name}の態度にチーム内でも不安の声が</t>
         </is>
@@ -2178,20 +2539,25 @@
       </c>
       <c r="B73" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C73" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr" s="12">
+      <c r="E73" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N5_low[6].detail</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr" s="3">
+      <c r="H73" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}の不満げな態度がチームメイトにも伝わっている。このまま放置すると退団リスクが高まりそうだ。待遇改善や直接の対話が必要かもしれない。</t>
         </is>
@@ -2205,20 +2571,25 @@
       </c>
       <c r="B74" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C74" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr" s="12">
+      <c r="E74" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[1].text</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr" s="3">
+      <c r="H74" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😶 {name}が最近、練習で一人でいることが増えた…</t>
         </is>
@@ -2232,20 +2603,25 @@
       </c>
       <c r="B75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C75" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr" s="12">
+      <c r="E75" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[1].detail</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr" s="3">
+      <c r="H75" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">合同練習の後も{name}は一人で黙々とストレッチをしている。以前はチームメイトと談笑していたのだが、最近はほとんど会話がない。</t>
         </is>
@@ -2259,20 +2635,25 @@
       </c>
       <c r="B76" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C76" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr" s="12">
+      <c r="E76" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[2].text</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr" s="3">
+      <c r="H76" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🚶 {name}が練習後にすぐ帰るようになった</t>
         </is>
@@ -2286,20 +2667,25 @@
       </c>
       <c r="B77" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C77" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr" s="12">
+      <c r="E77" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[2].detail</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr" s="3">
+      <c r="H77" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">以前は最後まで残って自主練をしていた{name}だが、最近は練習が終わると荷物をまとめてさっと帰ってしまう。何かを抱えているようだ。</t>
         </is>
@@ -2313,20 +2699,25 @@
       </c>
       <c r="B78" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C78" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr" s="12">
+      <c r="E78" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[3].text</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr" s="3">
+      <c r="H78" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😔 {name}が休憩時間にひとりぼっちだった</t>
         </is>
@@ -2340,20 +2731,25 @@
       </c>
       <c r="B79" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C79" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr" s="12">
+      <c r="E79" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[3].detail</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr" s="3">
+      <c r="H79" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">休憩時間、他の選手たちが輪になって話す中、{name}は隅でスマホを見つめていた。以前はいつも誰かと一緒にいたのに。</t>
         </is>
@@ -2367,20 +2763,25 @@
       </c>
       <c r="B80" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C80" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr" s="12">
+      <c r="E80" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[4].text</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr" s="3">
+      <c r="H80" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👤 {name}が道場の隅で黙々と練習していた</t>
         </is>
@@ -2394,20 +2795,25 @@
       </c>
       <c r="B81" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C81" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr" s="12">
+      <c r="E81" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[4].detail</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr" s="3">
+      <c r="H81" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">みんなが中央のリングで合同練習をしている時、{name}は壁際で一人、基礎練習を繰り返していた。周囲とは見えない壁ができている。</t>
         </is>
@@ -2421,20 +2827,25 @@
       </c>
       <c r="B82" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C82" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr" s="12">
+      <c r="E82" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[5].text</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr" s="3">
+      <c r="H82" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🫥 {name}の表情が硬い日が増えた</t>
         </is>
@@ -2448,20 +2859,25 @@
       </c>
       <c r="B83" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C83" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr" s="12">
+      <c r="E83" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[5].detail</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr" s="3">
+      <c r="H83" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}の笑顔を見る機会がめっきり減った。練習中も淡々とメニューをこなすだけで、チームメイトとの雑談もほとんどない。</t>
         </is>
@@ -2475,20 +2891,25 @@
       </c>
       <c r="B84" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C84" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr" s="12">
+      <c r="E84" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[6].text</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr" s="3">
+      <c r="H84" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">😶‍🌫️ {name}が自主練も一人で行うようになった</t>
         </is>
@@ -2502,20 +2923,25 @@
       </c>
       <c r="B85" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C85" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr" s="12">
+      <c r="E85" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_isolation[6].detail</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr" s="3">
+      <c r="H85" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">以前はスパーリング相手を自分から探していた{name}が、最近は一人でサンドバッグを叩いている姿しか見ない。心を閉ざし始めているのかもしれない。</t>
         </is>
@@ -2529,20 +2955,25 @@
       </c>
       <c r="B86" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C86" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr" s="12">
+      <c r="E86" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[1].text</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr" s="3">
+      <c r="H86" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📋 コーチ{coach}が報告:「{name}の様子が最近おかしい」</t>
         </is>
@@ -2556,20 +2987,25 @@
       </c>
       <c r="B87" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C87" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr" s="12">
+      <c r="E87" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[1].detail</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr" s="3">
+      <c r="H87" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">コーチ{coach}が社長室を訪れた。「{name}のことなんですが…練習中の集中力が明らかに落ちています。少し気にかけてやってほしい」</t>
         </is>
@@ -2583,20 +3019,25 @@
       </c>
       <c r="B88" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C88" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr" s="12">
+      <c r="E88" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[2].text</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr" s="3">
+      <c r="H88" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📝 コーチ{coach}:「{name}のことで相談が…」</t>
         </is>
@@ -2610,20 +3051,25 @@
       </c>
       <c r="B89" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C89" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr" s="12">
+      <c r="E89" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[2].detail</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr" s="3">
+      <c r="H89" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「{name}が最近、試合後も練習後もすぐに帰ってしまうんです。前は自主練していたのに。何か不満があるのかもしれません」とコーチ{coach}が心配そうに報告した。</t>
         </is>
@@ -2637,20 +3083,25 @@
       </c>
       <c r="B90" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C90" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr" s="12">
+      <c r="E90" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[3].text</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr" s="3">
+      <c r="H90" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🗣️ コーチ{coach}が{name}について進言</t>
         </is>
@@ -2664,20 +3115,25 @@
       </c>
       <c r="B91" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C91" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr" s="12">
+      <c r="E91" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[3].detail</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr" s="3">
+      <c r="H91" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「社長、{name}のモチベーションが下がっているように見えます。練習態度は悪くないんですが…どこか投げやりというか。ケアが必要かもしれません」</t>
         </is>
@@ -2691,20 +3147,25 @@
       </c>
       <c r="B92" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C92" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr" s="12">
+      <c r="E92" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[4].text</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr" s="3">
+      <c r="H92" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ コーチ{coach}:「{name}が心配です」</t>
         </is>
@@ -2718,20 +3179,25 @@
       </c>
       <c r="B93" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C93" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr" s="12">
+      <c r="E93" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[4].detail</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr" s="3">
+      <c r="H93" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「{name}とは最近あまり話せていないんです。こちらから声をかけても素っ気ない返事しか返ってこなくて。何か手を打った方がいいかもしれません」</t>
         </is>
@@ -2745,20 +3211,25 @@
       </c>
       <c r="B94" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C94" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr" s="12">
+      <c r="E94" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[5].text</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr" s="3">
+      <c r="H94" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👀 コーチ{coach}が{name}の変調に気づいた</t>
         </is>
@@ -2772,20 +3243,25 @@
       </c>
       <c r="B95" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C95" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr" s="12">
+      <c r="E95" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[5].detail</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr" s="3">
+      <c r="H95" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「{name}、最近ちょっとおかしいです。技の精度は保ってるんですが、目が死んでるというか…このまま放っておくとまずいかもしれません」</t>
         </is>
@@ -2799,20 +3275,25 @@
       </c>
       <c r="B96" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C96" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr" s="12">
+      <c r="E96" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[6].text</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr" s="3">
+      <c r="H96" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📊 コーチ{coach}の定期報告に{name}の名前が</t>
         </is>
@@ -2826,20 +3307,25 @@
       </c>
       <c r="B97" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C97" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr" s="12">
+      <c r="E97" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_coach_report[6].detail</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr" s="3">
+      <c r="H97" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">月次の選手状態報告の中で、コーチ{coach}が{name}の名前を特記していた。「要注意。練習態度に変化あり。面談を推奨します」</t>
         </is>
@@ -2853,20 +3339,25 @@
       </c>
       <c r="B98" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C98" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr" s="12">
+      <c r="E98" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_sudden_departure[1].text</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr" s="3">
+      <c r="H98" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🚪 {name}が荷物をまとめて団体を去った</t>
         </is>
@@ -2880,20 +3371,25 @@
       </c>
       <c r="B99" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C99" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr" s="12">
+      <c r="E99" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_sudden_departure[1].detail</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr" s="3">
+      <c r="H99" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">朝、道場に着くと{name}のロッカーが空になっていた。誰にも何も言わず、荷物をまとめて去ったらしい。誰も止められなかった。</t>
         </is>
@@ -2907,20 +3403,25 @@
       </c>
       <c r="B100" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C100" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr" s="12">
+      <c r="E100" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_sudden_departure[2].text</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr" s="3">
+      <c r="H100" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📦 {name}が突然いなくなった…</t>
         </is>
@@ -2934,20 +3435,25 @@
       </c>
       <c r="B101" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C101" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr" s="12">
+      <c r="E101" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_sudden_departure[2].detail</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr" s="3">
+      <c r="H101" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">昨日まで普通に練習に来ていた{name}が、今日は姿を見せなかった。ロッカーの私物はすべて持ち出されていた。連絡もつかない。</t>
         </is>
@@ -2961,20 +3467,25 @@
       </c>
       <c r="B102" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C102" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr" s="12">
+      <c r="E102" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_sudden_departure[3].text</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr" s="3">
+      <c r="H102" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💨 {name}の姿が消えた</t>
         </is>
@@ -2988,20 +3499,25 @@
       </c>
       <c r="B103" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C103" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">NOTIF_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr" s="12">
+      <c r="E103" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">N_sudden_departure[3].detail</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr" s="3">
+      <c r="H103" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">気がつけば{name}はもういなかった。ロッカールームには何も残っていない。チームメイトたちも言葉を失っている。</t>
         </is>
@@ -3015,20 +3531,25 @@
       </c>
       <c r="B104" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C104" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr" s="12">
+      <c r="E104" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G1.scene[1]</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr" s="3">
+      <c r="H104" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">給料日。{name}が明細をじっと見つめていた</t>
         </is>
@@ -3042,20 +3563,25 @@
       </c>
       <c r="B105" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C105" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr" s="12">
+      <c r="E105" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G1.scene[2]</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr" s="3">
+      <c r="H105" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が食堂で同僚たちの輪に入らず、黙って食事をしていた</t>
         </is>
@@ -3069,20 +3595,25 @@
       </c>
       <c r="B106" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C106" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr" s="12">
+      <c r="E106" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G1.scene[3]</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr" s="3">
+      <c r="H106" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}がロッカールームで、誰かの契約書をちらりと見ていた</t>
         </is>
@@ -3096,20 +3627,25 @@
       </c>
       <c r="B107" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C107" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr" s="12">
+      <c r="E107" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G2.scene[1]</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr" s="3">
+      <c r="H107" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が後輩の{name2}の試合を腕を組んで見ていた。複雑な表情だ</t>
         </is>
@@ -3123,20 +3659,25 @@
       </c>
       <c r="B108" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C108" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr" s="12">
+      <c r="E108" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G2.scene[2]</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr" s="3">
+      <c r="H108" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が{name2}に技を教えている。だが、その目にどこか翳りがある</t>
         </is>
@@ -3150,20 +3691,25 @@
       </c>
       <c r="B109" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C109" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr" s="12">
+      <c r="E109" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G3.scene[1]</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr" s="3">
+      <c r="H109" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}がタイトルマッチのポスターの前で足を止めていた</t>
         </is>
@@ -3177,20 +3723,25 @@
       </c>
       <c r="B110" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C110" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr" s="12">
+      <c r="E110" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G3.scene[2]</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr" s="3">
+      <c r="H110" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が練習中、いつもより打ち込みが荒い。何かを持て余している</t>
         </is>
@@ -3204,20 +3755,25 @@
       </c>
       <c r="B111" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C111" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr" s="12">
+      <c r="E111" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G3.scene[3]</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr" s="3">
+      <c r="H111" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">タイトル戦の話題が出た時、{name}だけが黙っていた</t>
         </is>
@@ -3231,20 +3787,25 @@
       </c>
       <c r="B112" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C112" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr" s="12">
+      <c r="E112" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G4.scene[1]</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr" s="3">
+      <c r="H112" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が試合のない週末を持て余しているようだ</t>
         </is>
@@ -3258,20 +3819,25 @@
       </c>
       <c r="B113" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C113" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr" s="12">
+      <c r="E113" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G4.scene[2]</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr" s="3">
+      <c r="H113" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">控え室の隅で、{name}がストレッチをしている。出番を待つ背中に焦りが見える</t>
         </is>
@@ -3285,20 +3851,25 @@
       </c>
       <c r="B114" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C114" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr" s="12">
+      <c r="E114" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">G4.scene[3]</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr" s="3">
+      <c r="H114" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が自主練の後、一人でリングを見つめていた</t>
         </is>
@@ -3312,20 +3883,25 @@
       </c>
       <c r="B115" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C115" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr" s="12">
+      <c r="E115" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R1.scene[1]</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr" s="3">
+      <c r="H115" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が控え室で目を合わせなかった</t>
         </is>
@@ -3339,20 +3915,25 @@
       </c>
       <c r="B116" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C116" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr" s="12">
+      <c r="E116" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R1.scene[2]</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr" s="3">
+      <c r="H116" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}の間に、見えない壁がある。周りもそれを感じている</t>
         </is>
@@ -3366,20 +3947,25 @@
       </c>
       <c r="B117" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C117" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr" s="12">
+      <c r="E117" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R1.scene[3]</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr" s="3">
+      <c r="H117" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が同じテーブルに座ることを避けていた</t>
         </is>
@@ -3393,20 +3979,25 @@
       </c>
       <c r="B118" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C118" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr" s="12">
+      <c r="E118" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R1.staff[1]</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr" s="3">
+      <c r="H118" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スタッフから: {name}と{name2}、最近どうも空気がピリついてまして…</t>
         </is>
@@ -3420,20 +4011,25 @@
       </c>
       <c r="B119" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C119" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr" s="12">
+      <c r="E119" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R2.scene[1]</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr" s="3">
+      <c r="H119" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">昼休み。他の選手たちが談笑する中、{name}だけが離れた場所にいた</t>
         </is>
@@ -3447,20 +4043,25 @@
       </c>
       <c r="B120" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C120" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr" s="12">
+      <c r="E120" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R2.scene[2]</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr" s="3">
+      <c r="H120" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が一人でリングの片付けをしている。手伝う者はいない</t>
         </is>
@@ -3474,20 +4075,25 @@
       </c>
       <c r="B121" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C121" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr" s="12">
+      <c r="E121" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R2.scene[3]</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr" s="3">
+      <c r="H121" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習後の更衣室。{name}のロッカーの周りだけ、少し空間が空いている</t>
         </is>
@@ -3501,20 +4107,25 @@
       </c>
       <c r="B122" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C122" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr" s="12">
+      <c r="E122" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R3.scene[1]</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr" s="3">
+      <c r="H122" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}は{name2}の退団を知り、しばらく言葉を失っていた</t>
         </is>
@@ -3528,20 +4139,25 @@
       </c>
       <c r="B123" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C123" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr" s="12">
+      <c r="E123" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R3.scene[2]</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr" s="3">
+      <c r="H123" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name2}がいなくなったロッカーの前で、{name}が立ち止まっていた</t>
         </is>
@@ -3555,20 +4171,25 @@
       </c>
       <c r="B124" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C124" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr" s="12">
+      <c r="E124" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R4.scene[1]</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr" s="3">
+      <c r="H124" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">試合後、{name}の目に静かな炎が燃えていた</t>
         </is>
@@ -3582,20 +4203,25 @@
       </c>
       <c r="B125" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C125" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr" s="12">
+      <c r="E125" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R4.scene[2]</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr" s="3">
+      <c r="H125" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}がリングを降りる時、一瞬だけ{name2}のほうを振り返った。満足げに</t>
         </is>
@@ -3609,20 +4235,25 @@
       </c>
       <c r="B126" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C126" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr" s="12">
+      <c r="E126" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R5.scene[1]</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr" s="3">
+      <c r="H126" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}は無言でリングを降りた。その拳だけが震えていた</t>
         </is>
@@ -3636,20 +4267,25 @@
       </c>
       <c r="B127" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C127" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr" s="12">
+      <c r="E127" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R5.scene[2]</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr" s="3">
+      <c r="H127" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が帰り際、振り返って{name2}のほうを一瞬だけ見た</t>
         </is>
@@ -3663,20 +4299,25 @@
       </c>
       <c r="B128" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C128" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr" s="12">
+      <c r="E128" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">R5.scene[3]</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr" s="3">
+      <c r="H128" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">試合後の通路で、{name}が壁を叩く音がした</t>
         </is>
@@ -3690,20 +4331,25 @@
       </c>
       <c r="B129" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C129" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr" s="12">
+      <c r="E129" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">friction.scene[1]</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr" s="3">
+      <c r="H129" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が練習メニューの順番で揉めていた。些細なことだが</t>
         </is>
@@ -3717,20 +4363,25 @@
       </c>
       <c r="B130" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C130" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr" s="12">
+      <c r="E130" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">friction.scene[2]</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr" s="3">
+      <c r="H130" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が{name2}の練習態度について、小声で何か言っていた</t>
         </is>
@@ -3744,20 +4395,25 @@
       </c>
       <c r="B131" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C131" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr" s="12">
+      <c r="E131" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">friction.scene[3]</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr" s="3">
+      <c r="H131" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が同時に控え室に入った瞬間、空気が変わった</t>
         </is>
@@ -3771,20 +4427,25 @@
       </c>
       <c r="B132" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C132" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr" s="12">
+      <c r="E132" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">friction.staff[1]</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr" s="3">
+      <c r="H132" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スタッフから: {name}と{name2}、ちょっと相性が良くないみたいで…</t>
         </is>
@@ -3798,20 +4459,25 @@
       </c>
       <c r="B133" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C133" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr" s="12">
+      <c r="E133" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">generation.scene[1]</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr" s="3">
+      <c r="H133" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が一緒に帰っていく姿が見えた。同世代の気安さがある</t>
         </is>
@@ -3825,20 +4491,25 @@
       </c>
       <c r="B134" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C134" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr" s="12">
+      <c r="E134" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">generation.scene[2]</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr" s="3">
+      <c r="H134" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が自販機の前で笑い合っていた。何が面白いのか、こちらには分からないが</t>
         </is>
@@ -3852,20 +4523,25 @@
       </c>
       <c r="B135" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C135" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr" s="12">
+      <c r="E135" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">generation.scene[3]</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr" s="3">
+      <c r="H135" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が{name2}を自主練に誘っている。いい雰囲気だ</t>
         </is>
@@ -3879,20 +4555,25 @@
       </c>
       <c r="B136" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C136" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr" s="12">
+      <c r="E136" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">generation.scene[4]</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr" s="3">
+      <c r="H136" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}と{name2}が昼食を一緒に取っている。どうやら仲がいいらしい</t>
         </is>
@@ -3906,20 +4587,25 @@
       </c>
       <c r="B137" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C137" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr" s="12">
+      <c r="E137" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rivalryResolved.scene[1]</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr" s="3">
+      <c r="H137" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">決着はついた。だが{name}と{name2}が目を合わせた時、そこにはまだ何かがあった</t>
         </is>
@@ -3933,20 +4619,25 @@
       </c>
       <c r="B138" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C138" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr" s="12">
+      <c r="E138" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">rivalryResolved.scene[2]</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr" s="3">
+      <c r="H138" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">因縁は終わった。はずだ。…だが{name}は{name2}の動向を気にしている</t>
         </is>
@@ -3960,20 +4651,25 @@
       </c>
       <c r="B139" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C139" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr" s="12">
+      <c r="E139" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">careerBestMQ.scene[1]</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr" s="3">
+      <c r="H139" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が試合後、自分の両手を見つめていた。何かを掴んだ表情だ</t>
         </is>
@@ -3987,20 +4683,25 @@
       </c>
       <c r="B140" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C140" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr" s="12">
+      <c r="E140" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">careerBestMQ.scene[2]</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr" s="3">
+      <c r="H140" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}の試合が終わった後、先輩たちが小さく頷いていた</t>
         </is>
@@ -4014,20 +4715,25 @@
       </c>
       <c r="B141" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C141" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">SNAPSHOT_TEXTS</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr" s="12">
+      <c r="E141" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">warVictory.scene[1]</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr" s="3">
+      <c r="H141" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}はチームの勝利に拳を握りしめた。この団体の看板を背負う覚悟が見えた</t>
         </is>
@@ -4041,20 +4747,25 @@
       </c>
       <c r="B142" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C142" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr" s="12">
+      <c r="E142" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bonus.label</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr" s="3">
+      <c r="H142" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ボーナス支給願</t>
         </is>
@@ -4068,20 +4779,25 @@
       </c>
       <c r="B143" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C143" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr" s="12">
+      <c r="E143" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bonus.categoryLabel</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr" s="3">
+      <c r="H143" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手ケア</t>
         </is>
@@ -4095,20 +4811,25 @@
       </c>
       <c r="B144" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C144" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr" s="12">
+      <c r="E144" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bonus.costLabel</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr" s="3">
+      <c r="H144" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">起案額による</t>
         </is>
@@ -4122,20 +4843,25 @@
       </c>
       <c r="B145" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C145" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr" s="12">
+      <c r="E145" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bonus.body</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr" s="3">
+      <c r="H145" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">対象選手に特別手当を支給し、組織貢献への感謝を示す</t>
         </is>
@@ -4149,20 +4875,25 @@
       </c>
       <c r="B146" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C146" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr" s="12">
+      <c r="E146" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bonus.detailText</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr" s="3">
+      <c r="H146" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">起案された支給額の中から、いくら積むかを社長が決める。額面が彼女の格に見合ってこそ、誠意は伝わる。安すぎる額は、かえって心を離れさせることもある。</t>
         </is>
@@ -4176,20 +4907,25 @@
       </c>
       <c r="B147" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C147" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr" s="12">
+      <c r="E147" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bonus.effectSummary</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr" s="3">
+      <c r="H147" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">支給額しだいで本人の受け止め方が変わる。相場を大きく超える額は深く響く</t>
         </is>
@@ -4203,20 +4939,25 @@
       </c>
       <c r="B148" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C148" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr" s="12">
+      <c r="E148" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">bonus.recommendation</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr" s="3">
+      <c r="H148" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">団体への気持ちが陰りはじめた選手に、早めに手を打つと効果的。同じ選手への再支給は相場が吊り上がる点に注意。</t>
         </is>
@@ -4230,20 +4971,25 @@
       </c>
       <c r="B149" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C149" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr" s="12">
+      <c r="E149" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">encourage.label</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr" s="3">
+      <c r="H149" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">声かけ</t>
         </is>
@@ -4257,20 +5003,25 @@
       </c>
       <c r="B150" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C150" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr" s="12">
+      <c r="E150" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">encourage.categoryLabel</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr" s="3">
+      <c r="H150" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手ケア</t>
         </is>
@@ -4284,20 +5035,25 @@
       </c>
       <c r="B151" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C151" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr" s="12">
+      <c r="E151" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">encourage.body</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr" s="3">
+      <c r="H151" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">気にかけている選手に社長自ら声をかけに行く</t>
         </is>
@@ -4311,20 +5067,25 @@
       </c>
       <c r="B152" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C152" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr" s="12">
+      <c r="E152" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">encourage.detailText</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr" s="3">
+      <c r="H152" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">決裁枠も資金も使わない、社長自らの自発的な行動。スランプ中・モチベ喪失中・最近様子が気になる選手に足を運んで声をかける。</t>
         </is>
@@ -4338,20 +5099,25 @@
       </c>
       <c r="B153" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C153" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr" s="12">
+      <c r="E153" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">encourage.effectSummary</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr" s="3">
+      <c r="H153" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">本人の表情が少し和らぐ（スランプ・モチベ喪失なら回復促進も）</t>
         </is>
@@ -4365,20 +5131,25 @@
       </c>
       <c r="B154" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C154" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr" s="12">
+      <c r="E154" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">encourage.recommendation</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr" s="3">
+      <c r="H154" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">気になる選手のポップアップから直接実行する。机には並ばない。</t>
         </is>
@@ -4392,20 +5163,25 @@
       </c>
       <c r="B155" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C155" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr" s="12">
+      <c r="E155" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">special_treatment.label</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr" s="3">
+      <c r="H155" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">特別治療指示書</t>
         </is>
@@ -4419,20 +5195,25 @@
       </c>
       <c r="B156" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C156" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr" s="12">
+      <c r="E156" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">special_treatment.categoryLabel</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr" s="3">
+      <c r="H156" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手ケア</t>
         </is>
@@ -4446,20 +5227,25 @@
       </c>
       <c r="B157" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C157" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr" s="12">
+      <c r="E157" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">special_treatment.body</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr" s="3">
+      <c r="H157" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">離脱中の選手に専門医を手配し、復帰を早める</t>
         </is>
@@ -4473,20 +5259,25 @@
       </c>
       <c r="B158" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C158" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr" s="12">
+      <c r="E158" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">special_treatment.detailText</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr" s="3">
+      <c r="H158" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">専門医による集中ケアを正式に発注。怪我からの離脱期間を確率的に短縮する、復帰前倒しの一手。確実な短縮量は治療結果次第。</t>
         </is>
@@ -4500,20 +5291,25 @@
       </c>
       <c r="B159" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C159" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr" s="12">
+      <c r="E159" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">special_treatment.effectSummary</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr" s="3">
+      <c r="H159" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">対象選手の離脱期間が1〜4週短縮される</t>
         </is>
@@ -4527,20 +5323,25 @@
       </c>
       <c r="B160" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C160" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr" s="12">
+      <c r="E160" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">special_treatment.recommendation</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr" s="3">
+      <c r="H160" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">主力選手や王座挑戦が控えている選手の離脱が痛手なときに。離脱が長引いている怪我ほど短縮量も大きくなりやすい。</t>
         </is>
@@ -4554,20 +5355,25 @@
       </c>
       <c r="B161" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C161" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr" s="12">
+      <c r="E161" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">refresh_leave.label</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr" s="3">
+      <c r="H161" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">休暇辞令</t>
         </is>
@@ -4581,20 +5387,25 @@
       </c>
       <c r="B162" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C162" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr" s="12">
+      <c r="E162" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">refresh_leave.categoryLabel</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr" s="3">
+      <c r="H162" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手ケア</t>
         </is>
@@ -4608,20 +5419,25 @@
       </c>
       <c r="B163" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C163" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr" s="12">
+      <c r="E163" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">refresh_leave.costLabel</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr" s="3">
+      <c r="H163" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">週給×週数+50万</t>
         </is>
@@ -4635,20 +5451,25 @@
       </c>
       <c r="B164" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C164" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr" s="12">
+      <c r="E164" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">refresh_leave.body</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr" s="3">
+      <c r="H164" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">心身の疲弊を察し、一定期間の休養を与える</t>
         </is>
@@ -4662,20 +5483,25 @@
       </c>
       <c r="B165" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C165" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr" s="12">
+      <c r="E165" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">refresh_leave.detailText</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr" s="3">
+      <c r="H165" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">1〜4週間の休暇を正式な辞令として発行する。休暇中の試合には欠場するが、そのぶん心身は着実に回復していく。長い休みは、積み重なった消耗までも癒やす。</t>
         </is>
@@ -4689,20 +5515,25 @@
       </c>
       <c r="B166" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C166" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr" s="12">
+      <c r="E166" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">refresh_leave.effectSummary</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr" s="3">
+      <c r="H166" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">休みの長さに応じて体調が戻り、長期なら蓄積した消耗も癒える。本人にも気遣いが伝わる</t>
         </is>
@@ -4716,20 +5547,25 @@
       </c>
       <c r="B167" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C167" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr" s="12">
+      <c r="E167" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">refresh_leave.recommendation</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr" s="3">
+      <c r="H167" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">疲れの見える主力を、大事な興行の前に立て直す疲労管理の要。休暇中の欠場と引き換えになる点は覚悟すること。</t>
         </is>
@@ -4743,20 +5579,25 @@
       </c>
       <c r="B168" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C168" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr" s="12">
+      <c r="E168" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">party.label</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr" s="3">
+      <c r="H168" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">慰労会開催届</t>
         </is>
@@ -4770,20 +5611,25 @@
       </c>
       <c r="B169" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C169" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr" s="12">
+      <c r="E169" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">party.categoryLabel</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr" s="3">
+      <c r="H169" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手ケア</t>
         </is>
@@ -4797,20 +5643,25 @@
       </c>
       <c r="B170" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C170" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr" s="12">
+      <c r="E170" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">party.body</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr" s="3">
+      <c r="H170" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">団体の雰囲気を立て直すべく、慰労の宴席を設ける</t>
         </is>
@@ -4824,20 +5675,25 @@
       </c>
       <c r="B171" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C171" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr" s="12">
+      <c r="E171" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">party.detailText</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr" s="3">
+      <c r="H171" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">全選手を集めた慰労の宴席。個別の数値を動かすより、ロッカールームの空気そのものを立て直すのが主目的。</t>
         </is>
@@ -4851,20 +5707,25 @@
       </c>
       <c r="B172" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C172" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr" s="12">
+      <c r="E172" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">party.effectSummary</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr" s="3">
+      <c r="H172" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手同士の会話が増え、ロッカールームと社長への空気が柔らかくなる</t>
         </is>
@@ -4878,20 +5739,25 @@
       </c>
       <c r="B173" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C173" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr" s="12">
+      <c r="E173" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">party.recommendation</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr" s="3">
+      <c r="H173" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ロッカールームの空気に少し陰りが見えてきたときの応急処置として。単発では決定打にならない点に留意。</t>
         </is>
@@ -4905,20 +5771,25 @@
       </c>
       <c r="B174" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C174" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr" s="12">
+      <c r="E174" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trainer.label</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr" s="3">
+      <c r="H174" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">外部コーチ招聘状</t>
         </is>
@@ -4932,20 +5803,25 @@
       </c>
       <c r="B175" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C175" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr" s="12">
+      <c r="E175" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trainer.categoryLabel</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr" s="3">
+      <c r="H175" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">育成</t>
         </is>
@@ -4959,20 +5835,25 @@
       </c>
       <c r="B176" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C176" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr" s="12">
+      <c r="E176" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trainer.costLabel</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr" s="3">
+      <c r="H176" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">コーチの格による</t>
         </is>
@@ -4986,20 +5867,25 @@
       </c>
       <c r="B177" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C177" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr" s="12">
+      <c r="E177" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trainer.body</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr" s="3">
+      <c r="H177" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今期の候補から外部コーチを選び、一人の選手に短期集中で指導を受けさせる</t>
         </is>
@@ -5013,20 +5899,25 @@
       </c>
       <c r="B178" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C178" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr" s="12">
+      <c r="E178" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trainer.detailText</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr" s="3">
+      <c r="H178" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今期市場に出ている外部コーチの中から一人を選び、期間限定で招聘する。指導タイプと選手の相性、得意スタイルの一致が効果を左右する。招聘中は雇用コーチの指導から外れ、そのコーチに専念する。</t>
         </is>
@@ -5040,20 +5931,25 @@
       </c>
       <c r="B179" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C179" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr" s="12">
+      <c r="E179" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trainer.effectSummary</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr" s="3">
+      <c r="H179" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">4週間のあいだ対象選手の練習効果が上がる。コーチの格・相性・特殊能力しだいで伸び方が変わる</t>
         </is>
@@ -5067,20 +5963,25 @@
       </c>
       <c r="B180" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C180" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr" s="12">
+      <c r="E180" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">trainer.recommendation</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr" s="3">
+      <c r="H180" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">今期の市場に出た顔ぶれを見て、伸ばしたい選手に合いそうな一人を選ぶ。同時に招聘できるのは1件のみ、同じ選手を続けて詰め込みすぎると効果が鈍る点に注意。</t>
         </is>
@@ -5094,20 +5995,25 @@
       </c>
       <c r="B181" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C181" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr" s="12">
+      <c r="E181" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">camp.label</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr" s="3">
+      <c r="H181" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">合宿実施手配書</t>
         </is>
@@ -5121,20 +6027,25 @@
       </c>
       <c r="B182" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C182" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr" s="12">
+      <c r="E182" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">camp.categoryLabel</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr" s="3">
+      <c r="H182" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">育成</t>
         </is>
@@ -5148,20 +6059,25 @@
       </c>
       <c r="B183" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C183" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr" s="12">
+      <c r="E183" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">camp.body</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr" s="3">
+      <c r="H183" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">全選手を集中的に強化するため、合宿を実施する</t>
         </is>
@@ -5175,20 +6091,25 @@
       </c>
       <c r="B184" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C184" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr" s="12">
+      <c r="E184" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">camp.detailText</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr" s="3">
+      <c r="H184" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手全員を合宿地へ送り込み、短期集中で基礎を鍛え直す。ひとり40万×人数ぶんの費用と決裁枠3を消費する重量級書類。</t>
         </is>
@@ -5202,20 +6123,25 @@
       </c>
       <c r="B185" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C185" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr" s="12">
+      <c r="E185" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">camp.effectSummary</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr" s="3">
+      <c r="H185" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">2週間のあいだ全員の練習効果が上がり、団体全体に一体感が育つ</t>
         </is>
@@ -5229,20 +6155,25 @@
       </c>
       <c r="B186" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C186" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr" s="12">
+      <c r="E186" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">camp.recommendation</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr" s="3">
+      <c r="H186" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">資金に余裕があり、オフシーズン前後に全体を底上げしたいとき。年1〜2回が現実的な使用頻度。</t>
         </is>
@@ -5256,20 +6187,25 @@
       </c>
       <c r="B187" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C187" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr" s="12">
+      <c r="E187" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">media.label</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr" s="3">
+      <c r="H187" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">メディア露出手配書</t>
         </is>
@@ -5283,20 +6219,25 @@
       </c>
       <c r="B188" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C188" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr" s="12">
+      <c r="E188" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">media.categoryLabel</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr" s="3">
+      <c r="H188" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">広報</t>
         </is>
@@ -5310,20 +6251,25 @@
       </c>
       <c r="B189" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C189" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr" s="12">
+      <c r="E189" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">media.body</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr" s="3">
+      <c r="H189" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">対象選手を広告塔とし、団体の知名度向上を図る</t>
         </is>
@@ -5337,20 +6283,25 @@
       </c>
       <c r="B190" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C190" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr" s="12">
+      <c r="E190" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">media.detailText</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr" s="3">
+      <c r="H190" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">対象選手をメディア露出の広告塔として起用。団体の知名度向上と本人の体調維持を両立させる外向き施策。</t>
         </is>
@@ -5364,20 +6315,25 @@
       </c>
       <c r="B191" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C191" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr" s="12">
+      <c r="E191" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">media.effectSummary</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr" s="3">
+      <c r="H191" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手人気と団体人気が上がり、体調が整う。本人も起用を前向きに受け止める</t>
         </is>
@@ -5391,20 +6347,25 @@
       </c>
       <c r="B192" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C192" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr" s="12">
+      <c r="E192" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">media.recommendation</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr" s="3">
+      <c r="H192" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">団体人気がある程度育ってから解禁される書類。看板選手の体調管理と兼ねて回すと無駄がない。選手の人気を直接押し上げたい時にも有効。</t>
         </is>
@@ -5418,20 +6379,25 @@
       </c>
       <c r="B193" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C193" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr" s="12">
+      <c r="E193" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">relationship_repair.label</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr" s="3">
+      <c r="H193" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">関係修復斡旋書</t>
         </is>
@@ -5445,20 +6411,25 @@
       </c>
       <c r="B194" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C194" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr" s="12">
+      <c r="E194" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">relationship_repair.categoryLabel</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr" s="3">
+      <c r="H194" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手ケア</t>
         </is>
@@ -5472,20 +6443,25 @@
       </c>
       <c r="B195" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C195" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr" s="12">
+      <c r="E195" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">relationship_repair.body</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr" s="3">
+      <c r="H195" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">長期的な険悪関係にあるペアの間に立ち、関係改善を図る</t>
         </is>
@@ -5499,20 +6475,25 @@
       </c>
       <c r="B196" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C196" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr" s="12">
+      <c r="E196" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">relationship_repair.detailText</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr" s="3">
+      <c r="H196" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">勝負の世界では険悪な関係も時に武器になる。だが限度を超えると組織全体を蝕む。社長が間に立ち、最悪の事態を避ける。成功率は約70%。失敗しても関係はそのまま。</t>
         </is>
@@ -5526,20 +6507,25 @@
       </c>
       <c r="B197" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C197" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr" s="12">
+      <c r="E197" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">relationship_repair.effectSummary</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr" s="3">
+      <c r="H197" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">成功時、双方向 bond +5〜+10。失敗時は据え置き。</t>
         </is>
@@ -5553,20 +6539,25 @@
       </c>
       <c r="B198" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C198" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D198" t="inlineStr" s="12">
+      <c r="E198" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">relationship_repair.recommendation</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr" s="3">
+      <c r="H198" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">W-1（憎い敵ゾーン）が累計4回以上発火したペアに対して使用できる。慢性化する前に手を打てば、亀裂が修復可能になることもある。</t>
         </is>
@@ -5580,20 +6571,25 @@
       </c>
       <c r="B199" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C199" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr" s="12">
+      <c r="E199" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">faction_decree.label</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr" s="3">
+      <c r="H199" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">派閥解散命令</t>
         </is>
@@ -5607,20 +6603,25 @@
       </c>
       <c r="B200" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C200" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr" s="12">
+      <c r="E200" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">faction_decree.categoryLabel</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr" s="3">
+      <c r="H200" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">人事</t>
         </is>
@@ -5634,20 +6635,25 @@
       </c>
       <c r="B201" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C201" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr" s="12">
+      <c r="E201" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">faction_decree.body</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr" s="3">
+      <c r="H201" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">団体内の派閥を社長命令で解散させ、以後の結成を認めるかどうかを決める</t>
         </is>
@@ -5661,20 +6667,25 @@
       </c>
       <c r="B202" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C202" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr" s="12">
+      <c r="E202" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">faction_decree.detailText</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr" s="3">
+      <c r="H202" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選手たちが自然に作った群れを、上から畳む。畳まれた側は当然おもしろくない。とくに束ねていた本人には深く残る。勢いに乗っていた派閥ほど、その傷は深い。</t>
         </is>
@@ -5688,20 +6699,25 @@
       </c>
       <c r="B203" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C203" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr" s="12">
+      <c r="E203" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">faction_decree.effectSummary</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr" s="3">
+      <c r="H203" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">選択した内容によって、解散のみ／解散して以後禁止／禁止の解除 が実行される</t>
         </is>
@@ -5715,20 +6731,25 @@
       </c>
       <c r="B204" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C204" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr" s="12">
+      <c r="E204" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">faction_decree.recommendation</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr" s="3">
+      <c r="H204" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">派閥の揉め事を団体から切り離したいときに。まだ派閥が生まれていないうちに禁止しておけば、誰の信頼も損なわずに済む。</t>
         </is>
@@ -5742,20 +6763,25 @@
       </c>
       <c r="B205" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C205" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr" s="12">
+      <c r="E205" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hireCoach.label</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr" s="3">
+      <c r="H205" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">コーチ雇用決裁書</t>
         </is>
@@ -5769,20 +6795,25 @@
       </c>
       <c r="B206" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C206" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr" s="12">
+      <c r="E206" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hireCoach.categoryLabel</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr" s="3">
+      <c r="H206" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">人事</t>
         </is>
@@ -5796,20 +6827,25 @@
       </c>
       <c r="B207" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C207" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr" s="12">
+      <c r="E207" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hireCoach.body</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr" s="3">
+      <c r="H207" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新たなスタッフを招聘し、団体の指導体制を強化する</t>
         </is>
@@ -5823,20 +6859,25 @@
       </c>
       <c r="B208" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C208" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr" s="12">
+      <c r="E208" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hireCoach.detailText</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr" s="3">
+      <c r="H208" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">新たなコーチを招聘し、指導体制を強化する。机には並ばず、コーチ画面から実行する特殊書類。</t>
         </is>
@@ -5850,20 +6891,25 @@
       </c>
       <c r="B209" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C209" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr" s="12">
+      <c r="E209" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hireCoach.effectSummary</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr" s="3">
+      <c r="H209" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">コーチを1名新しく迎える(決裁枠を2消費)</t>
         </is>
@@ -5877,20 +6923,25 @@
       </c>
       <c r="B210" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C210" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">DECISION_DOCS</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr" s="12">
+      <c r="E210" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">hireCoach.recommendation</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr" s="3">
+      <c r="H210" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">コーチ枠に空きがあり、新規雇用を検討している週に。机に書類として表示されない点に注意。</t>
         </is>
@@ -5904,20 +6955,25 @@
       </c>
       <c r="B211" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C211" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
-      <c r="D211" t="inlineStr" s="12">
+      <c r="E211" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr" s="3">
+      <c r="H211" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">無難な線です。ただ、響くかどうかは相手次第かと。</t>
         </is>
@@ -5931,20 +6987,25 @@
       </c>
       <c r="B212" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C212" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr" s="12">
+      <c r="E212" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr" s="3">
+      <c r="H212" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">彼女の格に見合った額かと存じます。</t>
         </is>
@@ -5958,20 +7019,25 @@
       </c>
       <c r="B213" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C213" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr" s="12">
+      <c r="E213" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr" s="3">
+      <c r="H213" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">相場を超えています。誠意は伝わるはずです。</t>
         </is>
@@ -5985,20 +7051,25 @@
       </c>
       <c r="B214" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C214" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">BONUS_PROPOSAL_MEMOS</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr" s="12">
+      <c r="E214" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr" s="3">
+      <c r="H214" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">……思い切りましたな。ここまで出す団体は他にありません。</t>
         </is>
@@ -6012,20 +7083,25 @@
       </c>
       <c r="B215" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C215" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr" s="12">
+      <c r="E215" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[1]</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr" s="3">
+      <c r="H215" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name1}と{name2}が朝から激しいスパーリングを繰り広げている…！</t>
         </is>
@@ -6039,20 +7115,25 @@
       </c>
       <c r="B216" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C216" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D216" t="inlineStr" s="12">
+      <c r="E216" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[2]</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr" s="3">
+      <c r="H216" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">夜の自主練で{name1}が黙々とスクワットをしている…</t>
         </is>
@@ -6066,20 +7147,25 @@
       </c>
       <c r="B217" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C217" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr" s="12">
+      <c r="E217" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[3]</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr" s="3">
+      <c r="H217" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name1}が{name2}に技の受け身を教えている場面が見られた</t>
         </is>
@@ -6093,20 +7179,25 @@
       </c>
       <c r="B218" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C218" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr" s="12">
+      <c r="E218" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[4]</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr" s="3">
+      <c r="H218" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">合宿の食事は{name1}が率先して準備していた</t>
         </is>
@@ -6120,20 +7211,25 @@
       </c>
       <c r="B219" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C219" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr" s="12">
+      <c r="E219" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[5]</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr" s="3">
+      <c r="H219" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name1}と{name2}が夕食後のランニングで競い合っている</t>
         </is>
@@ -6147,20 +7243,25 @@
       </c>
       <c r="B220" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C220" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr" s="12">
+      <c r="E220" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[6]</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr" s="3">
+      <c r="H220" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">早朝の海辺で{name1}が一人、基礎練習に励んでいた</t>
         </is>
@@ -6174,20 +7275,25 @@
       </c>
       <c r="B221" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C221" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr" s="12">
+      <c r="E221" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[7]</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr" s="3">
+      <c r="H221" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name1}が新技の研究に没頭している姿が印象的だった</t>
         </is>
@@ -6201,20 +7307,25 @@
       </c>
       <c r="B222" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C222" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr" s="12">
+      <c r="E222" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[8]</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr" s="3">
+      <c r="H222" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">消灯後も{name1}と{name2}がリングで語り合っていた</t>
         </is>
@@ -6228,20 +7339,25 @@
       </c>
       <c r="B223" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C223" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr" s="12">
+      <c r="E223" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[9]</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr" s="3">
+      <c r="H223" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name1}が合宿の記念写真を撮ろうとみんなを集めていた</t>
         </is>
@@ -6255,20 +7371,25 @@
       </c>
       <c r="B224" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C224" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr" s="12">
+      <c r="E224" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[10]</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr" s="3">
+      <c r="H224" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">全員で浜辺を走るメニューに{name1}が一番乗りでゴールした</t>
         </is>
@@ -6282,20 +7403,25 @@
       </c>
       <c r="B225" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C225" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr" s="12">
+      <c r="E225" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[11]</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr" s="3">
+      <c r="H225" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name1}のムードメーカーぶりで合宿の雰囲気がぐっと明るくなった</t>
         </is>
@@ -6309,20 +7435,25 @@
       </c>
       <c r="B226" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C226" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">CAMP_FLAVOR_TEXTS</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr" s="12">
+      <c r="E226" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">[12]</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr" s="3">
+      <c r="H226" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習後の大浴場で{name1}と{name2}が今後の抱負を語り合っていた</t>
         </is>
@@ -6336,20 +7467,25 @@
       </c>
       <c r="B227" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C227" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr" s="12">
+      <c r="E227" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[1].text</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr" s="3">
+      <c r="H227" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}が練習中にアクシデント</t>
         </is>
@@ -6363,20 +7499,25 @@
       </c>
       <c r="B228" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C228" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr" s="12">
+      <c r="E228" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[1].detail</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr" s="3">
+      <c r="H228" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が練習中に技を受けた際にバランスを崩し、負傷してしまった。</t>
         </is>
@@ -6390,20 +7531,25 @@
       </c>
       <c r="B229" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C229" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr" s="12">
+      <c r="E229" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[2].text</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr" s="3">
+      <c r="H229" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}が練習で負傷</t>
         </is>
@@ -6417,20 +7563,25 @@
       </c>
       <c r="B230" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C230" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr" s="12">
+      <c r="E230" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[2].detail</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr" s="3">
+      <c r="H230" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">スパーリング中に{name}が相手の技を受け損ね、マットに叩きつけられた。</t>
         </is>
@@ -6444,20 +7595,25 @@
       </c>
       <c r="B231" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C231" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr" s="12">
+      <c r="E231" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[3].text</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr" s="3">
+      <c r="H231" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}に練習中のトラブル</t>
         </is>
@@ -6471,20 +7627,25 @@
       </c>
       <c r="B232" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C232" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr" s="12">
+      <c r="E232" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[3].detail</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr" s="3">
+      <c r="H232" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name}が新技の練習中に着地に失敗。痛みを訴えている。</t>
         </is>
@@ -6498,20 +7659,25 @@
       </c>
       <c r="B233" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C233" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D233" t="inlineStr" s="12">
+      <c r="E233" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[4].text</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr" s="3">
+      <c r="H233" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}がロープワーク中に負傷</t>
         </is>
@@ -6525,20 +7691,25 @@
       </c>
       <c r="B234" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C234" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D234" t="inlineStr" s="12">
+      <c r="E234" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[4].detail</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr" s="3">
+      <c r="H234" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">ロープの反動を利用した連続技の練習中、{name}の足がロープに絡まり転倒。すぐには立ち上がれなかった。</t>
         </is>
@@ -6552,20 +7723,25 @@
       </c>
       <c r="B235" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C235" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr" s="12">
+      <c r="E235" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[5].text</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr" s="3">
+      <c r="H235" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}がスパーリング中に痛みを訴えた</t>
         </is>
@@ -6579,20 +7755,25 @@
       </c>
       <c r="B236" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C236" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr" s="12">
+      <c r="E236" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[5].detail</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr" s="3">
+      <c r="H236" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習パートナーとのスパーリングで{name}が技を受けた直後、顔をしかめて膝をついた。本人は続けられると言うが…</t>
         </is>
@@ -6606,20 +7787,25 @@
       </c>
       <c r="B237" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C237" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr" s="12">
+      <c r="E237" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[6].text</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr" s="3">
+      <c r="H237" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚠️ {name}が練習後に体の異変を報告</t>
         </is>
@@ -6633,20 +7819,25 @@
       </c>
       <c r="B238" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C238" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr" s="12">
+      <c r="E238" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B1[6].detail</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr" s="3">
+      <c r="H238" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">練習を終えた{name}が、動かすと痛む箇所があると申告。無理をしていた可能性がある。</t>
         </is>
@@ -6660,20 +7851,25 @@
       </c>
       <c r="B239" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C239" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr" s="12">
+      <c r="E239" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[1].text</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr" s="3">
+      <c r="H239" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💥 {name1}と{name2}が衝突</t>
         </is>
@@ -6687,20 +7883,25 @@
       </c>
       <c r="B240" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C240" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr" s="12">
+      <c r="E240" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[1].detail</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr" s="3">
+      <c r="H240" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">控室で{name1}と{name2}の間に激しい口論が発生。周囲の制止も聞かず一触即発の状態になっている。</t>
         </is>
@@ -6714,20 +7915,25 @@
       </c>
       <c r="B241" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C241" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr" s="12">
+      <c r="E241" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[2].text</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr" s="3">
+      <c r="H241" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💥 {name1}と{name2}の対立が深刻化</t>
         </is>
@@ -6741,20 +7947,25 @@
       </c>
       <c r="B242" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C242" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr" s="12">
+      <c r="E242" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[2].detail</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr" s="3">
+      <c r="H242" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">以前から不穏な空気があった{name1}と{name2}の関係がついに破綻。練習にも支障が出始めている。</t>
         </is>
@@ -6768,20 +7979,25 @@
       </c>
       <c r="B243" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C243" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr" s="12">
+      <c r="E243" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[3].text</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr" s="3">
+      <c r="H243" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💥 {name1}と{name2}がスパーリングでエスカレート</t>
         </is>
@@ -6795,20 +8011,25 @@
       </c>
       <c r="B244" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C244" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr" s="12">
+      <c r="E244" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[3].detail</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr" s="3">
+      <c r="H244" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">本来は軽い打ち合いのはずが、{name1}と{name2}のスパーリングが本気のぶつかり合いに発展。コーチが間に割って入る事態となった。</t>
         </is>
@@ -6822,20 +8043,25 @@
       </c>
       <c r="B245" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C245" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr" s="12">
+      <c r="E245" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[4].text</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr" s="3">
+      <c r="H245" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💥 {name1}と{name2}の間に亀裂</t>
         </is>
@@ -6849,20 +8075,25 @@
       </c>
       <c r="B246" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C246" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr" s="12">
+      <c r="E246" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[4].detail</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr" s="3">
+      <c r="H246" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{name1}がSNSに意味深な投稿をしたことで{name2}が激怒。控室で怒鳴り合う二人の声が外まで漏れていた。</t>
         </is>
@@ -6876,20 +8107,25 @@
       </c>
       <c r="B247" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C247" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr" s="12">
+      <c r="E247" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[5].text</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr" s="3">
+      <c r="H247" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">💥 {name1}と{name2}の関係が限界に</t>
         </is>
@@ -6903,20 +8139,25 @@
       </c>
       <c r="B248" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C248" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr" s="12">
+      <c r="E248" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B2[5].detail</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr" s="3">
+      <c r="H248" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">合同練習中、{name1}が{name2}への不満を公然と口にした。全員の前での出来事に、チーム全体が凍りついた。</t>
         </is>
@@ -6930,20 +8171,25 @@
       </c>
       <c r="B249" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C249" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr" s="12">
+      <c r="E249" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[1].text</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr" s="3">
+      <c r="H249" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚔️ {orgName}から挑戦状</t>
         </is>
@@ -6957,20 +8203,25 @@
       </c>
       <c r="B250" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C250" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr" s="12">
+      <c r="E250" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[1].detail</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr" s="3">
+      <c r="H250" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{orgName}が「実力を見せてやる」と挑戦状を叩きつけてきた。</t>
         </is>
@@ -6984,20 +8235,25 @@
       </c>
       <c r="B251" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C251" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr" s="12">
+      <c r="E251" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[2].text</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr" s="3">
+      <c r="H251" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚔️ {orgName}が宣戦布告</t>
         </is>
@@ -7011,20 +8267,25 @@
       </c>
       <c r="B252" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C252" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr" s="12">
+      <c r="E252" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[2].detail</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr" s="3">
+      <c r="H252" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{orgName}の代表が公の場でこちらの団体を挑発。挑戦状で決着をつけようと迫ってきた。</t>
         </is>
@@ -7038,20 +8299,25 @@
       </c>
       <c r="B253" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C253" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D253" t="inlineStr" s="12">
+      <c r="E253" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[3].text</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr" s="3">
+      <c r="H253" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚔️ {orgName}の選手が記者会見で挑発</t>
         </is>
@@ -7065,20 +8331,25 @@
       </c>
       <c r="B254" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C254" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr" s="12">
+      <c r="E254" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[3].detail</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr" s="3">
+      <c r="H254" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{orgName}の選手がメディアの前でこちらの団体名を出し、「いつでも受けて立つ」と公開挑戦状を叩きつけた。</t>
         </is>
@@ -7092,20 +8363,25 @@
       </c>
       <c r="B255" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C255" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr" s="12">
+      <c r="E255" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[4].text</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr" s="3">
+      <c r="H255" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚔️ {orgName}から果たし状が届いた</t>
         </is>
@@ -7119,20 +8395,25 @@
       </c>
       <c r="B256" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C256" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr" s="12">
+      <c r="E256" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[4].detail</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr" s="3">
+      <c r="H256" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{orgName}から正式な書面が届いた。「団体の威信をかけて一騎打ちを行いたい」——無視するわけにはいかない雰囲気だ。</t>
         </is>
@@ -7146,20 +8427,25 @@
       </c>
       <c r="B257" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C257" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr" s="12">
+      <c r="E257" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[5].text</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr" s="3">
+      <c r="H257" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">⚔️ {orgName}が興行に乗り込んできた</t>
         </is>
@@ -7173,20 +8459,25 @@
       </c>
       <c r="B258" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C258" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D258" t="inlineStr" s="12">
+      <c r="E258" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B3[5].detail</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr" s="3">
+      <c r="H258" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">こちらの興行会場に{orgName}の関係者が姿を見せ、「リングで語り合おう」と挑戦状を突きつけてきた。</t>
         </is>
@@ -7200,20 +8491,25 @@
       </c>
       <c r="B259" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C259" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr" s="12">
+      <c r="E259" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.youngStar[1].text</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr" s="3">
+      <c r="H259" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}から若手特集の申し入れ</t>
         </is>
@@ -7227,20 +8523,25 @@
       </c>
       <c r="B260" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C260" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr" s="12">
+      <c r="E260" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.youngStar[1].detail</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr" s="3">
+      <c r="H260" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「次世代のスターを追いかけたい」と密着取材を申し出ている。</t>
         </is>
@@ -7254,20 +8555,25 @@
       </c>
       <c r="B261" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C261" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr" s="12">
+      <c r="E261" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.youngStar[2].text</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr" s="3">
+      <c r="H261" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}が注目の新星を追いたいと打診</t>
         </is>
@@ -7281,20 +8587,25 @@
       </c>
       <c r="B262" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C262" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D262" t="inlineStr" s="12">
+      <c r="E262" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.youngStar[2].detail</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr" s="3">
+      <c r="H262" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}のディレクターが「若い才能に密着したい」と話を持ちかけてきた。</t>
         </is>
@@ -7308,20 +8619,25 @@
       </c>
       <c r="B263" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C263" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr" s="12">
+      <c r="E263" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.youngStar[3].text</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr" s="3">
+      <c r="H263" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}の「若手発掘」企画にうちの選手が候補に</t>
         </is>
@@ -7335,20 +8651,25 @@
       </c>
       <c r="B264" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C264" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr" s="12">
+      <c r="E264" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.youngStar[3].detail</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr" s="3">
+      <c r="H264" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「プロレス界の未来を担う若手を追う」——{outletName}からそんな企画の依頼が来た。</t>
         </is>
@@ -7362,20 +8683,25 @@
       </c>
       <c r="B265" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C265" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D265" t="inlineStr" s="12">
+      <c r="E265" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.ace[1].text</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr" s="3">
+      <c r="H265" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}がエース密着企画を提案</t>
         </is>
@@ -7389,20 +8715,25 @@
       </c>
       <c r="B266" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C266" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr" s="12">
+      <c r="E266" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.ace[1].detail</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr" s="3">
+      <c r="H266" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「団体の顔に密着したい」とドキュメンタリー企画を持ち込んできた。</t>
         </is>
@@ -7416,20 +8747,25 @@
       </c>
       <c r="B267" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C267" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr" s="12">
+      <c r="E267" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.ace[2].text</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr" s="3">
+      <c r="H267" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}から「頂点の景色」取材オファー</t>
         </is>
@@ -7443,20 +8779,25 @@
       </c>
       <c r="B268" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C268" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr" s="12">
+      <c r="E268" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.ace[2].detail</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr" s="3">
+      <c r="H268" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「頂点に立つ選手の日常を追いたい」と密着取材を打診してきた。</t>
         </is>
@@ -7470,20 +8811,25 @@
       </c>
       <c r="B269" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C269" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr" s="12">
+      <c r="E269" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.ace[3].text</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr" s="3">
+      <c r="H269" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}がトップ選手の特集を企画中</t>
         </is>
@@ -7497,20 +8843,25 @@
       </c>
       <c r="B270" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C270" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr" s="12">
+      <c r="E270" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.ace[3].detail</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr" s="3">
+      <c r="H270" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「団体を背負うエースに迫る」——{outletName}からそんなオファーが届いた。推薦する選手を選んでほしいという。</t>
         </is>
@@ -7524,20 +8875,25 @@
       </c>
       <c r="B271" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C271" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr" s="12">
+      <c r="E271" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.veteran[1].text</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr" s="3">
+      <c r="H271" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}がベテラン特集を企画</t>
         </is>
@@ -7551,20 +8907,25 @@
       </c>
       <c r="B272" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C272" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr" s="12">
+      <c r="E272" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.veteran[1].detail</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr" s="3">
+      <c r="H272" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「長く戦い続ける選手の矜持に迫りたい」と密着取材を申し出ている。</t>
         </is>
@@ -7578,20 +8939,25 @@
       </c>
       <c r="B273" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C273" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr" s="12">
+      <c r="E273" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.veteran[2].text</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr" s="3">
+      <c r="H273" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}から「キャリアの深み」取材依頼</t>
         </is>
@@ -7605,20 +8971,25 @@
       </c>
       <c r="B274" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C274" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr" s="12">
+      <c r="E274" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.veteran[2].detail</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr" s="3">
+      <c r="H274" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}のプロデューサーが来訪。「経験豊富な選手の素顔を追いたい」とのこと。</t>
         </is>
@@ -7632,20 +9003,25 @@
       </c>
       <c r="B275" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C275" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr" s="12">
+      <c r="E275" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.veteran[3].text</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr" s="3">
+      <c r="H275" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}が「円熟の技」ドキュメントを提案</t>
         </is>
@@ -7659,20 +9035,25 @@
       </c>
       <c r="B276" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C276" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D276" t="inlineStr" s="12">
+      <c r="E276" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4.veteran[3].detail</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr" s="3">
+      <c r="H276" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「ベテランだからこそ見える景色がある」——{outletName}からそんなテーマの企画が持ち込まれた。</t>
         </is>
@@ -7686,20 +9067,25 @@
       </c>
       <c r="B277" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C277" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr" s="12">
+      <c r="E277" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_cm[1].text</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr" s="3">
+      <c r="H277" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📸 {outletName}からCM出演の打診</t>
         </is>
@@ -7713,20 +9099,25 @@
       </c>
       <c r="B278" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C278" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr" s="12">
+      <c r="E278" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_cm[1].detail</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr" s="3">
+      <c r="H278" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}から「選手をCMの顔として起用したい」と打診が来た。</t>
         </is>
@@ -7740,20 +9131,25 @@
       </c>
       <c r="B279" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C279" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr" s="12">
+      <c r="E279" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_cm[2].text</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr" s="3">
+      <c r="H279" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📸 {outletName}がCMキャストを探している</t>
         </is>
@@ -7767,20 +9163,25 @@
       </c>
       <c r="B280" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C280" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr" s="12">
+      <c r="E280" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_cm[2].detail</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr" s="3">
+      <c r="H280" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「プロレスラーのカッコよさをCMで表現したい」——{outletName}からそんな依頼が届いた。</t>
         </is>
@@ -7794,20 +9195,25 @@
       </c>
       <c r="B281" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C281" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr" s="12">
+      <c r="E281" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_cm[3].text</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr" s="3">
+      <c r="H281" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📸 {outletName}のCM出演オファー</t>
         </is>
@@ -7821,20 +9227,25 @@
       </c>
       <c r="B282" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C282" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr" s="12">
+      <c r="E282" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_cm[3].detail</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr" s="3">
+      <c r="H282" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}のプロデューサーが来訪。「うちの団体の選手を広告塔に使いたい」とのこと。</t>
         </is>
@@ -7848,20 +9259,25 @@
       </c>
       <c r="B283" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C283" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr" s="12">
+      <c r="E283" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_gravure[1].text</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr" s="3">
+      <c r="H283" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📷 {outletName}からグラビア撮影の依頼</t>
         </is>
@@ -7875,20 +9291,25 @@
       </c>
       <c r="B284" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C284" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D284" t="inlineStr" s="12">
+      <c r="E284" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_gravure[1].detail</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr" s="3">
+      <c r="H284" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「プロレスラーの魅力をグラビアで届けたい」と申し出てきた。</t>
         </is>
@@ -7902,20 +9323,25 @@
       </c>
       <c r="B285" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C285" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr" s="12">
+      <c r="E285" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_gravure[2].text</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr" s="3">
+      <c r="H285" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📷 {outletName}がグラビア特集企画を検討</t>
         </is>
@@ -7929,20 +9355,25 @@
       </c>
       <c r="B286" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C286" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr" s="12">
+      <c r="E286" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_gravure[2].detail</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr" s="3">
+      <c r="H286" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「女子プロレスラーの素顔に迫りたい」——{outletName}からそんな企画の打診が来た。</t>
         </is>
@@ -7956,20 +9387,25 @@
       </c>
       <c r="B287" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C287" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr" s="12">
+      <c r="E287" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_gravure[3].text</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr" s="3">
+      <c r="H287" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📷 {outletName}からグラビア出演のオファー</t>
         </is>
@@ -7983,20 +9419,25 @@
       </c>
       <c r="B288" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C288" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr" s="12">
+      <c r="E288" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_gravure[3].detail</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr" s="3">
+      <c r="H288" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}の編集長から直接連絡が入った。「ぜひ選手を誌面に起用したい」とのこと。</t>
         </is>
@@ -8010,20 +9451,25 @@
       </c>
       <c r="B289" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C289" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr" s="12">
+      <c r="E289" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_variety[1].text</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr" s="3">
+      <c r="H289" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}からバラエティ出演のオファー</t>
         </is>
@@ -8037,20 +9483,25 @@
       </c>
       <c r="B290" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C290" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr" s="12">
+      <c r="E290" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_variety[1].detail</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr" s="3">
+      <c r="H290" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「プロレスラーがゲスト出演するコーナーを作りたい」と打診してきた。</t>
         </is>
@@ -8064,20 +9515,25 @@
       </c>
       <c r="B291" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C291" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr" s="12">
+      <c r="E291" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_variety[2].text</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr" s="3">
+      <c r="H291" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}がゲスト出演の候補を探している</t>
         </is>
@@ -8091,20 +9547,25 @@
       </c>
       <c r="B292" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C292" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr" s="12">
+      <c r="E292" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_variety[2].detail</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr" s="3">
+      <c r="H292" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「面白いキャラクターのプロレスラーを探している」——{outletName}からそんな依頼が届いた。</t>
         </is>
@@ -8118,20 +9579,25 @@
       </c>
       <c r="B293" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C293" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr" s="12">
+      <c r="E293" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_variety[3].text</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr" s="3">
+      <c r="H293" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">📺 {outletName}のトーク番組に出演依頼</t>
         </is>
@@ -8145,20 +9611,25 @@
       </c>
       <c r="B294" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C294" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr" s="12">
+      <c r="E294" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_variety[3].detail</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr" s="3">
+      <c r="H294" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}のディレクターが来訪。「選手のキャラクターを全国に届けたい」とのこと。</t>
         </is>
@@ -8172,20 +9643,25 @@
       </c>
       <c r="B295" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C295" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr" s="12">
+      <c r="E295" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_brand[1].text</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr" s="3">
+      <c r="H295" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🤝 {outletName}からコラボ商品の提案</t>
         </is>
@@ -8199,20 +9675,25 @@
       </c>
       <c r="B296" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C296" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr" s="12">
+      <c r="E296" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_brand[1].detail</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr" s="3">
+      <c r="H296" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「選手とのコラボ商品を作りたい」と申し出てきた。</t>
         </is>
@@ -8226,20 +9707,25 @@
       </c>
       <c r="B297" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C297" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr" s="12">
+      <c r="E297" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_brand[2].text</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr" s="3">
+      <c r="H297" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🤝 {outletName}がコラボパートナーを探している</t>
         </is>
@@ -8253,20 +9739,25 @@
       </c>
       <c r="B298" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C298" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr" s="12">
+      <c r="E298" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_brand[2].detail</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr" s="3">
+      <c r="H298" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「プロレスのパワーとブランドのスタイルを組み合わせたい」——{outletName}からそんな話が来た。</t>
         </is>
@@ -8280,20 +9771,25 @@
       </c>
       <c r="B299" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C299" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr" s="12">
+      <c r="E299" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_brand[3].text</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr" s="3">
+      <c r="H299" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🤝 {outletName}とのコラボ企画の打診</t>
         </is>
@@ -8307,20 +9803,25 @@
       </c>
       <c r="B300" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C300" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr" s="12">
+      <c r="E300" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_brand[3].detail</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr" s="3">
+      <c r="H300" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}の担当者が来訪。「選手のイメージを商品に落とし込みたい」とのこと。</t>
         </is>
@@ -8334,20 +9835,25 @@
       </c>
       <c r="B301" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C301" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr" s="12">
+      <c r="E301" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fashion[1].text</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr" s="3">
+      <c r="H301" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👗 {outletName}のランウェイ出演オファー</t>
         </is>
@@ -8361,20 +9867,25 @@
       </c>
       <c r="B302" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C302" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr" s="12">
+      <c r="E302" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fashion[1].detail</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr" s="3">
+      <c r="H302" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}が「アスリートのランウェイ参加を企画している」と打診してきた。</t>
         </is>
@@ -8388,20 +9899,25 @@
       </c>
       <c r="B303" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C303" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr" s="12">
+      <c r="E303" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fashion[2].text</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr" s="3">
+      <c r="H303" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👗 {outletName}がファッションショー出演者を募集</t>
         </is>
@@ -8415,20 +9931,25 @@
       </c>
       <c r="B304" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C304" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr" s="12">
+      <c r="E304" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fashion[2].detail</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr" s="3">
+      <c r="H304" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「プロレスラーの迫力をランウェイで表現したい」——{outletName}からそんな話が届いた。</t>
         </is>
@@ -8442,20 +9963,25 @@
       </c>
       <c r="B305" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C305" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr" s="12">
+      <c r="E305" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fashion[3].text</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr" s="3">
+      <c r="H305" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">👗 {outletName}のコレクションへの参加依頼</t>
         </is>
@@ -8469,20 +9995,25 @@
       </c>
       <c r="B306" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C306" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr" s="12">
+      <c r="E306" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fashion[3].detail</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr" s="3">
+      <c r="H306" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">{outletName}のデザイナーが来訪。「ぜひ選手にランウェイを歩いてほしい」とのこと。</t>
         </is>
@@ -8496,20 +10027,25 @@
       </c>
       <c r="B307" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C307" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr" s="12">
+      <c r="E307" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fan[1].text</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr" s="3">
+      <c r="H307" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🎤 ファンイベント開催の打診</t>
         </is>
@@ -8523,20 +10059,25 @@
       </c>
       <c r="B308" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C308" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr" s="12">
+      <c r="E308" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fan[1].detail</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr" s="3">
+      <c r="H308" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">主催者から「選手とファンが直接交流できるイベントを開きたい」と相談が来た。</t>
         </is>
@@ -8550,20 +10091,25 @@
       </c>
       <c r="B309" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C309" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr" s="12">
+      <c r="E309" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fan[2].text</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr" s="3">
+      <c r="H309" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🎤 サイン会・トークショーの開催依頼</t>
         </is>
@@ -8577,20 +10123,25 @@
       </c>
       <c r="B310" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C310" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr" s="12">
+      <c r="E310" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fan[2].detail</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr" s="3">
+      <c r="H310" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「ファンと選手が触れ合える機会を作りたい」——イベント会社からそんな提案が届いた。</t>
         </is>
@@ -8604,20 +10155,25 @@
       </c>
       <c r="B311" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C311" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr" s="12">
+      <c r="E311" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fan[3].text</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr" s="3">
+      <c r="H311" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">🎤 ファンミーティングの企画提案</t>
         </is>
@@ -8631,27 +10187,32 @@
       </c>
       <c r="B312" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">src/data.js</t>
+          <t xml:space="preserve">通知・スナップショット系</t>
         </is>
       </c>
       <c r="C312" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">src/data.js</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">LARGE_EVENT_TEXTS</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr" s="12">
+      <c r="E312" t="inlineStr" s="12">
         <is>
           <t xml:space="preserve">B4_fan[3].detail</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr" s="3">
+      <c r="H312" t="inlineStr" s="3">
         <is>
           <t xml:space="preserve">「選手の素顔をファンに見せる場を作りたい」と主催者から打診があった。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I312"/>
+  <autoFilter ref="A1:J312"/>
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
